--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>100478863</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582098.489331683</v>
+        <v>582099</v>
       </c>
       <c r="R3" t="n">
-        <v>6958385.971295028</v>
+        <v>6958386</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +865,9 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,7 +902,7 @@
         <v>100478964</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582069.4349294722</v>
+        <v>582069</v>
       </c>
       <c r="R4" t="n">
-        <v>6958409.546711401</v>
+        <v>6958410</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -987,19 +977,9 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1146,7 +1126,7 @@
         <v>100478894</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582097.5716244632</v>
+        <v>582098</v>
       </c>
       <c r="R6" t="n">
-        <v>6958385.948406713</v>
+        <v>6958386</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1221,19 +1201,9 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>100478863</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>100478964</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>100478894</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>100478863</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>100478964</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>100478894</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>100478863</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>100478964</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>100478894</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>100478863</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>100478964</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>100478894</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,7576 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127626360</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>581836</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6958416</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127626338</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>581544</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6958500</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127626319</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>581409</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6958406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127626355</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>581582</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6958488</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127626320</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>581658</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6958452</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127626344</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>581534</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6958399</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127626287</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>581481</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6958554</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127626332</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>581833</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6958448</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127626348</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>582065</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6958321</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127626289</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>581425</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6958401</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127626323</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>581803</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6958429</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127626285</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>581551</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6958485</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127626336</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>582065</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6958323</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127626321</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>581718</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6958467</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127626322</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>581761</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6958462</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127626356</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>581795</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6958432</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127626306</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>581878</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6958484</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127626283</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>582010</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6958445</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127626309</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>581870</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6958478</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127626312</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>581642</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6958463</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127626317</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>581500</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6958522</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Misstänkt äldre bohål</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127626293</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>581771</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6958476</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127626291</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>581538</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6958404</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127626333</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>581835</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6958440</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127626295</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>581885</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6958529</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127626305</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>581928</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6958485</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127626340</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>581474</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6958474</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127626318</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>581380</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6958472</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127626324</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>581807</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6958490</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127626302</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>582050</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6958390</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127622592</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91688</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>581432</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6958399</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127626337</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91784</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>581550</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6958488</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127626347</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>582104</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6958386</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127626299</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>582073</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6958325</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127626292</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>581696</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6958457</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127626325</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>581819</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6958488</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127626300</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>582063</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6958321</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127626354</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>582103</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6958332</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127626284</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>581922</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6958467</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127626327</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>581824</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6958505</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127626350</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>581948</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6958486</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127626316</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>581480</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6958548</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127626297</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>582085</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6958383</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127626342</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>658</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>581440</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6958403</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127626345</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>658</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>581775</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6958475</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127626282</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>581658</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6958442</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127626351</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>581501</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6958530</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127626296</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>581882</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6958519</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127620475</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>581829</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6958465</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127626339</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>658</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>581484</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6958540</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127626290</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>581438</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6958399</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127626352</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>581490</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6958524</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127626303</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>582006</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6958447</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127626329</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>581831</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6958455</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127626315</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>581503</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6958538</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127626294</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>581835</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6958427</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127626343</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>658</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>581513</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6958410</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127626353</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>581843</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6958404</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127626314</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>581570</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6958491</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127620834</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>581829</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6958465</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Död gran med tre bohål som misstänks tillhöra tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127626361</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92000</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>898</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>581464</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6958401</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127626298</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>582124</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6958327</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127626358</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>582087</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6958421</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127626301</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>582037</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6958341</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127626286</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>581497</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6958542</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127626328</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>581823</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6958452</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127626357</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>581828</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6958421</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127622082</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>581489</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6958404</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127626326</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>581814</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6958498</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127626346</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>581833</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6958501</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127626307</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>581874</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6958490</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127627415</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91531</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>48</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>581429</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6958404</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127626304</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>581961</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6958482</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127626311</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>581684</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6958471</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127626288</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>581468</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6958479</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127626341</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>658</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>581425</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6958396</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626360</v>
+        <v>127626338</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581836</v>
+        <v>581544</v>
       </c>
       <c r="R7" t="n">
-        <v>6958416</v>
+        <v>6958500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626338</v>
+        <v>127626319</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581544</v>
+        <v>581409</v>
       </c>
       <c r="R8" t="n">
-        <v>6958500</v>
+        <v>6958406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R9" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R10" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B12" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R12" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R15" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626289</v>
+        <v>127626348</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581425</v>
+        <v>582065</v>
       </c>
       <c r="R16" t="n">
-        <v>6958401</v>
+        <v>6958321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626285</v>
+        <v>127626336</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581551</v>
+        <v>582065</v>
       </c>
       <c r="R18" t="n">
-        <v>6958485</v>
+        <v>6958323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626336</v>
+        <v>127626321</v>
       </c>
       <c r="B19" t="n">
-        <v>80150</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582065</v>
+        <v>581718</v>
       </c>
       <c r="R19" t="n">
-        <v>6958323</v>
+        <v>6958467</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626321</v>
+        <v>127626285</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581718</v>
+        <v>581551</v>
       </c>
       <c r="R20" t="n">
-        <v>6958467</v>
+        <v>6958485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,11 +2592,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626322</v>
+        <v>127626356</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581761</v>
+        <v>581795</v>
       </c>
       <c r="R21" t="n">
-        <v>6958462</v>
+        <v>6958432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626356</v>
+        <v>127626306</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,21 +2726,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581795</v>
+        <v>581878</v>
       </c>
       <c r="R22" t="n">
-        <v>6958432</v>
+        <v>6958484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2791,6 +2786,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626306</v>
+        <v>127626322</v>
       </c>
       <c r="B23" t="n">
         <v>57661</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581878</v>
+        <v>581761</v>
       </c>
       <c r="R23" t="n">
-        <v>6958484</v>
+        <v>6958462</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3016,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626309</v>
+        <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,21 +3027,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581870</v>
+        <v>581771</v>
       </c>
       <c r="R25" t="n">
-        <v>6958478</v>
+        <v>6958476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3118,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3129,21 +3124,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R26" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3189,11 +3184,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,7 +3210,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626317</v>
+        <v>127626309</v>
       </c>
       <c r="B27" t="n">
         <v>57661</v>
@@ -3255,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581500</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6958522</v>
+        <v>6958478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,7 +3285,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Misstänkt äldre bohål</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3322,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B28" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3323,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R28" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,6 +3383,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3419,10 +3414,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3454,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R29" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3485,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3516,7 +3516,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626333</v>
+        <v>127626302</v>
       </c>
       <c r="B30" t="n">
         <v>57661</v>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581835</v>
+        <v>582050</v>
       </c>
       <c r="R30" t="n">
-        <v>6958440</v>
+        <v>6958390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,7 +3618,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626295</v>
+        <v>127626305</v>
       </c>
       <c r="B31" t="n">
         <v>57661</v>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581885</v>
+        <v>581928</v>
       </c>
       <c r="R31" t="n">
-        <v>6958529</v>
+        <v>6958485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3720,7 +3720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626305</v>
+        <v>127626318</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581928</v>
+        <v>581380</v>
       </c>
       <c r="R32" t="n">
-        <v>6958485</v>
+        <v>6958472</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626340</v>
+        <v>127626324</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581474</v>
+        <v>581807</v>
       </c>
       <c r="R33" t="n">
-        <v>6958474</v>
+        <v>6958490</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3893,6 +3893,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,7 +3924,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626318</v>
+        <v>127626295</v>
       </c>
       <c r="B34" t="n">
         <v>57661</v>
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581380</v>
+        <v>581885</v>
       </c>
       <c r="R34" t="n">
-        <v>6958472</v>
+        <v>6958529</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,7 +3999,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,45 +4026,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626324</v>
+        <v>127622592</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>91688</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581807</v>
+        <v>581432</v>
       </c>
       <c r="R35" t="n">
-        <v>6958490</v>
+        <v>6958399</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,11 +4097,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127626302</v>
+        <v>127626340</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582050</v>
+        <v>581474</v>
       </c>
       <c r="R36" t="n">
-        <v>6958390</v>
+        <v>6958474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,45 +4220,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127622592</v>
+        <v>127626292</v>
       </c>
       <c r="B37" t="n">
-        <v>91688</v>
+        <v>91330</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581432</v>
+        <v>581696</v>
       </c>
       <c r="R37" t="n">
-        <v>6958399</v>
+        <v>6958457</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4419,32 +4414,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626347</v>
+        <v>127626354</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582104</v>
+        <v>582103</v>
       </c>
       <c r="R39" t="n">
-        <v>6958386</v>
+        <v>6958332</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,32 +4511,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626299</v>
+        <v>127626347</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4546,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582073</v>
+        <v>582104</v>
       </c>
       <c r="R40" t="n">
-        <v>6958325</v>
+        <v>6958386</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4582,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4608,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626292</v>
+        <v>127626299</v>
       </c>
       <c r="B41" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4619,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4643,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581696</v>
+        <v>582073</v>
       </c>
       <c r="R41" t="n">
-        <v>6958457</v>
+        <v>6958325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4679,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4715,7 +4710,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626325</v>
+        <v>127626300</v>
       </c>
       <c r="B42" t="n">
         <v>57661</v>
@@ -4750,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581819</v>
+        <v>582063</v>
       </c>
       <c r="R42" t="n">
-        <v>6958488</v>
+        <v>6958321</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4817,7 +4812,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626300</v>
+        <v>127626325</v>
       </c>
       <c r="B43" t="n">
         <v>57661</v>
@@ -4852,10 +4847,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582063</v>
+        <v>581819</v>
       </c>
       <c r="R43" t="n">
-        <v>6958321</v>
+        <v>6958488</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626354</v>
+        <v>127626342</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4954,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582103</v>
+        <v>581440</v>
       </c>
       <c r="R44" t="n">
-        <v>6958332</v>
+        <v>6958403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5113,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626327</v>
+        <v>127626350</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5124,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5148,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581824</v>
+        <v>581948</v>
       </c>
       <c r="R46" t="n">
-        <v>6958505</v>
+        <v>6958486</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,11 +5179,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5215,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626350</v>
+        <v>127626297</v>
       </c>
       <c r="B47" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5226,21 +5216,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5250,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581948</v>
+        <v>582085</v>
       </c>
       <c r="R47" t="n">
-        <v>6958486</v>
+        <v>6958383</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,6 +5276,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5312,7 +5307,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626316</v>
+        <v>127626327</v>
       </c>
       <c r="B48" t="n">
         <v>57661</v>
@@ -5347,10 +5342,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581480</v>
+        <v>581824</v>
       </c>
       <c r="R48" t="n">
-        <v>6958548</v>
+        <v>6958505</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,7 +5409,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626297</v>
+        <v>127626316</v>
       </c>
       <c r="B49" t="n">
         <v>57661</v>
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582085</v>
+        <v>581480</v>
       </c>
       <c r="R49" t="n">
-        <v>6958383</v>
+        <v>6958548</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5516,10 +5511,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626342</v>
+        <v>127626296</v>
       </c>
       <c r="B50" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,21 +5522,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581440</v>
+        <v>581882</v>
       </c>
       <c r="R50" t="n">
-        <v>6958403</v>
+        <v>6958519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5587,6 +5582,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626282</v>
+        <v>127626351</v>
       </c>
       <c r="B52" t="n">
-        <v>91295</v>
+        <v>91348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581658</v>
+        <v>581501</v>
       </c>
       <c r="R52" t="n">
-        <v>6958442</v>
+        <v>6958530</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B53" t="n">
-        <v>91348</v>
+        <v>91295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R53" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626296</v>
+        <v>127626339</v>
       </c>
       <c r="B54" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,21 +5915,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581882</v>
+        <v>581484</v>
       </c>
       <c r="R54" t="n">
-        <v>6958519</v>
+        <v>6958540</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5975,11 +5975,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6006,7 +6001,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127620475</v>
+        <v>127626290</v>
       </c>
       <c r="B55" t="n">
         <v>91330</v>
@@ -6037,14 +6032,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581829</v>
+        <v>581438</v>
       </c>
       <c r="R55" t="n">
-        <v>6958465</v>
+        <v>6958399</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626339</v>
+        <v>127620475</v>
       </c>
       <c r="B56" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,34 +6109,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581484</v>
+        <v>581829</v>
       </c>
       <c r="R56" t="n">
-        <v>6958540</v>
+        <v>6958465</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6200,10 +6195,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626290</v>
+        <v>127626303</v>
       </c>
       <c r="B57" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6206,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581438</v>
+        <v>582006</v>
       </c>
       <c r="R57" t="n">
-        <v>6958399</v>
+        <v>6958447</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,6 +6266,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6297,10 +6297,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127626352</v>
+        <v>127626329</v>
       </c>
       <c r="B58" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6308,21 +6308,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581490</v>
+        <v>581831</v>
       </c>
       <c r="R58" t="n">
-        <v>6958524</v>
+        <v>6958455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6368,6 +6368,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6394,10 +6399,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626303</v>
+        <v>127626352</v>
       </c>
       <c r="B59" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6405,21 +6410,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>582006</v>
+        <v>581490</v>
       </c>
       <c r="R59" t="n">
-        <v>6958447</v>
+        <v>6958524</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6465,11 +6470,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6496,7 +6496,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626329</v>
+        <v>127626315</v>
       </c>
       <c r="B60" t="n">
         <v>57661</v>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581831</v>
+        <v>581503</v>
       </c>
       <c r="R60" t="n">
-        <v>6958455</v>
+        <v>6958538</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626315</v>
+        <v>127626343</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581503</v>
+        <v>581513</v>
       </c>
       <c r="R61" t="n">
-        <v>6958538</v>
+        <v>6958410</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,11 +6669,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6797,10 +6792,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626343</v>
+        <v>127626353</v>
       </c>
       <c r="B63" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,21 +6803,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6827,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581513</v>
+        <v>581843</v>
       </c>
       <c r="R63" t="n">
-        <v>6958410</v>
+        <v>6958404</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6894,10 +6889,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B64" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6905,21 +6900,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6929,10 +6924,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R64" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6965,6 +6960,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626314</v>
+        <v>127626298</v>
       </c>
       <c r="B65" t="n">
         <v>57661</v>
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581570</v>
+        <v>582124</v>
       </c>
       <c r="R65" t="n">
-        <v>6958491</v>
+        <v>6958327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7093,50 +7093,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127620834</v>
+        <v>127626361</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>92000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581829</v>
+        <v>581464</v>
       </c>
       <c r="R66" t="n">
-        <v>6958465</v>
+        <v>6958401</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,11 +7164,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Död gran med tre bohål som misstänks tillhöra tretåig hackspett</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,32 +7190,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626361</v>
+        <v>127626301</v>
       </c>
       <c r="B67" t="n">
-        <v>92000</v>
+        <v>57661</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7225,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581464</v>
+        <v>582037</v>
       </c>
       <c r="R67" t="n">
-        <v>6958401</v>
+        <v>6958341</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7261,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,32 +7292,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7327,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R68" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,11 +7363,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7399,32 +7389,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626358</v>
+        <v>127626286</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>91330</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7434,10 +7424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>582087</v>
+        <v>581497</v>
       </c>
       <c r="R69" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7496,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127626301</v>
+        <v>127626357</v>
       </c>
       <c r="B70" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7507,21 +7497,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7531,10 +7521,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>582037</v>
+        <v>581828</v>
       </c>
       <c r="R70" t="n">
-        <v>6958341</v>
+        <v>6958421</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,7 +7561,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7598,10 +7588,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B71" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7609,21 +7599,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7633,10 +7623,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R71" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7669,6 +7659,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7695,7 +7690,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127626328</v>
+        <v>127626326</v>
       </c>
       <c r="B72" t="n">
         <v>57661</v>
@@ -7730,10 +7725,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581823</v>
+        <v>581814</v>
       </c>
       <c r="R72" t="n">
-        <v>6958452</v>
+        <v>6958498</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7797,10 +7792,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626357</v>
+        <v>127622082</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7808,34 +7803,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581828</v>
+        <v>581489</v>
       </c>
       <c r="R73" t="n">
-        <v>6958421</v>
+        <v>6958404</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7868,11 +7872,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7899,54 +7898,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127622082</v>
+        <v>127626346</v>
       </c>
       <c r="B74" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581489</v>
+        <v>581833</v>
       </c>
       <c r="R74" t="n">
-        <v>6958404</v>
+        <v>6958501</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8005,45 +7995,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626326</v>
+        <v>127627415</v>
       </c>
       <c r="B75" t="n">
-        <v>57661</v>
+        <v>91531</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581814</v>
+        <v>581429</v>
       </c>
       <c r="R75" t="n">
-        <v>6958498</v>
+        <v>6958404</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8078,17 +8071,13 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8107,32 +8096,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626346</v>
+        <v>127626307</v>
       </c>
       <c r="B76" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8131,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581833</v>
+        <v>581874</v>
       </c>
       <c r="R76" t="n">
-        <v>6958501</v>
+        <v>6958490</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8178,6 +8167,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8204,10 +8198,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127626307</v>
+        <v>127626288</v>
       </c>
       <c r="B77" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,21 +8209,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8239,10 +8233,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>581874</v>
+        <v>581468</v>
       </c>
       <c r="R77" t="n">
-        <v>6958490</v>
+        <v>6958479</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8275,11 +8269,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8306,48 +8295,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127627415</v>
+        <v>127626341</v>
       </c>
       <c r="B78" t="n">
-        <v>91531</v>
+        <v>91626</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>581429</v>
+        <v>581425</v>
       </c>
       <c r="R78" t="n">
-        <v>6958404</v>
+        <v>6958396</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8388,7 +8374,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8407,7 +8392,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127626304</v>
+        <v>127626311</v>
       </c>
       <c r="B79" t="n">
         <v>57661</v>
@@ -8442,10 +8427,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>581961</v>
+        <v>581684</v>
       </c>
       <c r="R79" t="n">
-        <v>6958482</v>
+        <v>6958471</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8482,7 +8467,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8509,7 +8494,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B80" t="n">
         <v>57661</v>
@@ -8544,10 +8529,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R80" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8584,7 +8569,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8611,10 +8596,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127626288</v>
+        <v>127626317</v>
       </c>
       <c r="B81" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8622,34 +8607,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>581468</v>
+        <v>581500</v>
       </c>
       <c r="R81" t="n">
-        <v>6958479</v>
+        <v>6958522</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8682,6 +8675,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Misstänkt äldre bohål i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8708,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127626341</v>
+        <v>127620834</v>
       </c>
       <c r="B82" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8719,34 +8717,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581425</v>
+        <v>581829</v>
       </c>
       <c r="R82" t="n">
-        <v>6958396</v>
+        <v>6958465</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8779,6 +8785,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Död gran med tre bohål som misstänks tillhöra tretåig hackspett. Två på ena sidan och ett på andra sidan.</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626320</v>
+        <v>127626355</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581658</v>
+        <v>581582</v>
       </c>
       <c r="R11" t="n">
-        <v>6958452</v>
+        <v>6958488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626355</v>
+        <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581582</v>
+        <v>581658</v>
       </c>
       <c r="R12" t="n">
-        <v>6958488</v>
+        <v>6958452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626356</v>
+        <v>127626322</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581795</v>
+        <v>581761</v>
       </c>
       <c r="R21" t="n">
-        <v>6958432</v>
+        <v>6958462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626306</v>
+        <v>127626356</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2750,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581878</v>
+        <v>581795</v>
       </c>
       <c r="R22" t="n">
-        <v>6958484</v>
+        <v>6958432</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,11 +2791,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626322</v>
+        <v>127626306</v>
       </c>
       <c r="B23" t="n">
         <v>57661</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581761</v>
+        <v>581878</v>
       </c>
       <c r="R23" t="n">
-        <v>6958462</v>
+        <v>6958484</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4026,45 +4026,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127622592</v>
+        <v>127626340</v>
       </c>
       <c r="B35" t="n">
-        <v>91688</v>
+        <v>91626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581432</v>
+        <v>581474</v>
       </c>
       <c r="R35" t="n">
-        <v>6958399</v>
+        <v>6958474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127626340</v>
+        <v>127626300</v>
       </c>
       <c r="B36" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581474</v>
+        <v>582063</v>
       </c>
       <c r="R36" t="n">
-        <v>6958474</v>
+        <v>6958321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4194,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,10 +4225,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626292</v>
+        <v>127626354</v>
       </c>
       <c r="B37" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4231,21 +4236,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581696</v>
+        <v>582103</v>
       </c>
       <c r="R37" t="n">
-        <v>6958457</v>
+        <v>6958332</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,32 +4322,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626337</v>
+        <v>127626347</v>
       </c>
       <c r="B38" t="n">
-        <v>91784</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4357,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581550</v>
+        <v>582104</v>
       </c>
       <c r="R38" t="n">
-        <v>6958488</v>
+        <v>6958386</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626354</v>
+        <v>127626292</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4425,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582103</v>
+        <v>581696</v>
       </c>
       <c r="R39" t="n">
-        <v>6958332</v>
+        <v>6958457</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,32 +4516,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626347</v>
+        <v>127626325</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582104</v>
+        <v>581819</v>
       </c>
       <c r="R40" t="n">
-        <v>6958386</v>
+        <v>6958488</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4582,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4710,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626300</v>
+        <v>127626342</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4721,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4745,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582063</v>
+        <v>581440</v>
       </c>
       <c r="R42" t="n">
-        <v>6958321</v>
+        <v>6958403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4781,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4812,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626325</v>
+        <v>127626284</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4847,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581819</v>
+        <v>581922</v>
       </c>
       <c r="R43" t="n">
-        <v>6958488</v>
+        <v>6958467</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4883,11 +4888,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4914,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626342</v>
+        <v>127626350</v>
       </c>
       <c r="B44" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581440</v>
+        <v>581948</v>
       </c>
       <c r="R44" t="n">
-        <v>6958403</v>
+        <v>6958486</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626284</v>
+        <v>127626316</v>
       </c>
       <c r="B45" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581922</v>
+        <v>581480</v>
       </c>
       <c r="R45" t="n">
-        <v>6958467</v>
+        <v>6958548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,6 +5082,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5108,10 +5113,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626350</v>
+        <v>127626297</v>
       </c>
       <c r="B46" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5124,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581948</v>
+        <v>582085</v>
       </c>
       <c r="R46" t="n">
-        <v>6958486</v>
+        <v>6958383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5179,6 +5184,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5205,7 +5215,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626297</v>
+        <v>127626327</v>
       </c>
       <c r="B47" t="n">
         <v>57661</v>
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>582085</v>
+        <v>581824</v>
       </c>
       <c r="R47" t="n">
-        <v>6958383</v>
+        <v>6958505</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5307,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626327</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5318,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5342,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581824</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958505</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5378,11 +5388,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5409,10 +5414,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626316</v>
+        <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5420,21 +5425,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5444,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581480</v>
+        <v>581501</v>
       </c>
       <c r="R49" t="n">
-        <v>6958548</v>
+        <v>6958530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5480,11 +5485,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626296</v>
+        <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>57661</v>
+        <v>91295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581882</v>
+        <v>581658</v>
       </c>
       <c r="R50" t="n">
-        <v>6958519</v>
+        <v>6958442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,11 +5582,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,10 +5608,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626345</v>
+        <v>127626296</v>
       </c>
       <c r="B51" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5619,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581775</v>
+        <v>581882</v>
       </c>
       <c r="R51" t="n">
-        <v>6958475</v>
+        <v>6958519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5684,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626351</v>
+        <v>127626339</v>
       </c>
       <c r="B52" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581501</v>
+        <v>581484</v>
       </c>
       <c r="R52" t="n">
-        <v>6958530</v>
+        <v>6958540</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626282</v>
+        <v>127626290</v>
       </c>
       <c r="B53" t="n">
-        <v>91295</v>
+        <v>91330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581658</v>
+        <v>581438</v>
       </c>
       <c r="R53" t="n">
-        <v>6958442</v>
+        <v>6958399</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626339</v>
+        <v>127620475</v>
       </c>
       <c r="B54" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,34 +5915,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581484</v>
+        <v>581829</v>
       </c>
       <c r="R54" t="n">
-        <v>6958540</v>
+        <v>6958465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626290</v>
+        <v>127626352</v>
       </c>
       <c r="B55" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581438</v>
+        <v>581490</v>
       </c>
       <c r="R55" t="n">
-        <v>6958399</v>
+        <v>6958524</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127620475</v>
+        <v>127626303</v>
       </c>
       <c r="B56" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6109,34 +6109,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581829</v>
+        <v>582006</v>
       </c>
       <c r="R56" t="n">
-        <v>6958465</v>
+        <v>6958447</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6169,6 +6169,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6195,7 +6200,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626303</v>
+        <v>127626329</v>
       </c>
       <c r="B57" t="n">
         <v>57661</v>
@@ -6230,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582006</v>
+        <v>581831</v>
       </c>
       <c r="R57" t="n">
-        <v>6958447</v>
+        <v>6958455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6270,7 +6275,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6297,7 +6302,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127626329</v>
+        <v>127626315</v>
       </c>
       <c r="B58" t="n">
         <v>57661</v>
@@ -6332,10 +6337,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581831</v>
+        <v>581503</v>
       </c>
       <c r="R58" t="n">
-        <v>6958455</v>
+        <v>6958538</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6372,7 +6377,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6399,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626352</v>
+        <v>127626343</v>
       </c>
       <c r="B59" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6410,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6434,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581490</v>
+        <v>581513</v>
       </c>
       <c r="R59" t="n">
-        <v>6958524</v>
+        <v>6958410</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6496,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626315</v>
+        <v>127626294</v>
       </c>
       <c r="B60" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6507,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6531,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581503</v>
+        <v>581835</v>
       </c>
       <c r="R60" t="n">
-        <v>6958538</v>
+        <v>6958427</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6567,11 +6572,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626343</v>
+        <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581513</v>
+        <v>581843</v>
       </c>
       <c r="R61" t="n">
-        <v>6958410</v>
+        <v>6958404</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6695,10 +6695,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626294</v>
+        <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6706,21 +6706,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581835</v>
+        <v>581570</v>
       </c>
       <c r="R62" t="n">
-        <v>6958427</v>
+        <v>6958491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6792,10 +6797,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626353</v>
+        <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6803,21 +6808,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6827,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581843</v>
+        <v>582124</v>
       </c>
       <c r="R63" t="n">
-        <v>6958404</v>
+        <v>6958327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6863,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6889,7 +6899,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626314</v>
+        <v>127626301</v>
       </c>
       <c r="B64" t="n">
         <v>57661</v>
@@ -6924,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581570</v>
+        <v>582037</v>
       </c>
       <c r="R64" t="n">
-        <v>6958491</v>
+        <v>6958341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6964,7 +6974,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6991,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7026,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R65" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7062,11 +7072,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7093,32 +7098,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626361</v>
+        <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>92000</v>
+        <v>91330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581464</v>
+        <v>581497</v>
       </c>
       <c r="R66" t="n">
-        <v>6958401</v>
+        <v>6958542</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626301</v>
+        <v>127626357</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7225,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>582037</v>
+        <v>581828</v>
       </c>
       <c r="R67" t="n">
-        <v>6958341</v>
+        <v>6958421</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7265,7 +7270,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7292,32 +7297,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626358</v>
+        <v>127626328</v>
       </c>
       <c r="B68" t="n">
-        <v>98364</v>
+        <v>57661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7327,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>582087</v>
+        <v>581823</v>
       </c>
       <c r="R68" t="n">
-        <v>6958421</v>
+        <v>6958452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7363,6 +7368,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7389,10 +7399,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626286</v>
+        <v>127622082</v>
       </c>
       <c r="B69" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,34 +7410,43 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581497</v>
+        <v>581489</v>
       </c>
       <c r="R69" t="n">
-        <v>6958542</v>
+        <v>6958404</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7486,10 +7505,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127626357</v>
+        <v>127626326</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,21 +7516,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7521,10 +7540,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581828</v>
+        <v>581814</v>
       </c>
       <c r="R70" t="n">
-        <v>6958421</v>
+        <v>6958498</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7561,7 +7580,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7588,7 +7607,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127626328</v>
+        <v>127626307</v>
       </c>
       <c r="B71" t="n">
         <v>57661</v>
@@ -7623,10 +7642,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581823</v>
+        <v>581874</v>
       </c>
       <c r="R71" t="n">
-        <v>6958452</v>
+        <v>6958490</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7663,7 +7682,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7690,32 +7709,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127626326</v>
+        <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7725,10 +7744,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581814</v>
+        <v>581833</v>
       </c>
       <c r="R72" t="n">
-        <v>6958498</v>
+        <v>6958501</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7761,11 +7780,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7792,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127622082</v>
+        <v>127626288</v>
       </c>
       <c r="B73" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7803,43 +7817,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581489</v>
+        <v>581468</v>
       </c>
       <c r="R73" t="n">
-        <v>6958404</v>
+        <v>6958479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7898,32 +7903,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626346</v>
+        <v>127626341</v>
       </c>
       <c r="B74" t="n">
-        <v>97325</v>
+        <v>91626</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581833</v>
+        <v>581425</v>
       </c>
       <c r="R74" t="n">
-        <v>6958501</v>
+        <v>6958396</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7995,48 +8000,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127627415</v>
+        <v>127626311</v>
       </c>
       <c r="B75" t="n">
-        <v>91531</v>
+        <v>57661</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581429</v>
+        <v>581684</v>
       </c>
       <c r="R75" t="n">
-        <v>6958404</v>
+        <v>6958471</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8071,13 +8073,17 @@
           <t>2025-08-16</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8096,7 +8102,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626307</v>
+        <v>127626304</v>
       </c>
       <c r="B76" t="n">
         <v>57661</v>
@@ -8131,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581874</v>
+        <v>581961</v>
       </c>
       <c r="R76" t="n">
-        <v>6958490</v>
+        <v>6958482</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8171,7 +8177,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8198,10 +8204,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127626288</v>
+        <v>127626317</v>
       </c>
       <c r="B77" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8209,34 +8215,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>581468</v>
+        <v>581500</v>
       </c>
       <c r="R77" t="n">
-        <v>6958479</v>
+        <v>6958522</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8269,6 +8283,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Misstänkt äldre bohål i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8295,10 +8314,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127626341</v>
+        <v>127620834</v>
       </c>
       <c r="B78" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8306,34 +8325,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>581425</v>
+        <v>581829</v>
       </c>
       <c r="R78" t="n">
-        <v>6958396</v>
+        <v>6958465</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8366,6 +8393,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Död gran med tre bohål som misstänks tillhöra tretåig hackspett. Två på ena sidan och ett på andra sidan.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8392,45 +8424,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127626311</v>
+        <v>127622592</v>
       </c>
       <c r="B79" t="n">
-        <v>57661</v>
+        <v>91688</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>581684</v>
+        <v>581432</v>
       </c>
       <c r="R79" t="n">
-        <v>6958471</v>
+        <v>6958399</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8463,11 +8495,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8494,32 +8521,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127626304</v>
+        <v>127626337</v>
       </c>
       <c r="B80" t="n">
-        <v>57661</v>
+        <v>91784</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8529,10 +8556,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>581961</v>
+        <v>581550</v>
       </c>
       <c r="R80" t="n">
-        <v>6958482</v>
+        <v>6958488</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8565,11 +8592,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8596,53 +8618,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127626317</v>
+        <v>127626361</v>
       </c>
       <c r="B81" t="n">
-        <v>57661</v>
+        <v>92000</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>581500</v>
+        <v>581464</v>
       </c>
       <c r="R81" t="n">
-        <v>6958522</v>
+        <v>6958401</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8675,11 +8689,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Misstänkt äldre bohål i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8706,42 +8715,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127620834</v>
+        <v>127627415</v>
       </c>
       <c r="B82" t="n">
-        <v>57661</v>
+        <v>91531</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8749,10 +8753,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581829</v>
+        <v>581429</v>
       </c>
       <c r="R82" t="n">
-        <v>6958465</v>
+        <v>6958404</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8787,17 +8791,13 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Död gran med tre bohål som misstänks tillhöra tretåig hackspett. Två på ena sidan och ett på andra sidan.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626355</v>
+        <v>127626320</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581582</v>
+        <v>581658</v>
       </c>
       <c r="R11" t="n">
-        <v>6958488</v>
+        <v>6958452</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626320</v>
+        <v>127626355</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581658</v>
+        <v>581582</v>
       </c>
       <c r="R12" t="n">
-        <v>6958452</v>
+        <v>6958488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626289</v>
+        <v>127626323</v>
       </c>
       <c r="B15" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581425</v>
+        <v>581803</v>
       </c>
       <c r="R15" t="n">
-        <v>6958401</v>
+        <v>6958429</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R16" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626323</v>
+        <v>127626348</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581803</v>
+        <v>582065</v>
       </c>
       <c r="R17" t="n">
-        <v>6958429</v>
+        <v>6958321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626336</v>
+        <v>127626285</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582065</v>
+        <v>581551</v>
       </c>
       <c r="R18" t="n">
-        <v>6958323</v>
+        <v>6958485</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626321</v>
+        <v>127626336</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581718</v>
+        <v>582065</v>
       </c>
       <c r="R19" t="n">
-        <v>6958467</v>
+        <v>6958323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626285</v>
+        <v>127626321</v>
       </c>
       <c r="B20" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581551</v>
+        <v>581718</v>
       </c>
       <c r="R20" t="n">
-        <v>6958485</v>
+        <v>6958467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2592,6 +2587,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3516,7 +3516,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626302</v>
+        <v>127626324</v>
       </c>
       <c r="B30" t="n">
         <v>57661</v>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582050</v>
+        <v>581807</v>
       </c>
       <c r="R30" t="n">
-        <v>6958390</v>
+        <v>6958490</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,7 +3618,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626305</v>
+        <v>127626295</v>
       </c>
       <c r="B31" t="n">
         <v>57661</v>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581928</v>
+        <v>581885</v>
       </c>
       <c r="R31" t="n">
-        <v>6958485</v>
+        <v>6958529</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3720,10 +3720,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626318</v>
+        <v>127626340</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,21 +3731,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581380</v>
+        <v>581474</v>
       </c>
       <c r="R32" t="n">
-        <v>6958472</v>
+        <v>6958474</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,11 +3791,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626324</v>
+        <v>127626302</v>
       </c>
       <c r="B33" t="n">
         <v>57661</v>
@@ -3857,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581807</v>
+        <v>582050</v>
       </c>
       <c r="R33" t="n">
-        <v>6958490</v>
+        <v>6958390</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3924,7 +3919,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626295</v>
+        <v>127626305</v>
       </c>
       <c r="B34" t="n">
         <v>57661</v>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581885</v>
+        <v>581928</v>
       </c>
       <c r="R34" t="n">
-        <v>6958529</v>
+        <v>6958485</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4026,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626340</v>
+        <v>127626318</v>
       </c>
       <c r="B35" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4037,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4061,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581474</v>
+        <v>581380</v>
       </c>
       <c r="R35" t="n">
-        <v>6958474</v>
+        <v>6958472</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,6 +4092,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127626300</v>
+        <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582063</v>
+        <v>581696</v>
       </c>
       <c r="R36" t="n">
-        <v>6958321</v>
+        <v>6958457</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,10 +4220,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626354</v>
+        <v>127626325</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4236,21 +4231,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4260,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582103</v>
+        <v>581819</v>
       </c>
       <c r="R37" t="n">
-        <v>6958332</v>
+        <v>6958488</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,6 +4291,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4322,32 +4322,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626347</v>
+        <v>127626299</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582104</v>
+        <v>582073</v>
       </c>
       <c r="R38" t="n">
-        <v>6958386</v>
+        <v>6958325</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,6 +4393,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4419,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626292</v>
+        <v>127626300</v>
       </c>
       <c r="B39" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4435,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4459,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581696</v>
+        <v>582063</v>
       </c>
       <c r="R39" t="n">
-        <v>6958457</v>
+        <v>6958321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4490,6 +4495,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,10 +4526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626325</v>
+        <v>127626354</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4537,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4561,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581819</v>
+        <v>582103</v>
       </c>
       <c r="R40" t="n">
-        <v>6958488</v>
+        <v>6958332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4597,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,32 +4623,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626299</v>
+        <v>127626347</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4658,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582073</v>
+        <v>582104</v>
       </c>
       <c r="R41" t="n">
-        <v>6958325</v>
+        <v>6958386</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,11 +4694,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5011,7 +5011,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626316</v>
+        <v>127626297</v>
       </c>
       <c r="B45" t="n">
         <v>57661</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581480</v>
+        <v>582085</v>
       </c>
       <c r="R45" t="n">
-        <v>6958548</v>
+        <v>6958383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626297</v>
+        <v>127626327</v>
       </c>
       <c r="B46" t="n">
         <v>57661</v>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582085</v>
+        <v>581824</v>
       </c>
       <c r="R46" t="n">
-        <v>6958383</v>
+        <v>6958505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5215,7 +5215,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626327</v>
+        <v>127626316</v>
       </c>
       <c r="B47" t="n">
         <v>57661</v>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581824</v>
+        <v>581480</v>
       </c>
       <c r="R47" t="n">
-        <v>6958505</v>
+        <v>6958548</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B48" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R48" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B49" t="n">
-        <v>91348</v>
+        <v>91295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R49" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626282</v>
+        <v>127626296</v>
       </c>
       <c r="B50" t="n">
-        <v>91295</v>
+        <v>57661</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581658</v>
+        <v>581882</v>
       </c>
       <c r="R50" t="n">
-        <v>6958442</v>
+        <v>6958519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,6 +5582,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626296</v>
+        <v>127626345</v>
       </c>
       <c r="B51" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5619,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581882</v>
+        <v>581775</v>
       </c>
       <c r="R51" t="n">
-        <v>6958519</v>
+        <v>6958475</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5684,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B66" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R66" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,6 +7169,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7195,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R67" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,11 +7271,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R68" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7399,7 +7399,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127622082</v>
+        <v>127626326</v>
       </c>
       <c r="B69" t="n">
         <v>57661</v>
@@ -7427,26 +7427,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581489</v>
+        <v>581814</v>
       </c>
       <c r="R69" t="n">
-        <v>6958404</v>
+        <v>6958498</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7479,6 +7470,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7505,7 +7501,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127626326</v>
+        <v>127622082</v>
       </c>
       <c r="B70" t="n">
         <v>57661</v>
@@ -7533,17 +7529,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581814</v>
+        <v>581489</v>
       </c>
       <c r="R70" t="n">
-        <v>6958498</v>
+        <v>6958404</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7576,11 +7581,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127626307</v>
+        <v>127626346</v>
       </c>
       <c r="B71" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581874</v>
+        <v>581833</v>
       </c>
       <c r="R71" t="n">
-        <v>6958490</v>
+        <v>6958501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7678,11 +7678,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7709,32 +7704,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127626346</v>
+        <v>127626307</v>
       </c>
       <c r="B72" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7744,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581833</v>
+        <v>581874</v>
       </c>
       <c r="R72" t="n">
-        <v>6958501</v>
+        <v>6958490</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,6 +7775,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,7 +1437,7 @@
         <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R10" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626320</v>
+        <v>127626344</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581658</v>
+        <v>581534</v>
       </c>
       <c r="R11" t="n">
-        <v>6958452</v>
+        <v>6958399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626355</v>
+        <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581582</v>
+        <v>581658</v>
       </c>
       <c r="R12" t="n">
-        <v>6958488</v>
+        <v>6958452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626323</v>
+        <v>127626348</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581803</v>
+        <v>582065</v>
       </c>
       <c r="R15" t="n">
-        <v>6958429</v>
+        <v>6958321</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2097,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626289</v>
+        <v>127626323</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581425</v>
+        <v>581803</v>
       </c>
       <c r="R16" t="n">
-        <v>6958401</v>
+        <v>6958429</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R17" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626322</v>
+        <v>127626356</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581761</v>
+        <v>581795</v>
       </c>
       <c r="R21" t="n">
-        <v>6958462</v>
+        <v>6958432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626356</v>
+        <v>127626322</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,21 +2726,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581795</v>
+        <v>581761</v>
       </c>
       <c r="R22" t="n">
-        <v>6958432</v>
+        <v>6958462</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2791,6 +2786,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626283</v>
+        <v>127626291</v>
       </c>
       <c r="B24" t="n">
         <v>91330</v>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582010</v>
+        <v>581538</v>
       </c>
       <c r="R24" t="n">
-        <v>6958445</v>
+        <v>6958404</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626291</v>
+        <v>127626283</v>
       </c>
       <c r="B26" t="n">
         <v>91330</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581538</v>
+        <v>582010</v>
       </c>
       <c r="R26" t="n">
-        <v>6958404</v>
+        <v>6958445</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626324</v>
+        <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581807</v>
+        <v>581474</v>
       </c>
       <c r="R30" t="n">
-        <v>6958490</v>
+        <v>6958474</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3587,11 +3587,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,7 +3613,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626295</v>
+        <v>127626302</v>
       </c>
       <c r="B31" t="n">
         <v>57661</v>
@@ -3653,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581885</v>
+        <v>582050</v>
       </c>
       <c r="R31" t="n">
-        <v>6958529</v>
+        <v>6958390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,7 +3688,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3720,10 +3715,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626340</v>
+        <v>127626305</v>
       </c>
       <c r="B32" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3731,21 +3726,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581474</v>
+        <v>581928</v>
       </c>
       <c r="R32" t="n">
-        <v>6958474</v>
+        <v>6958485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,6 +3786,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626302</v>
+        <v>127626318</v>
       </c>
       <c r="B33" t="n">
         <v>57661</v>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582050</v>
+        <v>581380</v>
       </c>
       <c r="R33" t="n">
-        <v>6958390</v>
+        <v>6958472</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,7 +3919,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626305</v>
+        <v>127626324</v>
       </c>
       <c r="B34" t="n">
         <v>57661</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581928</v>
+        <v>581807</v>
       </c>
       <c r="R34" t="n">
-        <v>6958485</v>
+        <v>6958490</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,7 +4021,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626318</v>
+        <v>127626295</v>
       </c>
       <c r="B35" t="n">
         <v>57661</v>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581380</v>
+        <v>581885</v>
       </c>
       <c r="R35" t="n">
-        <v>6958472</v>
+        <v>6958529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626325</v>
+        <v>127626354</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581819</v>
+        <v>582103</v>
       </c>
       <c r="R37" t="n">
-        <v>6958488</v>
+        <v>6958332</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,11 +4291,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4322,32 +4317,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626299</v>
+        <v>127626347</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4357,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582073</v>
+        <v>582104</v>
       </c>
       <c r="R38" t="n">
-        <v>6958325</v>
+        <v>6958386</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,11 +4388,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4424,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626300</v>
+        <v>127626325</v>
       </c>
       <c r="B39" t="n">
         <v>57661</v>
@@ -4459,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582063</v>
+        <v>581819</v>
       </c>
       <c r="R39" t="n">
-        <v>6958321</v>
+        <v>6958488</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626354</v>
+        <v>127626299</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4537,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4561,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582103</v>
+        <v>582073</v>
       </c>
       <c r="R40" t="n">
-        <v>6958332</v>
+        <v>6958325</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4597,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4623,32 +4618,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626347</v>
+        <v>127626300</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4658,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582104</v>
+        <v>582063</v>
       </c>
       <c r="R41" t="n">
-        <v>6958386</v>
+        <v>6958321</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4694,6 +4689,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626342</v>
+        <v>127626350</v>
       </c>
       <c r="B42" t="n">
-        <v>91626</v>
+        <v>91348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581440</v>
+        <v>581948</v>
       </c>
       <c r="R42" t="n">
-        <v>6958403</v>
+        <v>6958486</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626284</v>
+        <v>127626342</v>
       </c>
       <c r="B43" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581922</v>
+        <v>581440</v>
       </c>
       <c r="R43" t="n">
-        <v>6958467</v>
+        <v>6958403</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626350</v>
+        <v>127626284</v>
       </c>
       <c r="B44" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581948</v>
+        <v>581922</v>
       </c>
       <c r="R44" t="n">
-        <v>6958486</v>
+        <v>6958467</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626351</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>91348</v>
+        <v>91626</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581501</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958530</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626282</v>
+        <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91295</v>
+        <v>91348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581658</v>
+        <v>581501</v>
       </c>
       <c r="R49" t="n">
-        <v>6958442</v>
+        <v>6958530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626296</v>
+        <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>57661</v>
+        <v>91295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581882</v>
+        <v>581658</v>
       </c>
       <c r="R50" t="n">
-        <v>6958519</v>
+        <v>6958442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,11 +5582,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,10 +5608,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626345</v>
+        <v>127626296</v>
       </c>
       <c r="B51" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5619,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581775</v>
+        <v>581882</v>
       </c>
       <c r="R51" t="n">
-        <v>6958475</v>
+        <v>6958519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5684,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626339</v>
+        <v>127626329</v>
       </c>
       <c r="B52" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581484</v>
+        <v>581831</v>
       </c>
       <c r="R52" t="n">
-        <v>6958540</v>
+        <v>6958455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,6 +5781,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5807,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626290</v>
+        <v>127626303</v>
       </c>
       <c r="B53" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581438</v>
+        <v>582006</v>
       </c>
       <c r="R53" t="n">
-        <v>6958399</v>
+        <v>6958447</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5883,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5904,10 +5914,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127620475</v>
+        <v>127626352</v>
       </c>
       <c r="B54" t="n">
-        <v>91330</v>
+        <v>91348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,34 +5925,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581829</v>
+        <v>581490</v>
       </c>
       <c r="R54" t="n">
-        <v>6958465</v>
+        <v>6958524</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626352</v>
+        <v>127626290</v>
       </c>
       <c r="B55" t="n">
-        <v>91348</v>
+        <v>91330</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6022,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6046,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581490</v>
+        <v>581438</v>
       </c>
       <c r="R55" t="n">
-        <v>6958524</v>
+        <v>6958399</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6098,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626303</v>
+        <v>127620475</v>
       </c>
       <c r="B56" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6109,34 +6119,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582006</v>
+        <v>581829</v>
       </c>
       <c r="R56" t="n">
-        <v>6958447</v>
+        <v>6958465</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6169,11 +6179,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6200,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626329</v>
+        <v>127626339</v>
       </c>
       <c r="B57" t="n">
-        <v>57661</v>
+        <v>91626</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6216,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6240,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581831</v>
+        <v>581484</v>
       </c>
       <c r="R57" t="n">
-        <v>6958455</v>
+        <v>6958540</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,11 +6276,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B59" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R59" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B60" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R60" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B61" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R61" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,6 +6669,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6695,10 +6700,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6706,21 +6711,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6730,10 +6735,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R62" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,11 +6771,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>98365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R63" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6899,7 +6894,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626301</v>
+        <v>127626298</v>
       </c>
       <c r="B64" t="n">
         <v>57661</v>
@@ -6934,10 +6929,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582037</v>
+        <v>582124</v>
       </c>
       <c r="R64" t="n">
-        <v>6958341</v>
+        <v>6958327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7001,32 +6996,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626358</v>
+        <v>127626301</v>
       </c>
       <c r="B65" t="n">
-        <v>98364</v>
+        <v>57661</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7031,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582087</v>
+        <v>582037</v>
       </c>
       <c r="R65" t="n">
-        <v>6958421</v>
+        <v>6958341</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,6 +7067,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626328</v>
+        <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581823</v>
+        <v>581497</v>
       </c>
       <c r="R66" t="n">
-        <v>6958452</v>
+        <v>6958542</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,11 +7169,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626286</v>
+        <v>127626357</v>
       </c>
       <c r="B67" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581497</v>
+        <v>581828</v>
       </c>
       <c r="R67" t="n">
-        <v>6958542</v>
+        <v>6958421</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7266,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626357</v>
+        <v>127626328</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581828</v>
+        <v>581823</v>
       </c>
       <c r="R68" t="n">
-        <v>6958421</v>
+        <v>6958452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7399,7 +7399,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626326</v>
+        <v>127622082</v>
       </c>
       <c r="B69" t="n">
         <v>57661</v>
@@ -7427,17 +7427,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581814</v>
+        <v>581489</v>
       </c>
       <c r="R69" t="n">
-        <v>6958498</v>
+        <v>6958404</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,11 +7479,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7501,7 +7505,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127622082</v>
+        <v>127626326</v>
       </c>
       <c r="B70" t="n">
         <v>57661</v>
@@ -7529,26 +7533,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581489</v>
+        <v>581814</v>
       </c>
       <c r="R70" t="n">
-        <v>6958404</v>
+        <v>6958498</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7581,6 +7576,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127626346</v>
+        <v>127626307</v>
       </c>
       <c r="B71" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581833</v>
+        <v>581874</v>
       </c>
       <c r="R71" t="n">
-        <v>6958501</v>
+        <v>6958490</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7678,6 +7678,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7704,32 +7709,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127626307</v>
+        <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7739,10 +7744,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581874</v>
+        <v>581833</v>
       </c>
       <c r="R72" t="n">
-        <v>6958490</v>
+        <v>6958501</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7775,11 +7780,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8314,53 +8314,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127620834</v>
+        <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>57661</v>
+        <v>91688</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>581829</v>
+        <v>581432</v>
       </c>
       <c r="R78" t="n">
-        <v>6958465</v>
+        <v>6958399</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8393,11 +8385,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Död gran med tre bohål som misstänks tillhöra tretåig hackspett. Två på ena sidan och ett på andra sidan.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8424,10 +8411,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127622592</v>
+        <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91688</v>
+        <v>91784</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8435,34 +8422,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2062</v>
+        <v>1209</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>581432</v>
+        <v>581550</v>
       </c>
       <c r="R79" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8521,10 +8508,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127626337</v>
+        <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>91784</v>
+        <v>92000</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8532,21 +8519,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8556,10 +8543,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>581550</v>
+        <v>581464</v>
       </c>
       <c r="R80" t="n">
-        <v>6958488</v>
+        <v>6958401</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8618,10 +8605,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127626361</v>
+        <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>92000</v>
+        <v>91531</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8629,34 +8616,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>898</v>
+        <v>48</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>581464</v>
+        <v>581429</v>
       </c>
       <c r="R81" t="n">
-        <v>6958401</v>
+        <v>6958404</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8697,6 +8687,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8715,48 +8706,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127627415</v>
+        <v>127700444</v>
       </c>
       <c r="B82" t="n">
-        <v>91531</v>
+        <v>57821</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581429</v>
+        <v>581826</v>
       </c>
       <c r="R82" t="n">
-        <v>6958404</v>
+        <v>6958437</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8783,12 +8780,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8797,7 +8794,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8813,6 +8809,5229 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127708940</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>581551</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6958433</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127708919</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>581468</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6958461</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127708929</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>581702</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6958462</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127702065</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91740</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>581516</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6958469</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127708953</v>
+      </c>
+      <c r="B87" t="n">
+        <v>88733</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>510</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>581497</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6958369</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127703408</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>581481</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6958339</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127708911</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>581597</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6958391</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127708910</v>
+      </c>
+      <c r="B90" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>581604</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6958417</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127708921</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>581549</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6958437</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127708935</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>581452</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6958446</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127708951</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>581943</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6958445</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7 ex</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127702448</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>658</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>581480</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6958518</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127708944</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>658</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>581469</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6958479</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127700375</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>581797</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6958452</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127708917</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>581459</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6958547</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127708945</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>658</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>581512</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6958472</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127701709</v>
+      </c>
+      <c r="B99" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>581590</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6958438</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127708916</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>581451</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6958466</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127708915</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>581387</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6958453</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127708920</v>
+      </c>
+      <c r="B102" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>581517</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6958471</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127708924</v>
+      </c>
+      <c r="B103" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>581607</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6958406</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>127702553</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91531</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>48</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>581423</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6958511</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127708942</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>658</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>581396</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6958454</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127708946</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>658</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>581559</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6958443</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127700450</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>581789</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6958477</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127708913</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>581501</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6958372</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127708947</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>658</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>581574</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6958443</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127708912</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>581558</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6958357</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127708937</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>581457</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6958514</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127708918</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>581472</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6958523</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127708932</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>581817</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6958438</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127702456</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>581480</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6958518</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127708926</v>
+      </c>
+      <c r="B115" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>581513</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6958336</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127703591</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91688</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>581485</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6958325</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127708941</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>658</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>581486</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6958333</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127703413</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>581481</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6958339</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127708922</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>581560</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6958445</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127708934</v>
+      </c>
+      <c r="B120" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>581654</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6958457</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127708930</v>
+      </c>
+      <c r="B121" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>581820</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6958448</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127703745</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>581549</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6958317</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127708948</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>658</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>581726</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6958466</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>127708923</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>581565</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6958441</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127708950</v>
+      </c>
+      <c r="B125" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>581502</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6958332</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>127708909</v>
+      </c>
+      <c r="B126" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>581606</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6958438</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>127701827</v>
+      </c>
+      <c r="B127" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>581564</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6958463</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127708949</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>581598</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6958396</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127708959</v>
+      </c>
+      <c r="B129" t="n">
+        <v>92000</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>898</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>581595</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6958389</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>127708939</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>581490</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6958459</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>127708927</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>581489</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6958369</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127702695</v>
+      </c>
+      <c r="B132" t="n">
+        <v>80121</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>581442</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6958493</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>127708914</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>581433</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6958423</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>127708943</v>
+      </c>
+      <c r="B134" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>658</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>581472</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6958521</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>127708952</v>
+      </c>
+      <c r="B135" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Dåvamyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>581959</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6958445</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626338</v>
+        <v>127626319</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581544</v>
+        <v>581409</v>
       </c>
       <c r="R7" t="n">
-        <v>6958500</v>
+        <v>6958406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1306,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>98365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R8" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1408,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626360</v>
+        <v>127626338</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>91626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581836</v>
+        <v>581544</v>
       </c>
       <c r="R9" t="n">
-        <v>6958416</v>
+        <v>6958500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R61" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,11 +6669,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6700,10 +6695,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6711,21 +6706,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,10 +6730,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R62" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8812,10 +8812,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708940</v>
+        <v>127703408</v>
       </c>
       <c r="B83" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581551</v>
+        <v>581481</v>
       </c>
       <c r="R83" t="n">
-        <v>6958433</v>
+        <v>6958339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8883,11 +8883,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8914,10 +8909,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708919</v>
+        <v>127708940</v>
       </c>
       <c r="B84" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8925,21 +8920,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8949,10 +8944,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581468</v>
+        <v>581551</v>
       </c>
       <c r="R84" t="n">
-        <v>6958461</v>
+        <v>6958433</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8985,6 +8980,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9011,32 +9011,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127708929</v>
+        <v>127708919</v>
       </c>
       <c r="B85" t="n">
-        <v>92027</v>
+        <v>91330</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581702</v>
+        <v>581468</v>
       </c>
       <c r="R85" t="n">
-        <v>6958462</v>
+        <v>6958461</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9108,10 +9108,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127702065</v>
+        <v>127708929</v>
       </c>
       <c r="B86" t="n">
-        <v>91740</v>
+        <v>92027</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9119,21 +9119,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9143,10 +9143,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581516</v>
+        <v>581702</v>
       </c>
       <c r="R86" t="n">
-        <v>6958469</v>
+        <v>6958462</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9205,32 +9205,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708953</v>
+        <v>127702065</v>
       </c>
       <c r="B87" t="n">
-        <v>88733</v>
+        <v>91740</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>510</v>
+        <v>4217</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581497</v>
+        <v>581516</v>
       </c>
       <c r="R87" t="n">
-        <v>6958369</v>
+        <v>6958469</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127703408</v>
+        <v>127708953</v>
       </c>
       <c r="B88" t="n">
-        <v>91330</v>
+        <v>88733</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581481</v>
+        <v>581497</v>
       </c>
       <c r="R88" t="n">
-        <v>6958339</v>
+        <v>6958369</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12449,7 +12449,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127708934</v>
+        <v>127708930</v>
       </c>
       <c r="B120" t="n">
         <v>57661</v>
@@ -12478,20 +12478,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>581654</v>
+        <v>581820</v>
       </c>
       <c r="R120" t="n">
-        <v>6958457</v>
+        <v>6958448</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12528,7 +12524,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>En födosökande individ</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12555,10 +12551,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127708930</v>
+        <v>127703745</v>
       </c>
       <c r="B121" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12566,21 +12562,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12590,10 +12586,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>581820</v>
+        <v>581549</v>
       </c>
       <c r="R121" t="n">
-        <v>6958448</v>
+        <v>6958317</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12630,7 +12626,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12657,10 +12653,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127703745</v>
+        <v>127708948</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12668,21 +12664,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12692,10 +12688,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>581549</v>
+        <v>581726</v>
       </c>
       <c r="R122" t="n">
-        <v>6958317</v>
+        <v>6958466</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12728,11 +12724,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12759,10 +12750,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127708948</v>
+        <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91626</v>
+        <v>91330</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12770,21 +12761,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12794,10 +12785,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>581726</v>
+        <v>581565</v>
       </c>
       <c r="R123" t="n">
-        <v>6958466</v>
+        <v>6958441</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12856,32 +12847,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127708923</v>
+        <v>127708950</v>
       </c>
       <c r="B124" t="n">
-        <v>91330</v>
+        <v>98365</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12891,10 +12882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>581565</v>
+        <v>581502</v>
       </c>
       <c r="R124" t="n">
-        <v>6958441</v>
+        <v>6958332</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12953,32 +12944,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127708950</v>
+        <v>127708909</v>
       </c>
       <c r="B125" t="n">
-        <v>98365</v>
+        <v>91330</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12988,10 +12979,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>581502</v>
+        <v>581606</v>
       </c>
       <c r="R125" t="n">
-        <v>6958332</v>
+        <v>6958438</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13050,10 +13041,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708909</v>
+        <v>127701827</v>
       </c>
       <c r="B126" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13061,34 +13052,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581606</v>
+        <v>581564</v>
       </c>
       <c r="R126" t="n">
-        <v>6958438</v>
+        <v>6958463</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13121,6 +13117,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13147,50 +13148,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127701827</v>
+        <v>127708949</v>
       </c>
       <c r="B127" t="n">
-        <v>57661</v>
+        <v>98365</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581564</v>
+        <v>581598</v>
       </c>
       <c r="R127" t="n">
-        <v>6958463</v>
+        <v>6958396</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13223,11 +13219,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13254,32 +13245,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708949</v>
+        <v>127708959</v>
       </c>
       <c r="B128" t="n">
-        <v>98365</v>
+        <v>92000</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>898</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13289,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581598</v>
+        <v>581595</v>
       </c>
       <c r="R128" t="n">
-        <v>6958396</v>
+        <v>6958389</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13351,32 +13342,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708959</v>
+        <v>127708939</v>
       </c>
       <c r="B129" t="n">
-        <v>92000</v>
+        <v>57661</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13386,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581595</v>
+        <v>581490</v>
       </c>
       <c r="R129" t="n">
-        <v>6958389</v>
+        <v>6958459</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13422,6 +13413,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13448,32 +13444,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708939</v>
+        <v>127708927</v>
       </c>
       <c r="B130" t="n">
-        <v>57661</v>
+        <v>92027</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13483,10 +13479,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581490</v>
+        <v>581489</v>
       </c>
       <c r="R130" t="n">
-        <v>6958459</v>
+        <v>6958369</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13519,11 +13515,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13550,32 +13541,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708927</v>
+        <v>127702695</v>
       </c>
       <c r="B131" t="n">
-        <v>92027</v>
+        <v>80121</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13585,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581489</v>
+        <v>581442</v>
       </c>
       <c r="R131" t="n">
-        <v>6958369</v>
+        <v>6958493</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13647,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127702695</v>
+        <v>127708914</v>
       </c>
       <c r="B132" t="n">
-        <v>80121</v>
+        <v>91330</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13658,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13682,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581442</v>
+        <v>581433</v>
       </c>
       <c r="R132" t="n">
-        <v>6958493</v>
+        <v>6958423</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13744,10 +13735,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B133" t="n">
-        <v>91330</v>
+        <v>91626</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13755,21 +13746,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13779,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R133" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13841,32 +13832,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127708943</v>
+        <v>127708952</v>
       </c>
       <c r="B134" t="n">
-        <v>91626</v>
+        <v>92620</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13876,10 +13867,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>581472</v>
+        <v>581959</v>
       </c>
       <c r="R134" t="n">
-        <v>6958521</v>
+        <v>6958445</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13938,45 +13929,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127708952</v>
+        <v>127708934</v>
       </c>
       <c r="B135" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>581959</v>
+        <v>581654</v>
       </c>
       <c r="R135" t="n">
-        <v>6958445</v>
+        <v>6958457</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14009,6 +14004,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD135" t="b">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626319</v>
+        <v>127626338</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>91628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581409</v>
+        <v>581544</v>
       </c>
       <c r="R7" t="n">
-        <v>6958406</v>
+        <v>6958500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1306,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626360</v>
+        <v>127626319</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581836</v>
+        <v>581409</v>
       </c>
       <c r="R8" t="n">
-        <v>6958416</v>
+        <v>6958406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626338</v>
+        <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>91626</v>
+        <v>98367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581544</v>
+        <v>581836</v>
       </c>
       <c r="R9" t="n">
-        <v>6958500</v>
+        <v>6958416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>91628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R10" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B11" t="n">
-        <v>91626</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R11" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127626332</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>127626348</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626323</v>
+        <v>127626289</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581803</v>
+        <v>581425</v>
       </c>
       <c r="R16" t="n">
-        <v>6958429</v>
+        <v>6958401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626289</v>
+        <v>127626323</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581425</v>
+        <v>581803</v>
       </c>
       <c r="R17" t="n">
-        <v>6958401</v>
+        <v>6958429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626285</v>
+        <v>127626336</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>80152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581551</v>
+        <v>582065</v>
       </c>
       <c r="R18" t="n">
-        <v>6958485</v>
+        <v>6958323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626336</v>
+        <v>127626285</v>
       </c>
       <c r="B19" t="n">
-        <v>80150</v>
+        <v>91332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582065</v>
+        <v>581551</v>
       </c>
       <c r="R19" t="n">
-        <v>6958323</v>
+        <v>6958485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,7 +2519,7 @@
         <v>127626321</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626356</v>
+        <v>127626322</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581795</v>
+        <v>581761</v>
       </c>
       <c r="R21" t="n">
-        <v>6958432</v>
+        <v>6958462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626322</v>
+        <v>127626306</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581761</v>
+        <v>581878</v>
       </c>
       <c r="R22" t="n">
-        <v>6958462</v>
+        <v>6958484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626306</v>
+        <v>127626356</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581878</v>
+        <v>581795</v>
       </c>
       <c r="R23" t="n">
-        <v>6958484</v>
+        <v>6958432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,11 +2893,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626291</v>
+        <v>127626309</v>
       </c>
       <c r="B24" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581538</v>
+        <v>581870</v>
       </c>
       <c r="R24" t="n">
-        <v>6958404</v>
+        <v>6958478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,6 +2990,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3016,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,21 +3032,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R25" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,6 +3092,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626283</v>
+        <v>127626312</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,21 +3134,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3148,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582010</v>
+        <v>581642</v>
       </c>
       <c r="R26" t="n">
-        <v>6958445</v>
+        <v>6958463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,6 +3194,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3210,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,21 +3236,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3245,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R27" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,11 +3296,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3312,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R28" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,11 +3393,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,10 +3419,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,21 +3430,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R29" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,11 +3490,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3519,7 @@
         <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>127626302</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127626305</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>127626318</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>127626324</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127626295</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>127626354</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>127626347</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>127626325</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>127626299</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>127626300</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626350</v>
+        <v>127626316</v>
       </c>
       <c r="B42" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581948</v>
+        <v>581480</v>
       </c>
       <c r="R42" t="n">
-        <v>6958486</v>
+        <v>6958548</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626342</v>
+        <v>127626297</v>
       </c>
       <c r="B43" t="n">
-        <v>91626</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581440</v>
+        <v>582085</v>
       </c>
       <c r="R43" t="n">
-        <v>6958403</v>
+        <v>6958383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,6 +4893,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4914,10 +4924,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626284</v>
+        <v>127626327</v>
       </c>
       <c r="B44" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4935,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4959,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581922</v>
+        <v>581824</v>
       </c>
       <c r="R44" t="n">
-        <v>6958467</v>
+        <v>6958505</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4995,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,10 +5026,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626297</v>
+        <v>127626342</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>91628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5037,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5061,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582085</v>
+        <v>581440</v>
       </c>
       <c r="R45" t="n">
-        <v>6958383</v>
+        <v>6958403</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,11 +5097,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5113,10 +5123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626327</v>
+        <v>127626284</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5124,21 +5134,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581824</v>
+        <v>581922</v>
       </c>
       <c r="R46" t="n">
-        <v>6958505</v>
+        <v>6958467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,11 +5194,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5215,10 +5220,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626316</v>
+        <v>127626350</v>
       </c>
       <c r="B47" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5226,21 +5231,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5250,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581480</v>
+        <v>581948</v>
       </c>
       <c r="R47" t="n">
-        <v>6958548</v>
+        <v>6958486</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,11 +5291,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5320,7 +5320,7 @@
         <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>127626296</v>
       </c>
       <c r="B51" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626329</v>
+        <v>127626352</v>
       </c>
       <c r="B52" t="n">
-        <v>57661</v>
+        <v>91350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581831</v>
+        <v>581490</v>
       </c>
       <c r="R52" t="n">
-        <v>6958455</v>
+        <v>6958524</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,11 +5781,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626303</v>
+        <v>127626329</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582006</v>
+        <v>581831</v>
       </c>
       <c r="R53" t="n">
-        <v>6958447</v>
+        <v>6958455</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5887,7 +5882,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5914,10 +5909,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626352</v>
+        <v>127626303</v>
       </c>
       <c r="B54" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5925,21 +5920,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5949,10 +5944,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581490</v>
+        <v>582006</v>
       </c>
       <c r="R54" t="n">
-        <v>6958524</v>
+        <v>6958447</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5985,6 +5980,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6011,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626290</v>
+        <v>127626339</v>
       </c>
       <c r="B55" t="n">
-        <v>91330</v>
+        <v>91628</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,21 +6022,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581438</v>
+        <v>581484</v>
       </c>
       <c r="R55" t="n">
-        <v>6958399</v>
+        <v>6958540</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127620475</v>
+        <v>127626290</v>
       </c>
       <c r="B56" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6139,14 +6139,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581829</v>
+        <v>581438</v>
       </c>
       <c r="R56" t="n">
-        <v>6958465</v>
+        <v>6958399</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6205,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626339</v>
+        <v>127620475</v>
       </c>
       <c r="B57" t="n">
-        <v>91626</v>
+        <v>91332</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,34 +6216,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581484</v>
+        <v>581829</v>
       </c>
       <c r="R57" t="n">
-        <v>6958540</v>
+        <v>6958465</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,7 +6305,7 @@
         <v>127626315</v>
       </c>
       <c r="B58" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B59" t="n">
-        <v>91330</v>
+        <v>91628</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R59" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B60" t="n">
-        <v>91626</v>
+        <v>91332</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R60" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
         <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626358</v>
+        <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582087</v>
+        <v>582124</v>
       </c>
       <c r="R63" t="n">
-        <v>6958421</v>
+        <v>6958327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626298</v>
+        <v>127626301</v>
       </c>
       <c r="B64" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6929,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582124</v>
+        <v>582037</v>
       </c>
       <c r="R64" t="n">
-        <v>6958327</v>
+        <v>6958341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6996,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626301</v>
+        <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>57661</v>
+        <v>98367</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7031,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582037</v>
+        <v>582087</v>
       </c>
       <c r="R65" t="n">
-        <v>6958341</v>
+        <v>6958421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7067,11 +7072,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B66" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R66" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,6 +7169,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7195,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R67" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,11 +7271,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R68" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7402,7 +7402,7 @@
         <v>127622082</v>
       </c>
       <c r="B69" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>127626326</v>
       </c>
       <c r="B70" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>127626307</v>
       </c>
       <c r="B71" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>127626288</v>
       </c>
       <c r="B73" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>127626341</v>
       </c>
       <c r="B74" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>127626311</v>
       </c>
       <c r="B75" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>127626304</v>
       </c>
       <c r="B76" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>127626317</v>
       </c>
       <c r="B77" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92000</v>
+        <v>92002</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127700444</v>
+        <v>127708953</v>
       </c>
       <c r="B82" t="n">
-        <v>57821</v>
+        <v>88735</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,43 +8717,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581826</v>
+        <v>581497</v>
       </c>
       <c r="R82" t="n">
-        <v>6958437</v>
+        <v>6958369</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8812,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127703408</v>
+        <v>127708929</v>
       </c>
       <c r="B83" t="n">
-        <v>91330</v>
+        <v>92029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8847,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581481</v>
+        <v>581702</v>
       </c>
       <c r="R83" t="n">
-        <v>6958339</v>
+        <v>6958462</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8909,32 +8900,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708940</v>
+        <v>127702065</v>
       </c>
       <c r="B84" t="n">
-        <v>57661</v>
+        <v>91742</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8944,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581551</v>
+        <v>581516</v>
       </c>
       <c r="R84" t="n">
-        <v>6958433</v>
+        <v>6958469</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8980,11 +8971,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9011,10 +8997,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127708919</v>
+        <v>127703408</v>
       </c>
       <c r="B85" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9046,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581468</v>
+        <v>581481</v>
       </c>
       <c r="R85" t="n">
-        <v>6958461</v>
+        <v>6958339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9108,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708929</v>
+        <v>127708919</v>
       </c>
       <c r="B86" t="n">
-        <v>92027</v>
+        <v>91332</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9143,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581702</v>
+        <v>581468</v>
       </c>
       <c r="R86" t="n">
-        <v>6958462</v>
+        <v>6958461</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9205,32 +9191,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127702065</v>
+        <v>127708940</v>
       </c>
       <c r="B87" t="n">
-        <v>91740</v>
+        <v>57663</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9240,10 +9226,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581516</v>
+        <v>581551</v>
       </c>
       <c r="R87" t="n">
-        <v>6958469</v>
+        <v>6958433</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9276,6 +9262,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9302,10 +9293,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127708953</v>
+        <v>127700444</v>
       </c>
       <c r="B88" t="n">
-        <v>88733</v>
+        <v>57823</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9313,34 +9304,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581497</v>
+        <v>581826</v>
       </c>
       <c r="R88" t="n">
-        <v>6958369</v>
+        <v>6958437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9402,7 +9402,7 @@
         <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>127708921</v>
       </c>
       <c r="B91" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708935</v>
+        <v>127702448</v>
       </c>
       <c r="B92" t="n">
-        <v>57661</v>
+        <v>91628</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581452</v>
+        <v>581480</v>
       </c>
       <c r="R92" t="n">
-        <v>6958446</v>
+        <v>6958518</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,11 +9761,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9795,7 +9790,7 @@
         <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9894,10 +9889,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127702448</v>
+        <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>91626</v>
+        <v>57663</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9905,21 +9900,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581480</v>
+        <v>581452</v>
       </c>
       <c r="R94" t="n">
-        <v>6958518</v>
+        <v>6958446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9965,6 +9960,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9994,7 +9994,7 @@
         <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127700375</v>
+        <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,42 +10099,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581797</v>
+        <v>581459</v>
       </c>
       <c r="R96" t="n">
-        <v>6958452</v>
+        <v>6958547</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10167,11 +10159,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10198,10 +10185,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127708917</v>
+        <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10209,34 +10196,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581459</v>
+        <v>581797</v>
       </c>
       <c r="R97" t="n">
-        <v>6958547</v>
+        <v>6958452</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10269,6 +10264,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10298,7 +10298,7 @@
         <v>127708945</v>
       </c>
       <c r="B98" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127701709</v>
+        <v>127708916</v>
       </c>
       <c r="B99" t="n">
-        <v>92027</v>
+        <v>91332</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581590</v>
+        <v>581451</v>
       </c>
       <c r="R99" t="n">
-        <v>6958438</v>
+        <v>6958466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708916</v>
+        <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>91330</v>
+        <v>92029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581451</v>
+        <v>581590</v>
       </c>
       <c r="R100" t="n">
-        <v>6958466</v>
+        <v>6958438</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127702553</v>
+        <v>127708942</v>
       </c>
       <c r="B104" t="n">
-        <v>91531</v>
+        <v>91628</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581423</v>
+        <v>581396</v>
       </c>
       <c r="R104" t="n">
-        <v>6958511</v>
+        <v>6958454</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708942</v>
+        <v>127708946</v>
       </c>
       <c r="B105" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581396</v>
+        <v>581559</v>
       </c>
       <c r="R105" t="n">
-        <v>6958454</v>
+        <v>6958443</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708946</v>
+        <v>127702553</v>
       </c>
       <c r="B106" t="n">
-        <v>91626</v>
+        <v>91533</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581559</v>
+        <v>581423</v>
       </c>
       <c r="R106" t="n">
-        <v>6958443</v>
+        <v>6958511</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11171,7 +11171,7 @@
         <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>127708947</v>
       </c>
       <c r="B109" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127708912</v>
       </c>
       <c r="B110" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>127708937</v>
       </c>
       <c r="B111" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B112" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R112" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,6 +11734,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11760,10 +11765,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B113" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11771,21 +11776,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11795,10 +11800,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R113" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11831,11 +11836,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127702456</v>
+        <v>127708926</v>
       </c>
       <c r="B114" t="n">
-        <v>91330</v>
+        <v>92029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581480</v>
+        <v>581513</v>
       </c>
       <c r="R114" t="n">
-        <v>6958518</v>
+        <v>6958336</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,32 +11959,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708926</v>
+        <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>92027</v>
+        <v>91628</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581513</v>
+        <v>581486</v>
       </c>
       <c r="R115" t="n">
-        <v>6958336</v>
+        <v>6958333</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127703591</v>
+        <v>127702456</v>
       </c>
       <c r="B116" t="n">
-        <v>91688</v>
+        <v>91332</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581485</v>
+        <v>581480</v>
       </c>
       <c r="R116" t="n">
-        <v>6958325</v>
+        <v>6958518</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127708941</v>
+        <v>127703591</v>
       </c>
       <c r="B117" t="n">
-        <v>91626</v>
+        <v>91690</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581486</v>
+        <v>581485</v>
       </c>
       <c r="R117" t="n">
-        <v>6958333</v>
+        <v>6958325</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>57821</v>
+        <v>91332</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R118" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,10 +12347,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B119" t="n">
-        <v>91330</v>
+        <v>57823</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12363,34 +12358,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R119" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12452,7 +12452,7 @@
         <v>127708930</v>
       </c>
       <c r="B120" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12551,10 +12551,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127703745</v>
+        <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>91628</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12562,21 +12562,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>581549</v>
+        <v>581726</v>
       </c>
       <c r="R121" t="n">
-        <v>6958317</v>
+        <v>6958466</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12622,11 +12622,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12653,10 +12648,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127708948</v>
+        <v>127703745</v>
       </c>
       <c r="B122" t="n">
-        <v>91626</v>
+        <v>79020</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12664,21 +12659,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12688,10 +12683,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>581726</v>
+        <v>581549</v>
       </c>
       <c r="R122" t="n">
-        <v>6958466</v>
+        <v>6958317</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12724,6 +12719,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av garnlav inom området</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12847,32 +12847,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127708950</v>
+        <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>98365</v>
+        <v>91332</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>581502</v>
+        <v>581606</v>
       </c>
       <c r="R124" t="n">
-        <v>6958332</v>
+        <v>6958438</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12944,32 +12944,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127708909</v>
+        <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>91330</v>
+        <v>98367</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>581606</v>
+        <v>581502</v>
       </c>
       <c r="R125" t="n">
-        <v>6958438</v>
+        <v>6958332</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13041,10 +13041,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127701827</v>
+        <v>127708939</v>
       </c>
       <c r="B126" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13070,21 +13070,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581564</v>
+        <v>581490</v>
       </c>
       <c r="R126" t="n">
-        <v>6958463</v>
+        <v>6958459</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13121,7 +13116,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13148,45 +13143,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708949</v>
+        <v>127701827</v>
       </c>
       <c r="B127" t="n">
-        <v>98365</v>
+        <v>57663</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581598</v>
+        <v>581564</v>
       </c>
       <c r="R127" t="n">
-        <v>6958396</v>
+        <v>6958463</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13219,6 +13219,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13245,32 +13250,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708959</v>
+        <v>127708949</v>
       </c>
       <c r="B128" t="n">
-        <v>92000</v>
+        <v>98367</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>898</v>
+        <v>219790</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13285,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581595</v>
+        <v>581598</v>
       </c>
       <c r="R128" t="n">
-        <v>6958389</v>
+        <v>6958396</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,32 +13347,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708939</v>
+        <v>127708959</v>
       </c>
       <c r="B129" t="n">
-        <v>57661</v>
+        <v>92002</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581490</v>
+        <v>581595</v>
       </c>
       <c r="R129" t="n">
-        <v>6958459</v>
+        <v>6958389</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13413,11 +13418,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13447,7 +13447,7 @@
         <v>127708927</v>
       </c>
       <c r="B130" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127702695</v>
+        <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>80121</v>
+        <v>91332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581442</v>
+        <v>581433</v>
       </c>
       <c r="R131" t="n">
-        <v>6958493</v>
+        <v>6958423</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>91330</v>
+        <v>91628</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R132" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,10 +13735,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708943</v>
+        <v>127702695</v>
       </c>
       <c r="B133" t="n">
-        <v>91626</v>
+        <v>80123</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13746,21 +13746,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581472</v>
+        <v>581442</v>
       </c>
       <c r="R133" t="n">
-        <v>6958521</v>
+        <v>6958493</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13835,7 +13835,7 @@
         <v>127708952</v>
       </c>
       <c r="B134" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>127708934</v>
       </c>
       <c r="B135" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R15" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626289</v>
+        <v>127626348</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581425</v>
+        <v>582065</v>
       </c>
       <c r="R16" t="n">
-        <v>6958401</v>
+        <v>6958321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626336</v>
+        <v>127626285</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582065</v>
+        <v>581551</v>
       </c>
       <c r="R18" t="n">
-        <v>6958323</v>
+        <v>6958485</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626285</v>
+        <v>127626336</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>80152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581551</v>
+        <v>582065</v>
       </c>
       <c r="R19" t="n">
-        <v>6958485</v>
+        <v>6958323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626322</v>
+        <v>127626356</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581761</v>
+        <v>581795</v>
       </c>
       <c r="R21" t="n">
-        <v>6958462</v>
+        <v>6958432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626306</v>
+        <v>127626322</v>
       </c>
       <c r="B22" t="n">
         <v>57663</v>
@@ -2755,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581878</v>
+        <v>581761</v>
       </c>
       <c r="R22" t="n">
-        <v>6958484</v>
+        <v>6958462</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626356</v>
+        <v>127626306</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581795</v>
+        <v>581878</v>
       </c>
       <c r="R23" t="n">
-        <v>6958432</v>
+        <v>6958484</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2888,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R24" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,11 +2990,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,21 +3027,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R25" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,21 +3124,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R26" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,11 +3184,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,10 +3210,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626283</v>
+        <v>127626309</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,21 +3221,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3260,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582010</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6958445</v>
+        <v>6958478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,6 +3281,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3322,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B28" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3323,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R28" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,6 +3383,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3419,10 +3414,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B29" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3454,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R29" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3485,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626316</v>
+        <v>127626342</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581480</v>
+        <v>581440</v>
       </c>
       <c r="R42" t="n">
-        <v>6958548</v>
+        <v>6958403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626297</v>
+        <v>127626284</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582085</v>
+        <v>581922</v>
       </c>
       <c r="R43" t="n">
-        <v>6958383</v>
+        <v>6958467</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,11 +4888,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4924,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626327</v>
+        <v>127626350</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4935,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4959,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581824</v>
+        <v>581948</v>
       </c>
       <c r="R44" t="n">
-        <v>6958505</v>
+        <v>6958486</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,11 +4985,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5026,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626342</v>
+        <v>127626297</v>
       </c>
       <c r="B45" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5037,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5061,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581440</v>
+        <v>582085</v>
       </c>
       <c r="R45" t="n">
-        <v>6958403</v>
+        <v>6958383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5097,6 +5082,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5123,10 +5113,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626284</v>
+        <v>127626327</v>
       </c>
       <c r="B46" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,21 +5124,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5158,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581922</v>
+        <v>581824</v>
       </c>
       <c r="R46" t="n">
-        <v>6958467</v>
+        <v>6958505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5194,6 +5184,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5220,10 +5215,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626350</v>
+        <v>127626316</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,21 +5226,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581948</v>
+        <v>581480</v>
       </c>
       <c r="R47" t="n">
-        <v>6958486</v>
+        <v>6958548</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,6 +5286,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626352</v>
+        <v>127626339</v>
       </c>
       <c r="B52" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581490</v>
+        <v>581484</v>
       </c>
       <c r="R52" t="n">
-        <v>6958524</v>
+        <v>6958540</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626329</v>
+        <v>127626290</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581831</v>
+        <v>581438</v>
       </c>
       <c r="R53" t="n">
-        <v>6958455</v>
+        <v>6958399</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,11 +5878,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5909,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626303</v>
+        <v>127620475</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5920,34 +5915,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>582006</v>
+        <v>581829</v>
       </c>
       <c r="R54" t="n">
-        <v>6958447</v>
+        <v>6958465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5980,11 +5975,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6011,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626339</v>
+        <v>127626329</v>
       </c>
       <c r="B55" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6046,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581484</v>
+        <v>581831</v>
       </c>
       <c r="R55" t="n">
-        <v>6958540</v>
+        <v>6958455</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6082,6 +6072,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6108,10 +6103,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626290</v>
+        <v>127626303</v>
       </c>
       <c r="B56" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,21 +6114,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6143,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581438</v>
+        <v>582006</v>
       </c>
       <c r="R56" t="n">
-        <v>6958399</v>
+        <v>6958447</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6179,6 +6174,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6205,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127620475</v>
+        <v>127626352</v>
       </c>
       <c r="B57" t="n">
-        <v>91332</v>
+        <v>91350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,34 +6216,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581829</v>
+        <v>581490</v>
       </c>
       <c r="R57" t="n">
-        <v>6958465</v>
+        <v>6958524</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>98367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R63" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6899,7 +6894,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626301</v>
+        <v>127626298</v>
       </c>
       <c r="B64" t="n">
         <v>57663</v>
@@ -6934,10 +6929,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582037</v>
+        <v>582124</v>
       </c>
       <c r="R64" t="n">
-        <v>6958341</v>
+        <v>6958327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7001,32 +6996,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626358</v>
+        <v>127626301</v>
       </c>
       <c r="B65" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7031,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582087</v>
+        <v>582037</v>
       </c>
       <c r="R65" t="n">
-        <v>6958421</v>
+        <v>6958341</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,6 +7067,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R66" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B67" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R67" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7271,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7302,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7313,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R68" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,11 +7373,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708929</v>
+        <v>127703408</v>
       </c>
       <c r="B83" t="n">
-        <v>92029</v>
+        <v>91332</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581702</v>
+        <v>581481</v>
       </c>
       <c r="R83" t="n">
-        <v>6958462</v>
+        <v>6958339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127702065</v>
+        <v>127708919</v>
       </c>
       <c r="B84" t="n">
-        <v>91742</v>
+        <v>91332</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581516</v>
+        <v>581468</v>
       </c>
       <c r="R84" t="n">
-        <v>6958469</v>
+        <v>6958461</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,32 +8997,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127703408</v>
+        <v>127708929</v>
       </c>
       <c r="B85" t="n">
-        <v>91332</v>
+        <v>92029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581481</v>
+        <v>581702</v>
       </c>
       <c r="R85" t="n">
-        <v>6958339</v>
+        <v>6958462</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708919</v>
+        <v>127702065</v>
       </c>
       <c r="B86" t="n">
-        <v>91332</v>
+        <v>91742</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581468</v>
+        <v>581516</v>
       </c>
       <c r="R86" t="n">
-        <v>6958461</v>
+        <v>6958469</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708921</v>
+        <v>127708935</v>
       </c>
       <c r="B91" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581549</v>
+        <v>581452</v>
       </c>
       <c r="R91" t="n">
-        <v>6958437</v>
+        <v>6958446</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,6 +9664,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9690,10 +9695,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127702448</v>
+        <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9706,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9730,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581480</v>
+        <v>581549</v>
       </c>
       <c r="R92" t="n">
-        <v>6958518</v>
+        <v>6958437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9787,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708951</v>
+        <v>127702448</v>
       </c>
       <c r="B93" t="n">
-        <v>92622</v>
+        <v>91628</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581943</v>
+        <v>581480</v>
       </c>
       <c r="R93" t="n">
-        <v>6958445</v>
+        <v>6958518</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9863,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708935</v>
+        <v>127708951</v>
       </c>
       <c r="B94" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581452</v>
+        <v>581943</v>
       </c>
       <c r="R94" t="n">
-        <v>6958446</v>
+        <v>6958445</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127708944</v>
+        <v>127700375</v>
       </c>
       <c r="B95" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,34 +10002,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581469</v>
+        <v>581797</v>
       </c>
       <c r="R95" t="n">
-        <v>6958479</v>
+        <v>6958452</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10062,6 +10070,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10088,10 +10101,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708917</v>
+        <v>127708944</v>
       </c>
       <c r="B96" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,21 +10112,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10123,10 +10136,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581459</v>
+        <v>581469</v>
       </c>
       <c r="R96" t="n">
-        <v>6958547</v>
+        <v>6958479</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10185,10 +10198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127700375</v>
+        <v>127708917</v>
       </c>
       <c r="B97" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10196,42 +10209,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581797</v>
+        <v>581459</v>
       </c>
       <c r="R97" t="n">
-        <v>6958452</v>
+        <v>6958547</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10264,11 +10269,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127708942</v>
+        <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>91628</v>
+        <v>91533</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581396</v>
+        <v>581423</v>
       </c>
       <c r="R104" t="n">
-        <v>6958454</v>
+        <v>6958511</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,7 +10974,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708946</v>
+        <v>127708942</v>
       </c>
       <c r="B105" t="n">
         <v>91628</v>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581559</v>
+        <v>581396</v>
       </c>
       <c r="R105" t="n">
-        <v>6958443</v>
+        <v>6958454</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127702553</v>
+        <v>127708946</v>
       </c>
       <c r="B106" t="n">
-        <v>91533</v>
+        <v>91628</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581423</v>
+        <v>581559</v>
       </c>
       <c r="R106" t="n">
-        <v>6958511</v>
+        <v>6958443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708947</v>
+        <v>127708937</v>
       </c>
       <c r="B109" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581574</v>
+        <v>581457</v>
       </c>
       <c r="R109" t="n">
-        <v>6958443</v>
+        <v>6958514</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11438,6 +11438,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11464,10 +11469,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708912</v>
+        <v>127708947</v>
       </c>
       <c r="B110" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11480,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11504,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581558</v>
+        <v>581574</v>
       </c>
       <c r="R110" t="n">
-        <v>6958357</v>
+        <v>6958443</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11561,10 +11566,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708937</v>
+        <v>127708912</v>
       </c>
       <c r="B111" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11572,21 +11577,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11596,10 +11601,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581457</v>
+        <v>581558</v>
       </c>
       <c r="R111" t="n">
-        <v>6958514</v>
+        <v>6958357</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11632,11 +11637,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R112" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,11 +11734,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11765,10 +11760,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11776,21 +11771,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11800,10 +11795,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R113" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11836,6 +11831,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127708926</v>
+        <v>127703591</v>
       </c>
       <c r="B114" t="n">
-        <v>92029</v>
+        <v>91690</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>2062</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581513</v>
+        <v>581485</v>
       </c>
       <c r="R114" t="n">
-        <v>6958336</v>
+        <v>6958325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,32 +11959,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708941</v>
+        <v>127708926</v>
       </c>
       <c r="B115" t="n">
-        <v>91628</v>
+        <v>92029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581486</v>
+        <v>581513</v>
       </c>
       <c r="R115" t="n">
-        <v>6958333</v>
+        <v>6958336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127702456</v>
+        <v>127708941</v>
       </c>
       <c r="B116" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12067,21 +12067,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581480</v>
+        <v>581486</v>
       </c>
       <c r="R116" t="n">
-        <v>6958518</v>
+        <v>6958333</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127703591</v>
+        <v>127702456</v>
       </c>
       <c r="B117" t="n">
-        <v>91690</v>
+        <v>91332</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581485</v>
+        <v>581480</v>
       </c>
       <c r="R117" t="n">
-        <v>6958325</v>
+        <v>6958518</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13041,32 +13041,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708939</v>
+        <v>127708927</v>
       </c>
       <c r="B126" t="n">
-        <v>57663</v>
+        <v>92029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581490</v>
+        <v>581489</v>
       </c>
       <c r="R126" t="n">
-        <v>6958459</v>
+        <v>6958369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13112,11 +13112,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13143,7 +13138,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127701827</v>
+        <v>127708939</v>
       </c>
       <c r="B127" t="n">
         <v>57663</v>
@@ -13172,21 +13167,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581564</v>
+        <v>581490</v>
       </c>
       <c r="R127" t="n">
-        <v>6958463</v>
+        <v>6958459</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13223,7 +13213,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13250,45 +13240,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708949</v>
+        <v>127701827</v>
       </c>
       <c r="B128" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581598</v>
+        <v>581564</v>
       </c>
       <c r="R128" t="n">
-        <v>6958396</v>
+        <v>6958463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13321,6 +13316,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13444,10 +13444,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708927</v>
+        <v>127708949</v>
       </c>
       <c r="B130" t="n">
-        <v>92029</v>
+        <v>98367</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13455,21 +13455,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3298</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581489</v>
+        <v>581598</v>
       </c>
       <c r="R130" t="n">
-        <v>6958369</v>
+        <v>6958396</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13735,32 +13735,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127702695</v>
+        <v>127708952</v>
       </c>
       <c r="B133" t="n">
-        <v>80123</v>
+        <v>92622</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581442</v>
+        <v>581959</v>
       </c>
       <c r="R133" t="n">
-        <v>6958493</v>
+        <v>6958445</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13832,32 +13832,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127708952</v>
+        <v>127702695</v>
       </c>
       <c r="B134" t="n">
-        <v>92622</v>
+        <v>80123</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13867,10 +13867,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>581959</v>
+        <v>581442</v>
       </c>
       <c r="R134" t="n">
-        <v>6958445</v>
+        <v>6958493</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626355</v>
+        <v>127626320</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581582</v>
+        <v>581658</v>
       </c>
       <c r="R11" t="n">
-        <v>6958488</v>
+        <v>6958452</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626320</v>
+        <v>127626355</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581658</v>
+        <v>581582</v>
       </c>
       <c r="R12" t="n">
-        <v>6958452</v>
+        <v>6958488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B13" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R13" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R14" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B48" t="n">
-        <v>91628</v>
+        <v>91350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R48" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B49" t="n">
-        <v>91350</v>
+        <v>91297</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R49" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626282</v>
+        <v>127626296</v>
       </c>
       <c r="B50" t="n">
-        <v>91297</v>
+        <v>57663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581658</v>
+        <v>581882</v>
       </c>
       <c r="R50" t="n">
-        <v>6958442</v>
+        <v>6958519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,6 +5582,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5608,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626296</v>
+        <v>127626345</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5619,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581882</v>
+        <v>581775</v>
       </c>
       <c r="R51" t="n">
-        <v>6958519</v>
+        <v>6958475</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5684,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7200,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626328</v>
+        <v>127626286</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581823</v>
+        <v>581497</v>
       </c>
       <c r="R67" t="n">
-        <v>6958452</v>
+        <v>6958542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,11 +7271,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B68" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7313,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R68" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,6 +7368,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127700375</v>
+        <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,42 +10002,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581797</v>
+        <v>581469</v>
       </c>
       <c r="R95" t="n">
-        <v>6958452</v>
+        <v>6958479</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,11 +10062,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10101,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708944</v>
+        <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91628</v>
+        <v>91332</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10112,21 +10099,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10136,10 +10123,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581469</v>
+        <v>581459</v>
       </c>
       <c r="R96" t="n">
-        <v>6958479</v>
+        <v>6958547</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10198,10 +10185,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127708917</v>
+        <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10209,34 +10196,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581459</v>
+        <v>581797</v>
       </c>
       <c r="R97" t="n">
-        <v>6958547</v>
+        <v>6958452</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10269,6 +10264,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13041,32 +13041,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708927</v>
+        <v>127708939</v>
       </c>
       <c r="B126" t="n">
-        <v>92029</v>
+        <v>57663</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581489</v>
+        <v>581490</v>
       </c>
       <c r="R126" t="n">
-        <v>6958369</v>
+        <v>6958459</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13112,6 +13112,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13138,7 +13143,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708939</v>
+        <v>127701827</v>
       </c>
       <c r="B127" t="n">
         <v>57663</v>
@@ -13167,16 +13172,21 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581490</v>
+        <v>581564</v>
       </c>
       <c r="R127" t="n">
-        <v>6958459</v>
+        <v>6958463</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13213,7 +13223,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Äldre ringhack på fallen död gran</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13240,50 +13250,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127701827</v>
+        <v>127708959</v>
       </c>
       <c r="B128" t="n">
-        <v>57663</v>
+        <v>92002</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R128" t="n">
-        <v>6958463</v>
+        <v>6958389</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13316,11 +13321,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,32 +13347,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708959</v>
+        <v>127708927</v>
       </c>
       <c r="B129" t="n">
-        <v>92002</v>
+        <v>92029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>898</v>
+        <v>3298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581595</v>
+        <v>581489</v>
       </c>
       <c r="R129" t="n">
-        <v>6958389</v>
+        <v>6958369</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626338</v>
+        <v>127626360</v>
       </c>
       <c r="B7" t="n">
-        <v>91628</v>
+        <v>98367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581544</v>
+        <v>581836</v>
       </c>
       <c r="R7" t="n">
-        <v>6958500</v>
+        <v>6958416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626319</v>
+        <v>127626338</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581409</v>
+        <v>581544</v>
       </c>
       <c r="R8" t="n">
-        <v>6958406</v>
+        <v>6958500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626360</v>
+        <v>127626319</v>
       </c>
       <c r="B9" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581836</v>
+        <v>581409</v>
       </c>
       <c r="R9" t="n">
-        <v>6958416</v>
+        <v>6958406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626320</v>
+        <v>127626355</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581658</v>
+        <v>581582</v>
       </c>
       <c r="R11" t="n">
-        <v>6958452</v>
+        <v>6958488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626355</v>
+        <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581582</v>
+        <v>581658</v>
       </c>
       <c r="R12" t="n">
-        <v>6958488</v>
+        <v>6958452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626348</v>
+        <v>127626323</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582065</v>
+        <v>581803</v>
       </c>
       <c r="R16" t="n">
-        <v>6958321</v>
+        <v>6958429</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626323</v>
+        <v>127626348</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581803</v>
+        <v>582065</v>
       </c>
       <c r="R17" t="n">
-        <v>6958429</v>
+        <v>6958321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3210,7 +3210,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626309</v>
+        <v>127626312</v>
       </c>
       <c r="B27" t="n">
         <v>57663</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581870</v>
+        <v>581642</v>
       </c>
       <c r="R27" t="n">
-        <v>6958478</v>
+        <v>6958463</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626333</v>
+        <v>127626309</v>
       </c>
       <c r="B28" t="n">
         <v>57663</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581835</v>
+        <v>581870</v>
       </c>
       <c r="R28" t="n">
-        <v>6958440</v>
+        <v>6958478</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626312</v>
+        <v>127626333</v>
       </c>
       <c r="B29" t="n">
         <v>57663</v>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581642</v>
+        <v>581835</v>
       </c>
       <c r="R29" t="n">
-        <v>6958463</v>
+        <v>6958440</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3516,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626340</v>
+        <v>127626302</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581474</v>
+        <v>582050</v>
       </c>
       <c r="R30" t="n">
-        <v>6958474</v>
+        <v>6958390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3587,6 +3587,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3613,7 +3618,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626302</v>
+        <v>127626305</v>
       </c>
       <c r="B31" t="n">
         <v>57663</v>
@@ -3648,10 +3653,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582050</v>
+        <v>581928</v>
       </c>
       <c r="R31" t="n">
-        <v>6958390</v>
+        <v>6958485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626305</v>
+        <v>127626318</v>
       </c>
       <c r="B32" t="n">
         <v>57663</v>
@@ -3750,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581928</v>
+        <v>581380</v>
       </c>
       <c r="R32" t="n">
-        <v>6958485</v>
+        <v>6958472</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,7 +3795,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,7 +3822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626318</v>
+        <v>127626324</v>
       </c>
       <c r="B33" t="n">
         <v>57663</v>
@@ -3852,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581380</v>
+        <v>581807</v>
       </c>
       <c r="R33" t="n">
-        <v>6958472</v>
+        <v>6958490</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3897,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,10 +3924,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626324</v>
+        <v>127626340</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3930,21 +3935,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581807</v>
+        <v>581474</v>
       </c>
       <c r="R34" t="n">
-        <v>6958490</v>
+        <v>6958474</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,11 +3995,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626342</v>
+        <v>127626327</v>
       </c>
       <c r="B42" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581440</v>
+        <v>581824</v>
       </c>
       <c r="R42" t="n">
-        <v>6958403</v>
+        <v>6958505</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626284</v>
+        <v>127626342</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581922</v>
+        <v>581440</v>
       </c>
       <c r="R43" t="n">
-        <v>6958467</v>
+        <v>6958403</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626350</v>
+        <v>127626284</v>
       </c>
       <c r="B44" t="n">
-        <v>91350</v>
+        <v>91332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4930,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581948</v>
+        <v>581922</v>
       </c>
       <c r="R44" t="n">
-        <v>6958486</v>
+        <v>6958467</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5011,10 +5016,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626297</v>
+        <v>127626350</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5027,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5051,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582085</v>
+        <v>581948</v>
       </c>
       <c r="R45" t="n">
-        <v>6958383</v>
+        <v>6958486</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,11 +5087,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5113,7 +5113,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626327</v>
+        <v>127626297</v>
       </c>
       <c r="B46" t="n">
         <v>57663</v>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581824</v>
+        <v>582085</v>
       </c>
       <c r="R46" t="n">
-        <v>6958505</v>
+        <v>6958383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626351</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>91350</v>
+        <v>91628</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581501</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958530</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626282</v>
+        <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91297</v>
+        <v>91350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581658</v>
+        <v>581501</v>
       </c>
       <c r="R49" t="n">
-        <v>6958442</v>
+        <v>6958530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626296</v>
+        <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>57663</v>
+        <v>91297</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581882</v>
+        <v>581658</v>
       </c>
       <c r="R50" t="n">
-        <v>6958519</v>
+        <v>6958442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,11 +5582,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5613,10 +5608,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626345</v>
+        <v>127626296</v>
       </c>
       <c r="B51" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5619,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581775</v>
+        <v>581882</v>
       </c>
       <c r="R51" t="n">
-        <v>6958475</v>
+        <v>6958519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5684,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127620475</v>
+        <v>127626329</v>
       </c>
       <c r="B54" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,34 +5915,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581829</v>
+        <v>581831</v>
       </c>
       <c r="R54" t="n">
-        <v>6958465</v>
+        <v>6958455</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5975,6 +5975,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6001,7 +6006,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626329</v>
+        <v>127626303</v>
       </c>
       <c r="B55" t="n">
         <v>57663</v>
@@ -6036,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581831</v>
+        <v>582006</v>
       </c>
       <c r="R55" t="n">
-        <v>6958455</v>
+        <v>6958447</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6076,7 +6081,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6103,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626303</v>
+        <v>127620475</v>
       </c>
       <c r="B56" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,34 +6119,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>582006</v>
+        <v>581829</v>
       </c>
       <c r="R56" t="n">
-        <v>6958447</v>
+        <v>6958465</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6174,11 +6179,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R66" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,11 +7169,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626286</v>
+        <v>127626357</v>
       </c>
       <c r="B67" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581497</v>
+        <v>581828</v>
       </c>
       <c r="R67" t="n">
-        <v>6958542</v>
+        <v>6958421</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7266,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626288</v>
+        <v>127626341</v>
       </c>
       <c r="B73" t="n">
-        <v>91332</v>
+        <v>91628</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581468</v>
+        <v>581425</v>
       </c>
       <c r="R73" t="n">
-        <v>6958479</v>
+        <v>6958396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,10 +7903,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626341</v>
+        <v>127626311</v>
       </c>
       <c r="B74" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7914,21 +7914,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581425</v>
+        <v>581684</v>
       </c>
       <c r="R74" t="n">
-        <v>6958396</v>
+        <v>6958471</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7974,6 +7974,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8000,7 +8005,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B75" t="n">
         <v>57663</v>
@@ -8035,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R75" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8075,7 +8080,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8102,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626304</v>
+        <v>127626288</v>
       </c>
       <c r="B76" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8113,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8137,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581961</v>
+        <v>581468</v>
       </c>
       <c r="R76" t="n">
-        <v>6958482</v>
+        <v>6958479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8173,11 +8178,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8803,10 +8803,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127703408</v>
+        <v>127708940</v>
       </c>
       <c r="B83" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8814,21 +8814,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581481</v>
+        <v>581551</v>
       </c>
       <c r="R83" t="n">
-        <v>6958339</v>
+        <v>6958433</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8874,6 +8874,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8900,10 +8905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708919</v>
+        <v>127700444</v>
       </c>
       <c r="B84" t="n">
-        <v>91332</v>
+        <v>57823</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8911,34 +8916,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581468</v>
+        <v>581826</v>
       </c>
       <c r="R84" t="n">
-        <v>6958461</v>
+        <v>6958437</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9191,10 +9205,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708940</v>
+        <v>127703408</v>
       </c>
       <c r="B87" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9202,21 +9216,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9226,10 +9240,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581551</v>
+        <v>581481</v>
       </c>
       <c r="R87" t="n">
-        <v>6958433</v>
+        <v>6958339</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9262,11 +9276,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9293,10 +9302,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700444</v>
+        <v>127708919</v>
       </c>
       <c r="B88" t="n">
-        <v>57823</v>
+        <v>91332</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9304,43 +9313,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581826</v>
+        <v>581468</v>
       </c>
       <c r="R88" t="n">
-        <v>6958437</v>
+        <v>6958461</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9399,7 +9399,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127708911</v>
+        <v>127708910</v>
       </c>
       <c r="B89" t="n">
         <v>91332</v>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>581597</v>
+        <v>581604</v>
       </c>
       <c r="R89" t="n">
-        <v>6958391</v>
+        <v>6958417</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9496,7 +9496,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127708910</v>
+        <v>127708911</v>
       </c>
       <c r="B90" t="n">
         <v>91332</v>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>581604</v>
+        <v>581597</v>
       </c>
       <c r="R90" t="n">
-        <v>6958417</v>
+        <v>6958391</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708935</v>
+        <v>127702448</v>
       </c>
       <c r="B91" t="n">
-        <v>57663</v>
+        <v>91628</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581452</v>
+        <v>581480</v>
       </c>
       <c r="R91" t="n">
-        <v>6958446</v>
+        <v>6958518</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,11 +9664,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9695,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708921</v>
+        <v>127708935</v>
       </c>
       <c r="B92" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9706,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9730,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581549</v>
+        <v>581452</v>
       </c>
       <c r="R92" t="n">
-        <v>6958437</v>
+        <v>6958446</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9766,6 +9761,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9792,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127702448</v>
+        <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>91628</v>
+        <v>92622</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581480</v>
+        <v>581943</v>
       </c>
       <c r="R93" t="n">
-        <v>6958518</v>
+        <v>6958445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,6 +9863,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9894,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708951</v>
+        <v>127708921</v>
       </c>
       <c r="B94" t="n">
-        <v>92622</v>
+        <v>91332</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581943</v>
+        <v>581549</v>
       </c>
       <c r="R94" t="n">
-        <v>6958445</v>
+        <v>6958437</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9960,11 +9965,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127708916</v>
+        <v>127701709</v>
       </c>
       <c r="B99" t="n">
-        <v>91332</v>
+        <v>92029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581451</v>
+        <v>581590</v>
       </c>
       <c r="R99" t="n">
-        <v>6958466</v>
+        <v>6958438</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127701709</v>
+        <v>127708916</v>
       </c>
       <c r="B100" t="n">
-        <v>92029</v>
+        <v>91332</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581590</v>
+        <v>581451</v>
       </c>
       <c r="R100" t="n">
-        <v>6958438</v>
+        <v>6958466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10683,32 +10683,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127708920</v>
+        <v>127708924</v>
       </c>
       <c r="B102" t="n">
-        <v>91332</v>
+        <v>92029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>581517</v>
+        <v>581607</v>
       </c>
       <c r="R102" t="n">
-        <v>6958471</v>
+        <v>6958406</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127708924</v>
+        <v>127708920</v>
       </c>
       <c r="B103" t="n">
-        <v>92029</v>
+        <v>91332</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>581607</v>
+        <v>581517</v>
       </c>
       <c r="R103" t="n">
-        <v>6958406</v>
+        <v>6958471</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127702553</v>
+        <v>127708946</v>
       </c>
       <c r="B104" t="n">
-        <v>91533</v>
+        <v>91628</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581423</v>
+        <v>581559</v>
       </c>
       <c r="R104" t="n">
-        <v>6958511</v>
+        <v>6958443</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708946</v>
+        <v>127700450</v>
       </c>
       <c r="B106" t="n">
-        <v>91628</v>
+        <v>57823</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11082,34 +11082,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581559</v>
+        <v>581789</v>
       </c>
       <c r="R106" t="n">
-        <v>6958443</v>
+        <v>6958477</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,50 +11173,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127700450</v>
+        <v>127702553</v>
       </c>
       <c r="B107" t="n">
-        <v>57823</v>
+        <v>91533</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581789</v>
+        <v>581423</v>
       </c>
       <c r="R107" t="n">
-        <v>6958477</v>
+        <v>6958511</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708937</v>
+        <v>127708912</v>
       </c>
       <c r="B109" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581457</v>
+        <v>581558</v>
       </c>
       <c r="R109" t="n">
-        <v>6958514</v>
+        <v>6958357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11438,11 +11438,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11566,10 +11561,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B111" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11577,21 +11572,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11601,10 +11596,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R111" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11637,6 +11632,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B112" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R112" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,6 +11734,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11760,10 +11765,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B113" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11771,21 +11776,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11795,10 +11800,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R113" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11831,11 +11836,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127703591</v>
+        <v>127708926</v>
       </c>
       <c r="B114" t="n">
-        <v>91690</v>
+        <v>92029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2062</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581485</v>
+        <v>581513</v>
       </c>
       <c r="R114" t="n">
-        <v>6958325</v>
+        <v>6958336</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,32 +11959,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708926</v>
+        <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>92029</v>
+        <v>91628</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581513</v>
+        <v>581486</v>
       </c>
       <c r="R115" t="n">
-        <v>6958336</v>
+        <v>6958333</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127708941</v>
+        <v>127703591</v>
       </c>
       <c r="B116" t="n">
-        <v>91628</v>
+        <v>91690</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581486</v>
+        <v>581485</v>
       </c>
       <c r="R116" t="n">
-        <v>6958333</v>
+        <v>6958325</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12847,32 +12847,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127708909</v>
+        <v>127708950</v>
       </c>
       <c r="B124" t="n">
-        <v>91332</v>
+        <v>98367</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>581606</v>
+        <v>581502</v>
       </c>
       <c r="R124" t="n">
-        <v>6958438</v>
+        <v>6958332</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12944,32 +12944,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127708950</v>
+        <v>127708909</v>
       </c>
       <c r="B125" t="n">
-        <v>98367</v>
+        <v>91332</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>581502</v>
+        <v>581606</v>
       </c>
       <c r="R125" t="n">
-        <v>6958332</v>
+        <v>6958438</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13041,7 +13041,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708939</v>
+        <v>127701827</v>
       </c>
       <c r="B126" t="n">
         <v>57663</v>
@@ -13070,16 +13070,21 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581490</v>
+        <v>581564</v>
       </c>
       <c r="R126" t="n">
-        <v>6958459</v>
+        <v>6958463</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13116,7 +13121,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Äldre ringhack på fallen död gran</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13143,7 +13148,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127701827</v>
+        <v>127708939</v>
       </c>
       <c r="B127" t="n">
         <v>57663</v>
@@ -13172,21 +13177,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581564</v>
+        <v>581490</v>
       </c>
       <c r="R127" t="n">
-        <v>6958463</v>
+        <v>6958459</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13250,32 +13250,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708959</v>
+        <v>127708949</v>
       </c>
       <c r="B128" t="n">
-        <v>92002</v>
+        <v>98367</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>898</v>
+        <v>219790</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581595</v>
+        <v>581598</v>
       </c>
       <c r="R128" t="n">
-        <v>6958389</v>
+        <v>6958396</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13347,32 +13347,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708927</v>
+        <v>127708959</v>
       </c>
       <c r="B129" t="n">
-        <v>92029</v>
+        <v>92002</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>898</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581489</v>
+        <v>581595</v>
       </c>
       <c r="R129" t="n">
-        <v>6958369</v>
+        <v>6958389</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13444,10 +13444,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708949</v>
+        <v>127708927</v>
       </c>
       <c r="B130" t="n">
-        <v>98367</v>
+        <v>92029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13455,21 +13455,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219790</v>
+        <v>3298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581598</v>
+        <v>581489</v>
       </c>
       <c r="R130" t="n">
-        <v>6958396</v>
+        <v>6958369</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708914</v>
+        <v>127702695</v>
       </c>
       <c r="B131" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581433</v>
+        <v>581442</v>
       </c>
       <c r="R131" t="n">
-        <v>6958423</v>
+        <v>6958493</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13832,10 +13832,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127702695</v>
+        <v>127708914</v>
       </c>
       <c r="B134" t="n">
-        <v>80123</v>
+        <v>91332</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13843,21 +13843,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13867,10 +13867,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>581442</v>
+        <v>581433</v>
       </c>
       <c r="R134" t="n">
-        <v>6958493</v>
+        <v>6958423</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626360</v>
+        <v>127626319</v>
       </c>
       <c r="B7" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581836</v>
+        <v>581409</v>
       </c>
       <c r="R7" t="n">
-        <v>6958416</v>
+        <v>6958406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1306,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1340,7 @@
         <v>127626338</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R9" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B10" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R10" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>91634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R11" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R13" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R14" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +1995,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626289</v>
+        <v>127626348</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581425</v>
+        <v>582065</v>
       </c>
       <c r="R15" t="n">
-        <v>6958401</v>
+        <v>6958321</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626323</v>
+        <v>127626289</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581803</v>
+        <v>581425</v>
       </c>
       <c r="R16" t="n">
-        <v>6958429</v>
+        <v>6958401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626348</v>
+        <v>127626323</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582065</v>
+        <v>581803</v>
       </c>
       <c r="R17" t="n">
-        <v>6958321</v>
+        <v>6958429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626285</v>
+        <v>127626321</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581551</v>
+        <v>581718</v>
       </c>
       <c r="R18" t="n">
-        <v>6958485</v>
+        <v>6958467</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,6 +2393,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626321</v>
+        <v>127626285</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581718</v>
+        <v>581551</v>
       </c>
       <c r="R20" t="n">
-        <v>6958467</v>
+        <v>6958485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,11 +2592,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626283</v>
+        <v>127626291</v>
       </c>
       <c r="B24" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582010</v>
+        <v>581538</v>
       </c>
       <c r="R24" t="n">
-        <v>6958445</v>
+        <v>6958404</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
         <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626291</v>
+        <v>127626283</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581538</v>
+        <v>582010</v>
       </c>
       <c r="R26" t="n">
-        <v>6958404</v>
+        <v>6958445</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626312</v>
+        <v>127626309</v>
       </c>
       <c r="B27" t="n">
         <v>57663</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581642</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6958463</v>
+        <v>6958478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626309</v>
+        <v>127626333</v>
       </c>
       <c r="B28" t="n">
         <v>57663</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581870</v>
+        <v>581835</v>
       </c>
       <c r="R28" t="n">
-        <v>6958478</v>
+        <v>6958440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626333</v>
+        <v>127626312</v>
       </c>
       <c r="B29" t="n">
         <v>57663</v>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581835</v>
+        <v>581642</v>
       </c>
       <c r="R29" t="n">
-        <v>6958440</v>
+        <v>6958463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3516,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626302</v>
+        <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>91634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582050</v>
+        <v>581474</v>
       </c>
       <c r="R30" t="n">
-        <v>6958390</v>
+        <v>6958474</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3587,11 +3587,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,7 +3613,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626305</v>
+        <v>127626302</v>
       </c>
       <c r="B31" t="n">
         <v>57663</v>
@@ -3653,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581928</v>
+        <v>582050</v>
       </c>
       <c r="R31" t="n">
-        <v>6958485</v>
+        <v>6958390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626318</v>
+        <v>127626305</v>
       </c>
       <c r="B32" t="n">
         <v>57663</v>
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581380</v>
+        <v>581928</v>
       </c>
       <c r="R32" t="n">
-        <v>6958472</v>
+        <v>6958485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3795,7 +3790,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626324</v>
+        <v>127626318</v>
       </c>
       <c r="B33" t="n">
         <v>57663</v>
@@ -3857,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581807</v>
+        <v>581380</v>
       </c>
       <c r="R33" t="n">
-        <v>6958490</v>
+        <v>6958472</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3924,10 +3919,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626340</v>
+        <v>127626324</v>
       </c>
       <c r="B34" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,21 +3930,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581474</v>
+        <v>581807</v>
       </c>
       <c r="R34" t="n">
-        <v>6958474</v>
+        <v>6958490</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3990,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4126,7 +4126,7 @@
         <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626327</v>
+        <v>127626297</v>
       </c>
       <c r="B42" t="n">
         <v>57663</v>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581824</v>
+        <v>582085</v>
       </c>
       <c r="R42" t="n">
-        <v>6958505</v>
+        <v>6958383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626342</v>
+        <v>127626327</v>
       </c>
       <c r="B43" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581440</v>
+        <v>581824</v>
       </c>
       <c r="R43" t="n">
-        <v>6958403</v>
+        <v>6958505</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,6 +4893,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4919,10 +4924,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626284</v>
+        <v>127626316</v>
       </c>
       <c r="B44" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4930,21 +4935,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581922</v>
+        <v>581480</v>
       </c>
       <c r="R44" t="n">
-        <v>6958467</v>
+        <v>6958548</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4990,6 +4995,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5016,10 +5026,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626350</v>
+        <v>127626342</v>
       </c>
       <c r="B45" t="n">
-        <v>91350</v>
+        <v>91634</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5027,21 +5037,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5051,10 +5061,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581948</v>
+        <v>581440</v>
       </c>
       <c r="R45" t="n">
-        <v>6958486</v>
+        <v>6958403</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,10 +5123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626297</v>
+        <v>127626284</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5124,21 +5134,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582085</v>
+        <v>581922</v>
       </c>
       <c r="R46" t="n">
-        <v>6958383</v>
+        <v>6958467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,11 +5194,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5215,10 +5220,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626316</v>
+        <v>127626350</v>
       </c>
       <c r="B47" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5226,21 +5231,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5250,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581480</v>
+        <v>581948</v>
       </c>
       <c r="R47" t="n">
-        <v>6958548</v>
+        <v>6958486</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,11 +5291,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B48" t="n">
-        <v>91628</v>
+        <v>91356</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R48" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B49" t="n">
-        <v>91350</v>
+        <v>91303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R49" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626282</v>
+        <v>127626345</v>
       </c>
       <c r="B50" t="n">
-        <v>91297</v>
+        <v>91634</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581658</v>
+        <v>581775</v>
       </c>
       <c r="R50" t="n">
-        <v>6958442</v>
+        <v>6958475</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626339</v>
+        <v>127626329</v>
       </c>
       <c r="B52" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581484</v>
+        <v>581831</v>
       </c>
       <c r="R52" t="n">
-        <v>6958540</v>
+        <v>6958455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,6 +5781,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5807,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626290</v>
+        <v>127626303</v>
       </c>
       <c r="B53" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581438</v>
+        <v>582006</v>
       </c>
       <c r="R53" t="n">
-        <v>6958399</v>
+        <v>6958447</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5883,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5904,10 +5914,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626329</v>
+        <v>127626290</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,21 +5925,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5949,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581831</v>
+        <v>581438</v>
       </c>
       <c r="R54" t="n">
-        <v>6958455</v>
+        <v>6958399</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5975,11 +5985,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6006,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626303</v>
+        <v>127620475</v>
       </c>
       <c r="B55" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,34 +6022,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>582006</v>
+        <v>581829</v>
       </c>
       <c r="R55" t="n">
-        <v>6958447</v>
+        <v>6958465</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6077,11 +6082,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127620475</v>
+        <v>127626339</v>
       </c>
       <c r="B56" t="n">
-        <v>91332</v>
+        <v>91634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,34 +6119,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581829</v>
+        <v>581484</v>
       </c>
       <c r="R56" t="n">
-        <v>6958465</v>
+        <v>6958540</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6208,7 +6208,7 @@
         <v>127626352</v>
       </c>
       <c r="B57" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B59" t="n">
-        <v>91628</v>
+        <v>91338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R59" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B60" t="n">
-        <v>91332</v>
+        <v>91634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R60" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
         <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626358</v>
+        <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582087</v>
+        <v>582124</v>
       </c>
       <c r="R63" t="n">
-        <v>6958421</v>
+        <v>6958327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,7 +6899,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626298</v>
+        <v>127626301</v>
       </c>
       <c r="B64" t="n">
         <v>57663</v>
@@ -6929,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582124</v>
+        <v>582037</v>
       </c>
       <c r="R64" t="n">
-        <v>6958327</v>
+        <v>6958341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6996,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626301</v>
+        <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>57663</v>
+        <v>98373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7031,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582037</v>
+        <v>582087</v>
       </c>
       <c r="R65" t="n">
-        <v>6958341</v>
+        <v>6958421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7067,11 +7072,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7101,7 +7101,7 @@
         <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626357</v>
+        <v>127626328</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581828</v>
+        <v>581823</v>
       </c>
       <c r="R67" t="n">
-        <v>6958421</v>
+        <v>6958452</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R68" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626341</v>
+        <v>127626311</v>
       </c>
       <c r="B73" t="n">
-        <v>91628</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581425</v>
+        <v>581684</v>
       </c>
       <c r="R73" t="n">
-        <v>6958396</v>
+        <v>6958471</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7877,6 +7877,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7903,7 +7908,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B74" t="n">
         <v>57663</v>
@@ -7938,10 +7943,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R74" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7978,7 +7983,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8005,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626304</v>
+        <v>127626288</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8016,21 +8021,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8040,10 +8045,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581961</v>
+        <v>581468</v>
       </c>
       <c r="R75" t="n">
-        <v>6958482</v>
+        <v>6958479</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8076,11 +8081,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8107,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626288</v>
+        <v>127626341</v>
       </c>
       <c r="B76" t="n">
-        <v>91332</v>
+        <v>91634</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581468</v>
+        <v>581425</v>
       </c>
       <c r="R76" t="n">
-        <v>6958479</v>
+        <v>6958396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92002</v>
+        <v>92008</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91533</v>
+        <v>91539</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127708953</v>
+        <v>127703408</v>
       </c>
       <c r="B82" t="n">
-        <v>88735</v>
+        <v>91338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581497</v>
+        <v>581481</v>
       </c>
       <c r="R82" t="n">
-        <v>6958369</v>
+        <v>6958339</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708940</v>
+        <v>127702065</v>
       </c>
       <c r="B83" t="n">
-        <v>57663</v>
+        <v>91748</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581551</v>
+        <v>581516</v>
       </c>
       <c r="R83" t="n">
-        <v>6958433</v>
+        <v>6958469</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8874,11 +8874,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8905,10 +8900,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B84" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8916,43 +8911,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R84" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8985,6 +8971,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9011,45 +9002,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127708929</v>
+        <v>127700444</v>
       </c>
       <c r="B85" t="n">
-        <v>92029</v>
+        <v>57823</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581702</v>
+        <v>581826</v>
       </c>
       <c r="R85" t="n">
-        <v>6958462</v>
+        <v>6958437</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9108,32 +9108,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127702065</v>
+        <v>127708953</v>
       </c>
       <c r="B86" t="n">
-        <v>91742</v>
+        <v>88741</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>510</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9143,10 +9143,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581516</v>
+        <v>581497</v>
       </c>
       <c r="R86" t="n">
-        <v>6958469</v>
+        <v>6958369</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127703408</v>
+        <v>127708919</v>
       </c>
       <c r="B87" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581481</v>
+        <v>581468</v>
       </c>
       <c r="R87" t="n">
-        <v>6958339</v>
+        <v>6958461</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9302,32 +9302,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127708919</v>
+        <v>127708929</v>
       </c>
       <c r="B88" t="n">
-        <v>91332</v>
+        <v>92035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581468</v>
+        <v>581702</v>
       </c>
       <c r="R88" t="n">
-        <v>6958461</v>
+        <v>6958462</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9402,7 +9402,7 @@
         <v>127708910</v>
       </c>
       <c r="B89" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>127708911</v>
       </c>
       <c r="B90" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>127702448</v>
       </c>
       <c r="B91" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708935</v>
+        <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581452</v>
+        <v>581549</v>
       </c>
       <c r="R92" t="n">
-        <v>6958446</v>
+        <v>6958437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,11 +9761,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9795,7 +9790,7 @@
         <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9894,10 +9889,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708921</v>
+        <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9905,21 +9900,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581549</v>
+        <v>581452</v>
       </c>
       <c r="R94" t="n">
-        <v>6958437</v>
+        <v>6958446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9965,6 +9960,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9994,7 +9994,7 @@
         <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B98" t="n">
-        <v>91628</v>
+        <v>91338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R98" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127701709</v>
+        <v>127708945</v>
       </c>
       <c r="B99" t="n">
-        <v>92029</v>
+        <v>91634</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581590</v>
+        <v>581512</v>
       </c>
       <c r="R99" t="n">
-        <v>6958438</v>
+        <v>6958472</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708916</v>
+        <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>91332</v>
+        <v>92035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581451</v>
+        <v>581590</v>
       </c>
       <c r="R100" t="n">
-        <v>6958466</v>
+        <v>6958438</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10683,32 +10683,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127708924</v>
+        <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>92029</v>
+        <v>91338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>581607</v>
+        <v>581517</v>
       </c>
       <c r="R102" t="n">
-        <v>6958406</v>
+        <v>6958471</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127708920</v>
+        <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>91332</v>
+        <v>92035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>581517</v>
+        <v>581607</v>
       </c>
       <c r="R103" t="n">
-        <v>6958471</v>
+        <v>6958406</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10880,7 +10880,7 @@
         <v>127708946</v>
       </c>
       <c r="B104" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>127708942</v>
       </c>
       <c r="B105" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11071,50 +11071,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127700450</v>
+        <v>127702553</v>
       </c>
       <c r="B106" t="n">
-        <v>57823</v>
+        <v>91539</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581789</v>
+        <v>581423</v>
       </c>
       <c r="R106" t="n">
-        <v>6958477</v>
+        <v>6958511</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11173,45 +11168,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127702553</v>
+        <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>91533</v>
+        <v>57823</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581423</v>
+        <v>581789</v>
       </c>
       <c r="R107" t="n">
-        <v>6958511</v>
+        <v>6958477</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B109" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R109" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11438,6 +11438,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11467,7 +11472,7 @@
         <v>127708947</v>
       </c>
       <c r="B110" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11561,10 +11566,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708937</v>
+        <v>127708912</v>
       </c>
       <c r="B111" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11572,21 +11577,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11596,10 +11601,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581457</v>
+        <v>581558</v>
       </c>
       <c r="R111" t="n">
-        <v>6958514</v>
+        <v>6958357</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11632,11 +11637,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R112" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,11 +11734,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11765,10 +11760,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11776,21 +11771,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11800,10 +11795,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R113" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11836,6 +11831,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127708926</v>
+        <v>127702456</v>
       </c>
       <c r="B114" t="n">
-        <v>92029</v>
+        <v>91338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581513</v>
+        <v>581480</v>
       </c>
       <c r="R114" t="n">
-        <v>6958336</v>
+        <v>6958518</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11962,7 +11962,7 @@
         <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127703591</v>
+        <v>127708926</v>
       </c>
       <c r="B116" t="n">
-        <v>91690</v>
+        <v>92035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>3298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581485</v>
+        <v>581513</v>
       </c>
       <c r="R116" t="n">
-        <v>6958325</v>
+        <v>6958336</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127702456</v>
+        <v>127703591</v>
       </c>
       <c r="B117" t="n">
-        <v>91332</v>
+        <v>91696</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581480</v>
+        <v>581485</v>
       </c>
       <c r="R117" t="n">
-        <v>6958518</v>
+        <v>6958325</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12253,7 +12253,7 @@
         <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>127708950</v>
       </c>
       <c r="B124" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>127708909</v>
       </c>
       <c r="B125" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13041,50 +13041,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127701827</v>
+        <v>127708959</v>
       </c>
       <c r="B126" t="n">
-        <v>57663</v>
+        <v>92008</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R126" t="n">
-        <v>6958463</v>
+        <v>6958389</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13117,11 +13112,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13250,45 +13240,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708949</v>
+        <v>127701827</v>
       </c>
       <c r="B128" t="n">
-        <v>98367</v>
+        <v>57663</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581598</v>
+        <v>581564</v>
       </c>
       <c r="R128" t="n">
-        <v>6958396</v>
+        <v>6958463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13321,6 +13316,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,32 +13347,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708959</v>
+        <v>127708949</v>
       </c>
       <c r="B129" t="n">
-        <v>92002</v>
+        <v>98373</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>898</v>
+        <v>219790</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581595</v>
+        <v>581598</v>
       </c>
       <c r="R129" t="n">
-        <v>6958389</v>
+        <v>6958396</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13447,7 +13447,7 @@
         <v>127708927</v>
       </c>
       <c r="B130" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B132" t="n">
-        <v>91628</v>
+        <v>91338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R132" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,32 +13735,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708952</v>
+        <v>127708943</v>
       </c>
       <c r="B133" t="n">
-        <v>92622</v>
+        <v>91634</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581959</v>
+        <v>581472</v>
       </c>
       <c r="R133" t="n">
-        <v>6958445</v>
+        <v>6958521</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13832,32 +13832,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127708914</v>
+        <v>127708952</v>
       </c>
       <c r="B134" t="n">
-        <v>91332</v>
+        <v>92628</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13867,10 +13867,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>581433</v>
+        <v>581959</v>
       </c>
       <c r="R134" t="n">
-        <v>6958423</v>
+        <v>6958445</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AY136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,7 +1238,7 @@
         <v>127626319</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626338</v>
+        <v>127626360</v>
       </c>
       <c r="B8" t="n">
-        <v>91634</v>
+        <v>98376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581544</v>
+        <v>581836</v>
       </c>
       <c r="R8" t="n">
-        <v>6958500</v>
+        <v>6958416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626360</v>
+        <v>127626338</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>91637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581836</v>
+        <v>581544</v>
       </c>
       <c r="R9" t="n">
-        <v>6958416</v>
+        <v>6958500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
         <v>127626355</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>127626344</v>
       </c>
       <c r="B11" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127626332</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>91341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R15" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626289</v>
+        <v>127626348</v>
       </c>
       <c r="B16" t="n">
-        <v>91338</v>
+        <v>80126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581425</v>
+        <v>582065</v>
       </c>
       <c r="R16" t="n">
-        <v>6958401</v>
+        <v>6958321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,7 +2223,7 @@
         <v>127626323</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626321</v>
+        <v>127626336</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>80155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581718</v>
+        <v>582065</v>
       </c>
       <c r="R18" t="n">
-        <v>6958467</v>
+        <v>6958323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626336</v>
+        <v>127626321</v>
       </c>
       <c r="B19" t="n">
-        <v>80152</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582065</v>
+        <v>581718</v>
       </c>
       <c r="R19" t="n">
-        <v>6958323</v>
+        <v>6958467</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,7 +2524,7 @@
         <v>127626285</v>
       </c>
       <c r="B20" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>127626356</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>127626322</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>127626306</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626291</v>
+        <v>127626309</v>
       </c>
       <c r="B24" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581538</v>
+        <v>581870</v>
       </c>
       <c r="R24" t="n">
-        <v>6958404</v>
+        <v>6958478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,6 +2990,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3016,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B25" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,21 +3032,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R25" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,6 +3092,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626283</v>
+        <v>127626312</v>
       </c>
       <c r="B26" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,21 +3134,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3148,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582010</v>
+        <v>581642</v>
       </c>
       <c r="R26" t="n">
-        <v>6958445</v>
+        <v>6958463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,6 +3194,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3210,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,21 +3236,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3245,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R27" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,11 +3296,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3312,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R28" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,11 +3393,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,10 +3419,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,21 +3430,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R29" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,11 +3490,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3519,7 @@
         <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>127626302</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127626305</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>127626318</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>127626324</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127626295</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626354</v>
+        <v>127626347</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>80154</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582103</v>
+        <v>582104</v>
       </c>
       <c r="R37" t="n">
-        <v>6958332</v>
+        <v>6958386</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,32 +4317,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626347</v>
+        <v>127626354</v>
       </c>
       <c r="B38" t="n">
-        <v>80151</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582104</v>
+        <v>582103</v>
       </c>
       <c r="R38" t="n">
-        <v>6958386</v>
+        <v>6958332</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4417,7 +4417,7 @@
         <v>127626325</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>127626299</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>127626300</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626297</v>
+        <v>127626316</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582085</v>
+        <v>581480</v>
       </c>
       <c r="R42" t="n">
-        <v>6958383</v>
+        <v>6958548</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626327</v>
+        <v>127626284</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4833,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581824</v>
+        <v>581922</v>
       </c>
       <c r="R43" t="n">
-        <v>6958505</v>
+        <v>6958467</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,11 +4893,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4924,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626316</v>
+        <v>127626350</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4935,21 +4930,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581480</v>
+        <v>581948</v>
       </c>
       <c r="R44" t="n">
-        <v>6958548</v>
+        <v>6958486</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,11 +4990,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5029,7 +5019,7 @@
         <v>127626342</v>
       </c>
       <c r="B45" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5123,10 +5113,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626284</v>
+        <v>127626297</v>
       </c>
       <c r="B46" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,21 +5124,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5158,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581922</v>
+        <v>582085</v>
       </c>
       <c r="R46" t="n">
-        <v>6958467</v>
+        <v>6958383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5194,6 +5184,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5220,10 +5215,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626350</v>
+        <v>127626327</v>
       </c>
       <c r="B47" t="n">
-        <v>91356</v>
+        <v>57666</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,21 +5226,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581948</v>
+        <v>581824</v>
       </c>
       <c r="R47" t="n">
-        <v>6958486</v>
+        <v>6958505</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,6 +5286,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5320,7 +5320,7 @@
         <v>127626351</v>
       </c>
       <c r="B48" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>127626282</v>
       </c>
       <c r="B49" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>127626345</v>
       </c>
       <c r="B50" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>127626296</v>
       </c>
       <c r="B51" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>127626329</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>127626303</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5914,10 +5914,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626290</v>
+        <v>127626352</v>
       </c>
       <c r="B54" t="n">
-        <v>91338</v>
+        <v>91359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5925,21 +5925,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581438</v>
+        <v>581490</v>
       </c>
       <c r="R54" t="n">
-        <v>6958399</v>
+        <v>6958524</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127620475</v>
+        <v>127626339</v>
       </c>
       <c r="B55" t="n">
-        <v>91338</v>
+        <v>91637</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,34 +6022,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581829</v>
+        <v>581484</v>
       </c>
       <c r="R55" t="n">
-        <v>6958465</v>
+        <v>6958540</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626339</v>
+        <v>127626290</v>
       </c>
       <c r="B56" t="n">
-        <v>91634</v>
+        <v>91341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,21 +6119,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581484</v>
+        <v>581438</v>
       </c>
       <c r="R56" t="n">
-        <v>6958540</v>
+        <v>6958399</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6205,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626352</v>
+        <v>127620475</v>
       </c>
       <c r="B57" t="n">
-        <v>91356</v>
+        <v>91341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,34 +6216,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581490</v>
+        <v>581829</v>
       </c>
       <c r="R57" t="n">
-        <v>6958524</v>
+        <v>6958465</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,7 +6305,7 @@
         <v>127626315</v>
       </c>
       <c r="B58" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>127626294</v>
       </c>
       <c r="B59" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>127626343</v>
       </c>
       <c r="B60" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127626301</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626286</v>
+        <v>127626357</v>
       </c>
       <c r="B66" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581497</v>
+        <v>581828</v>
       </c>
       <c r="R66" t="n">
-        <v>6958542</v>
+        <v>6958421</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,6 +7169,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7198,7 +7203,7 @@
         <v>127626328</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7297,10 +7302,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7313,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R68" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,11 +7373,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7402,7 +7402,7 @@
         <v>127622082</v>
       </c>
       <c r="B69" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>127626326</v>
       </c>
       <c r="B70" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>127626307</v>
       </c>
       <c r="B71" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626311</v>
+        <v>127626341</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>91637</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581684</v>
+        <v>581425</v>
       </c>
       <c r="R73" t="n">
-        <v>6958471</v>
+        <v>6958396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7877,11 +7877,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7911,7 +7906,7 @@
         <v>127626304</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8013,7 +8008,7 @@
         <v>127626288</v>
       </c>
       <c r="B75" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8107,10 +8102,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626341</v>
+        <v>127626311</v>
       </c>
       <c r="B76" t="n">
-        <v>91634</v>
+        <v>57666</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8113,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581425</v>
+        <v>581684</v>
       </c>
       <c r="R76" t="n">
-        <v>6958396</v>
+        <v>6958471</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8178,6 +8173,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8207,7 +8207,7 @@
         <v>127626317</v>
       </c>
       <c r="B77" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92008</v>
+        <v>92011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127703408</v>
+        <v>127708940</v>
       </c>
       <c r="B82" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581481</v>
+        <v>581551</v>
       </c>
       <c r="R82" t="n">
-        <v>6958339</v>
+        <v>6958433</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8777,6 +8777,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8803,32 +8808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127702065</v>
+        <v>127703408</v>
       </c>
       <c r="B83" t="n">
-        <v>91748</v>
+        <v>91341</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581516</v>
+        <v>581481</v>
       </c>
       <c r="R83" t="n">
-        <v>6958469</v>
+        <v>6958339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,10 +8905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708940</v>
+        <v>127708919</v>
       </c>
       <c r="B84" t="n">
-        <v>57663</v>
+        <v>91341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8911,21 +8916,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581551</v>
+        <v>581468</v>
       </c>
       <c r="R84" t="n">
-        <v>6958433</v>
+        <v>6958461</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8971,11 +8976,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9002,10 +9002,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127700444</v>
+        <v>127708953</v>
       </c>
       <c r="B85" t="n">
-        <v>57823</v>
+        <v>88744</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9013,43 +9013,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>510</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581826</v>
+        <v>581497</v>
       </c>
       <c r="R85" t="n">
-        <v>6958437</v>
+        <v>6958369</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9108,32 +9099,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708953</v>
+        <v>127702065</v>
       </c>
       <c r="B86" t="n">
-        <v>88741</v>
+        <v>91751</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>510</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9143,10 +9134,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581497</v>
+        <v>581516</v>
       </c>
       <c r="R86" t="n">
-        <v>6958369</v>
+        <v>6958469</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9205,32 +9196,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708919</v>
+        <v>127708929</v>
       </c>
       <c r="B87" t="n">
-        <v>91338</v>
+        <v>92038</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9240,10 +9231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581468</v>
+        <v>581702</v>
       </c>
       <c r="R87" t="n">
-        <v>6958461</v>
+        <v>6958462</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9302,45 +9293,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127708929</v>
+        <v>127700444</v>
       </c>
       <c r="B88" t="n">
-        <v>92035</v>
+        <v>57826</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581702</v>
+        <v>581826</v>
       </c>
       <c r="R88" t="n">
-        <v>6958462</v>
+        <v>6958437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127708910</v>
+        <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>581604</v>
+        <v>581597</v>
       </c>
       <c r="R89" t="n">
-        <v>6958417</v>
+        <v>6958391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9496,10 +9496,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127708911</v>
+        <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>581597</v>
+        <v>581604</v>
       </c>
       <c r="R90" t="n">
-        <v>6958391</v>
+        <v>6958417</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9593,32 +9593,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127702448</v>
+        <v>127708951</v>
       </c>
       <c r="B91" t="n">
-        <v>91634</v>
+        <v>92631</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581480</v>
+        <v>581943</v>
       </c>
       <c r="R91" t="n">
-        <v>6958518</v>
+        <v>6958445</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,6 +9664,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9693,7 +9698,7 @@
         <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9787,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708951</v>
+        <v>127702448</v>
       </c>
       <c r="B93" t="n">
-        <v>92628</v>
+        <v>91637</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581943</v>
+        <v>581480</v>
       </c>
       <c r="R93" t="n">
-        <v>6958445</v>
+        <v>6958518</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9863,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9892,7 +9892,7 @@
         <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B98" t="n">
-        <v>91338</v>
+        <v>91637</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R98" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B99" t="n">
-        <v>91634</v>
+        <v>91341</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10403,21 +10403,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R99" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
         <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127708946</v>
+        <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>91634</v>
+        <v>91542</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581559</v>
+        <v>581423</v>
       </c>
       <c r="R104" t="n">
-        <v>6958443</v>
+        <v>6958511</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708942</v>
+        <v>127700450</v>
       </c>
       <c r="B105" t="n">
-        <v>91634</v>
+        <v>57826</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,34 +10985,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581396</v>
+        <v>581789</v>
       </c>
       <c r="R105" t="n">
-        <v>6958454</v>
+        <v>6958477</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,32 +11076,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127702553</v>
+        <v>127708942</v>
       </c>
       <c r="B106" t="n">
-        <v>91539</v>
+        <v>91637</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581423</v>
+        <v>581396</v>
       </c>
       <c r="R106" t="n">
-        <v>6958511</v>
+        <v>6958454</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127700450</v>
+        <v>127708946</v>
       </c>
       <c r="B107" t="n">
-        <v>57823</v>
+        <v>91637</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11179,39 +11184,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581789</v>
+        <v>581559</v>
       </c>
       <c r="R107" t="n">
-        <v>6958477</v>
+        <v>6958443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708937</v>
+        <v>127708947</v>
       </c>
       <c r="B109" t="n">
-        <v>57663</v>
+        <v>91637</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581457</v>
+        <v>581574</v>
       </c>
       <c r="R109" t="n">
-        <v>6958514</v>
+        <v>6958443</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11438,11 +11438,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11469,10 +11464,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708947</v>
+        <v>127708912</v>
       </c>
       <c r="B110" t="n">
-        <v>91634</v>
+        <v>91341</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11480,21 +11475,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11504,10 +11499,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581574</v>
+        <v>581558</v>
       </c>
       <c r="R110" t="n">
-        <v>6958443</v>
+        <v>6958357</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11566,10 +11561,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B111" t="n">
-        <v>91338</v>
+        <v>57666</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11577,21 +11572,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11601,10 +11596,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R111" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11637,6 +11632,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11666,7 +11666,7 @@
         <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127702456</v>
+        <v>127703591</v>
       </c>
       <c r="B114" t="n">
-        <v>91338</v>
+        <v>91699</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581480</v>
+        <v>581485</v>
       </c>
       <c r="R114" t="n">
-        <v>6958518</v>
+        <v>6958325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11962,7 +11962,7 @@
         <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127708926</v>
+        <v>127702456</v>
       </c>
       <c r="B116" t="n">
-        <v>92035</v>
+        <v>91341</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581513</v>
+        <v>581480</v>
       </c>
       <c r="R116" t="n">
-        <v>6958336</v>
+        <v>6958518</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127703591</v>
+        <v>127708926</v>
       </c>
       <c r="B117" t="n">
-        <v>91696</v>
+        <v>92038</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2062</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581485</v>
+        <v>581513</v>
       </c>
       <c r="R117" t="n">
-        <v>6958325</v>
+        <v>6958336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12253,7 +12253,7 @@
         <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>127703413</v>
       </c>
       <c r="B119" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>127708930</v>
       </c>
       <c r="B120" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>127703745</v>
       </c>
       <c r="B122" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>127708950</v>
       </c>
       <c r="B124" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>127708909</v>
       </c>
       <c r="B125" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>127708959</v>
       </c>
       <c r="B126" t="n">
-        <v>92008</v>
+        <v>92011</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>127708939</v>
       </c>
       <c r="B127" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13240,50 +13240,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127701827</v>
+        <v>127708949</v>
       </c>
       <c r="B128" t="n">
-        <v>57663</v>
+        <v>98376</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581564</v>
+        <v>581598</v>
       </c>
       <c r="R128" t="n">
-        <v>6958463</v>
+        <v>6958396</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13316,11 +13311,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,10 +13337,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708949</v>
+        <v>127708927</v>
       </c>
       <c r="B129" t="n">
-        <v>98373</v>
+        <v>92038</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13358,21 +13348,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>3298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13382,10 +13372,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581598</v>
+        <v>581489</v>
       </c>
       <c r="R129" t="n">
-        <v>6958396</v>
+        <v>6958369</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13444,45 +13434,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708927</v>
+        <v>127701827</v>
       </c>
       <c r="B130" t="n">
-        <v>92035</v>
+        <v>57666</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581489</v>
+        <v>581564</v>
       </c>
       <c r="R130" t="n">
-        <v>6958369</v>
+        <v>6958463</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13515,6 +13510,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127702695</v>
+        <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>80123</v>
+        <v>91341</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581442</v>
+        <v>581433</v>
       </c>
       <c r="R131" t="n">
-        <v>6958493</v>
+        <v>6958423</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>91338</v>
+        <v>91637</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R132" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,10 +13735,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708943</v>
+        <v>127702695</v>
       </c>
       <c r="B133" t="n">
-        <v>91634</v>
+        <v>80126</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13746,21 +13746,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581472</v>
+        <v>581442</v>
       </c>
       <c r="R133" t="n">
-        <v>6958521</v>
+        <v>6958493</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13835,7 +13835,7 @@
         <v>127708952</v>
       </c>
       <c r="B134" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>127708934</v>
       </c>
       <c r="B135" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14033,6 +14033,103 @@
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>127701708</v>
+      </c>
+      <c r="B136" t="n">
+        <v>91707</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Dåvamyan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>581574</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6958447</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>127626319</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>127626360</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127626338</v>
       </c>
       <c r="B9" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>91645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R10" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B11" t="n">
-        <v>91637</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R11" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
         <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>127626332</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626289</v>
+        <v>127626323</v>
       </c>
       <c r="B15" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581425</v>
+        <v>581803</v>
       </c>
       <c r="R15" t="n">
-        <v>6958401</v>
+        <v>6958429</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B16" t="n">
-        <v>80126</v>
+        <v>91349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R16" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626323</v>
+        <v>127626348</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581803</v>
+        <v>582065</v>
       </c>
       <c r="R17" t="n">
-        <v>6958429</v>
+        <v>6958321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626336</v>
+        <v>127626321</v>
       </c>
       <c r="B18" t="n">
-        <v>80155</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582065</v>
+        <v>581718</v>
       </c>
       <c r="R18" t="n">
-        <v>6958323</v>
+        <v>6958467</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,6 +2393,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626321</v>
+        <v>127626285</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581718</v>
+        <v>581551</v>
       </c>
       <c r="R19" t="n">
-        <v>6958467</v>
+        <v>6958485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,32 +2521,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626285</v>
+        <v>127626336</v>
       </c>
       <c r="B20" t="n">
-        <v>91341</v>
+        <v>80161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581551</v>
+        <v>582065</v>
       </c>
       <c r="R20" t="n">
-        <v>6958485</v>
+        <v>6958323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626356</v>
+        <v>127626322</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581795</v>
+        <v>581761</v>
       </c>
       <c r="R21" t="n">
-        <v>6958432</v>
+        <v>6958462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626322</v>
+        <v>127626306</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581761</v>
+        <v>581878</v>
       </c>
       <c r="R22" t="n">
-        <v>6958462</v>
+        <v>6958484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626306</v>
+        <v>127626356</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581878</v>
+        <v>581795</v>
       </c>
       <c r="R23" t="n">
-        <v>6958484</v>
+        <v>6958432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,11 +2893,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R24" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,11 +2990,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,21 +3027,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R25" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,21 +3124,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R26" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,11 +3184,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,10 +3210,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626283</v>
+        <v>127626309</v>
       </c>
       <c r="B27" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,21 +3221,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3260,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582010</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6958445</v>
+        <v>6958478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,6 +3281,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3322,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B28" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3323,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R28" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,6 +3383,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3419,10 +3414,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B29" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3454,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R29" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3485,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3519,7 @@
         <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>127626302</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127626305</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>127626318</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>127626324</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>127626295</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626347</v>
+        <v>127626354</v>
       </c>
       <c r="B37" t="n">
-        <v>80154</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582104</v>
+        <v>582103</v>
       </c>
       <c r="R37" t="n">
-        <v>6958386</v>
+        <v>6958332</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,32 +4317,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626354</v>
+        <v>127626347</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>80160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582103</v>
+        <v>582104</v>
       </c>
       <c r="R38" t="n">
-        <v>6958332</v>
+        <v>6958386</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4417,7 +4417,7 @@
         <v>127626325</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>127626299</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>127626300</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626316</v>
+        <v>127626342</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>91645</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581480</v>
+        <v>581440</v>
       </c>
       <c r="R42" t="n">
-        <v>6958548</v>
+        <v>6958403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,7 +4820,7 @@
         <v>127626284</v>
       </c>
       <c r="B43" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,7 +4917,7 @@
         <v>127626350</v>
       </c>
       <c r="B44" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5016,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626342</v>
+        <v>127626297</v>
       </c>
       <c r="B45" t="n">
-        <v>91637</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5027,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5051,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581440</v>
+        <v>582085</v>
       </c>
       <c r="R45" t="n">
-        <v>6958403</v>
+        <v>6958383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,6 +5082,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5113,10 +5113,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626297</v>
+        <v>127626327</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582085</v>
+        <v>581824</v>
       </c>
       <c r="R46" t="n">
-        <v>6958383</v>
+        <v>6958505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626327</v>
+        <v>127626316</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581824</v>
+        <v>581480</v>
       </c>
       <c r="R47" t="n">
-        <v>6958505</v>
+        <v>6958548</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626351</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>91359</v>
+        <v>91645</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581501</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958530</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626282</v>
+        <v>127626296</v>
       </c>
       <c r="B49" t="n">
-        <v>91306</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581658</v>
+        <v>581882</v>
       </c>
       <c r="R49" t="n">
-        <v>6958442</v>
+        <v>6958519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,6 +5485,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5511,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B50" t="n">
-        <v>91637</v>
+        <v>91367</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5522,21 +5527,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R50" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5608,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626296</v>
+        <v>127626282</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>91314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581882</v>
+        <v>581658</v>
       </c>
       <c r="R51" t="n">
-        <v>6958519</v>
+        <v>6958442</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,11 +5684,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626329</v>
+        <v>127626303</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581831</v>
+        <v>582006</v>
       </c>
       <c r="R52" t="n">
-        <v>6958455</v>
+        <v>6958447</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626303</v>
+        <v>127626339</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>91645</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582006</v>
+        <v>581484</v>
       </c>
       <c r="R53" t="n">
-        <v>6958447</v>
+        <v>6958540</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,11 +5883,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5914,10 +5909,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626352</v>
+        <v>127620475</v>
       </c>
       <c r="B54" t="n">
-        <v>91359</v>
+        <v>91349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5925,34 +5920,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581490</v>
+        <v>581829</v>
       </c>
       <c r="R54" t="n">
-        <v>6958524</v>
+        <v>6958465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6011,10 +6006,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626339</v>
+        <v>127626352</v>
       </c>
       <c r="B55" t="n">
-        <v>91637</v>
+        <v>91367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,21 +6017,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6046,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581484</v>
+        <v>581490</v>
       </c>
       <c r="R55" t="n">
-        <v>6958540</v>
+        <v>6958524</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6111,7 +6106,7 @@
         <v>127626290</v>
       </c>
       <c r="B56" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6205,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127620475</v>
+        <v>127626329</v>
       </c>
       <c r="B57" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,34 +6211,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581829</v>
+        <v>581831</v>
       </c>
       <c r="R57" t="n">
-        <v>6958465</v>
+        <v>6958455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6276,6 +6271,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6305,7 +6305,7 @@
         <v>127626315</v>
       </c>
       <c r="B58" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B59" t="n">
-        <v>91341</v>
+        <v>91645</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R59" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B60" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R60" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
         <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127626301</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626357</v>
+        <v>127626328</v>
       </c>
       <c r="B66" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581828</v>
+        <v>581823</v>
       </c>
       <c r="R66" t="n">
-        <v>6958421</v>
+        <v>6958452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626328</v>
+        <v>127626286</v>
       </c>
       <c r="B67" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581823</v>
+        <v>581497</v>
       </c>
       <c r="R67" t="n">
-        <v>6958452</v>
+        <v>6958542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,11 +7271,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626286</v>
+        <v>127626357</v>
       </c>
       <c r="B68" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7313,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581497</v>
+        <v>581828</v>
       </c>
       <c r="R68" t="n">
-        <v>6958542</v>
+        <v>6958421</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,6 +7368,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7402,7 +7402,7 @@
         <v>127622082</v>
       </c>
       <c r="B69" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>127626326</v>
       </c>
       <c r="B70" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>127626307</v>
       </c>
       <c r="B71" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>127626341</v>
       </c>
       <c r="B73" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7903,10 +7903,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626304</v>
+        <v>127626288</v>
       </c>
       <c r="B74" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7914,21 +7914,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581961</v>
+        <v>581468</v>
       </c>
       <c r="R74" t="n">
-        <v>6958482</v>
+        <v>6958479</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7974,11 +7974,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8005,10 +8000,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626288</v>
+        <v>127626311</v>
       </c>
       <c r="B75" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8016,21 +8011,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8040,10 +8035,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581468</v>
+        <v>581684</v>
       </c>
       <c r="R75" t="n">
-        <v>6958479</v>
+        <v>6958471</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8076,6 +8071,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B76" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R76" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8207,7 +8207,7 @@
         <v>127626317</v>
       </c>
       <c r="B77" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92011</v>
+        <v>92019</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91542</v>
+        <v>91550</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127708940</v>
+        <v>127703408</v>
       </c>
       <c r="B82" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581551</v>
+        <v>581481</v>
       </c>
       <c r="R82" t="n">
-        <v>6958433</v>
+        <v>6958339</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8777,11 +8777,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8808,10 +8803,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127703408</v>
+        <v>127708919</v>
       </c>
       <c r="B83" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581481</v>
+        <v>581468</v>
       </c>
       <c r="R83" t="n">
-        <v>6958339</v>
+        <v>6958461</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8905,32 +8900,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708919</v>
+        <v>127708929</v>
       </c>
       <c r="B84" t="n">
-        <v>91341</v>
+        <v>92046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8940,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581468</v>
+        <v>581702</v>
       </c>
       <c r="R84" t="n">
-        <v>6958461</v>
+        <v>6958462</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9002,32 +8997,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127708953</v>
+        <v>127702065</v>
       </c>
       <c r="B85" t="n">
-        <v>88744</v>
+        <v>91759</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>4217</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9037,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581497</v>
+        <v>581516</v>
       </c>
       <c r="R85" t="n">
-        <v>6958369</v>
+        <v>6958469</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9099,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127702065</v>
+        <v>127708953</v>
       </c>
       <c r="B86" t="n">
-        <v>91751</v>
+        <v>88752</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>510</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9134,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581516</v>
+        <v>581497</v>
       </c>
       <c r="R86" t="n">
-        <v>6958469</v>
+        <v>6958369</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9196,45 +9191,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708929</v>
+        <v>127700444</v>
       </c>
       <c r="B87" t="n">
-        <v>92038</v>
+        <v>57832</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581702</v>
+        <v>581826</v>
       </c>
       <c r="R87" t="n">
-        <v>6958462</v>
+        <v>6958437</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9293,10 +9297,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B88" t="n">
-        <v>57826</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9304,43 +9308,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R88" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,6 +9368,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9402,7 +9402,7 @@
         <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9593,32 +9593,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708951</v>
+        <v>127702448</v>
       </c>
       <c r="B91" t="n">
-        <v>92631</v>
+        <v>91645</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581943</v>
+        <v>581480</v>
       </c>
       <c r="R91" t="n">
-        <v>6958445</v>
+        <v>6958518</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,11 +9664,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9695,32 +9690,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708921</v>
+        <v>127708951</v>
       </c>
       <c r="B92" t="n">
-        <v>91341</v>
+        <v>92639</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9730,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581549</v>
+        <v>581943</v>
       </c>
       <c r="R92" t="n">
-        <v>6958437</v>
+        <v>6958445</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9766,6 +9761,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9792,10 +9792,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127702448</v>
+        <v>127708921</v>
       </c>
       <c r="B93" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9803,21 +9803,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581480</v>
+        <v>581549</v>
       </c>
       <c r="R93" t="n">
-        <v>6958518</v>
+        <v>6958437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9892,7 +9892,7 @@
         <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127708944</v>
+        <v>127708917</v>
       </c>
       <c r="B95" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,21 +10002,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581469</v>
+        <v>581459</v>
       </c>
       <c r="R95" t="n">
-        <v>6958479</v>
+        <v>6958547</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708917</v>
+        <v>127708944</v>
       </c>
       <c r="B96" t="n">
-        <v>91341</v>
+        <v>91645</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,21 +10099,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581459</v>
+        <v>581469</v>
       </c>
       <c r="R96" t="n">
-        <v>6958547</v>
+        <v>6958479</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10188,7 +10188,7 @@
         <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B98" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R98" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127708916</v>
+        <v>127701709</v>
       </c>
       <c r="B99" t="n">
-        <v>91341</v>
+        <v>92046</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581451</v>
+        <v>581590</v>
       </c>
       <c r="R99" t="n">
-        <v>6958466</v>
+        <v>6958438</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127701709</v>
+        <v>127708945</v>
       </c>
       <c r="B100" t="n">
-        <v>92038</v>
+        <v>91645</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581590</v>
+        <v>581512</v>
       </c>
       <c r="R100" t="n">
-        <v>6958438</v>
+        <v>6958472</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>91542</v>
+        <v>91550</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127700450</v>
+        <v>127708946</v>
       </c>
       <c r="B105" t="n">
-        <v>57826</v>
+        <v>91645</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,39 +10985,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581789</v>
+        <v>581559</v>
       </c>
       <c r="R105" t="n">
-        <v>6958477</v>
+        <v>6958443</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11079,7 +11074,7 @@
         <v>127708942</v>
       </c>
       <c r="B106" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127708946</v>
+        <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>91637</v>
+        <v>57832</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11184,34 +11179,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581559</v>
+        <v>581789</v>
       </c>
       <c r="R107" t="n">
-        <v>6958443</v>
+        <v>6958477</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708947</v>
+        <v>127708912</v>
       </c>
       <c r="B109" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581574</v>
+        <v>581558</v>
       </c>
       <c r="R109" t="n">
-        <v>6958443</v>
+        <v>6958357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708912</v>
+        <v>127708947</v>
       </c>
       <c r="B110" t="n">
-        <v>91341</v>
+        <v>91645</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581558</v>
+        <v>581574</v>
       </c>
       <c r="R110" t="n">
-        <v>6958357</v>
+        <v>6958443</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11564,7 +11564,7 @@
         <v>127708937</v>
       </c>
       <c r="B111" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>127703591</v>
       </c>
       <c r="B114" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708941</v>
+        <v>127702456</v>
       </c>
       <c r="B115" t="n">
-        <v>91637</v>
+        <v>91349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11970,21 +11970,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581486</v>
+        <v>581480</v>
       </c>
       <c r="R115" t="n">
-        <v>6958333</v>
+        <v>6958518</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127702456</v>
+        <v>127708926</v>
       </c>
       <c r="B116" t="n">
-        <v>91341</v>
+        <v>92046</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581480</v>
+        <v>581513</v>
       </c>
       <c r="R116" t="n">
-        <v>6958518</v>
+        <v>6958336</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127708926</v>
+        <v>127708941</v>
       </c>
       <c r="B117" t="n">
-        <v>92038</v>
+        <v>91645</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581513</v>
+        <v>581486</v>
       </c>
       <c r="R117" t="n">
-        <v>6958336</v>
+        <v>6958333</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B118" t="n">
-        <v>91341</v>
+        <v>57832</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R118" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12347,10 +12352,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B119" t="n">
-        <v>57826</v>
+        <v>91349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12358,39 +12363,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R119" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12452,7 +12452,7 @@
         <v>127708930</v>
       </c>
       <c r="B120" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>127703745</v>
       </c>
       <c r="B122" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12847,32 +12847,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127708950</v>
+        <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>98376</v>
+        <v>91349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>581502</v>
+        <v>581606</v>
       </c>
       <c r="R124" t="n">
-        <v>6958332</v>
+        <v>6958438</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12944,32 +12944,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127708909</v>
+        <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>91341</v>
+        <v>98384</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>581606</v>
+        <v>581502</v>
       </c>
       <c r="R125" t="n">
-        <v>6958438</v>
+        <v>6958332</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13041,32 +13041,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708959</v>
+        <v>127708927</v>
       </c>
       <c r="B126" t="n">
-        <v>92011</v>
+        <v>92046</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>898</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581595</v>
+        <v>581489</v>
       </c>
       <c r="R126" t="n">
-        <v>6958389</v>
+        <v>6958369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13138,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708939</v>
+        <v>127708959</v>
       </c>
       <c r="B127" t="n">
-        <v>57666</v>
+        <v>92019</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581490</v>
+        <v>581595</v>
       </c>
       <c r="R127" t="n">
-        <v>6958459</v>
+        <v>6958389</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13209,11 +13209,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13240,45 +13235,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708949</v>
+        <v>127701827</v>
       </c>
       <c r="B128" t="n">
-        <v>98376</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581598</v>
+        <v>581564</v>
       </c>
       <c r="R128" t="n">
-        <v>6958396</v>
+        <v>6958463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13311,6 +13311,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13337,32 +13342,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708927</v>
+        <v>127708939</v>
       </c>
       <c r="B129" t="n">
-        <v>92038</v>
+        <v>57672</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13372,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581489</v>
+        <v>581490</v>
       </c>
       <c r="R129" t="n">
-        <v>6958369</v>
+        <v>6958459</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13408,6 +13413,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13434,50 +13444,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127701827</v>
+        <v>127708949</v>
       </c>
       <c r="B130" t="n">
-        <v>57666</v>
+        <v>98384</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581564</v>
+        <v>581598</v>
       </c>
       <c r="R130" t="n">
-        <v>6958463</v>
+        <v>6958396</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13510,11 +13515,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13544,7 +13544,7 @@
         <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13638,32 +13638,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708943</v>
+        <v>127708952</v>
       </c>
       <c r="B132" t="n">
-        <v>91637</v>
+        <v>92639</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581472</v>
+        <v>581959</v>
       </c>
       <c r="R132" t="n">
-        <v>6958521</v>
+        <v>6958445</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,10 +13735,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127702695</v>
+        <v>127708943</v>
       </c>
       <c r="B133" t="n">
-        <v>80126</v>
+        <v>91645</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13746,21 +13746,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581442</v>
+        <v>581472</v>
       </c>
       <c r="R133" t="n">
-        <v>6958493</v>
+        <v>6958521</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13832,32 +13832,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127708952</v>
+        <v>127702695</v>
       </c>
       <c r="B134" t="n">
-        <v>92631</v>
+        <v>80132</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13867,10 +13867,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>581959</v>
+        <v>581442</v>
       </c>
       <c r="R134" t="n">
-        <v>6958445</v>
+        <v>6958493</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13932,7 +13932,7 @@
         <v>127708934</v>
       </c>
       <c r="B135" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R7" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1306,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626360</v>
+        <v>127626338</v>
       </c>
       <c r="B8" t="n">
-        <v>98384</v>
+        <v>91646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581836</v>
+        <v>581544</v>
       </c>
       <c r="R8" t="n">
-        <v>6958416</v>
+        <v>6958500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626338</v>
+        <v>127626319</v>
       </c>
       <c r="B9" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581544</v>
+        <v>581409</v>
       </c>
       <c r="R9" t="n">
-        <v>6958500</v>
+        <v>6958406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626344</v>
+        <v>127626320</v>
       </c>
       <c r="B10" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581534</v>
+        <v>581658</v>
       </c>
       <c r="R10" t="n">
-        <v>6958399</v>
+        <v>6958452</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R11" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626320</v>
+        <v>127626355</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581658</v>
+        <v>581582</v>
       </c>
       <c r="R12" t="n">
-        <v>6958452</v>
+        <v>6958488</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B13" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R13" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R14" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626323</v>
+        <v>127626348</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581803</v>
+        <v>582065</v>
       </c>
       <c r="R15" t="n">
-        <v>6958429</v>
+        <v>6958321</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2097,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,7 +2126,7 @@
         <v>127626289</v>
       </c>
       <c r="B16" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626348</v>
+        <v>127626323</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582065</v>
+        <v>581803</v>
       </c>
       <c r="R17" t="n">
-        <v>6958321</v>
+        <v>6958429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626321</v>
+        <v>127626336</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581718</v>
+        <v>582065</v>
       </c>
       <c r="R18" t="n">
-        <v>6958467</v>
+        <v>6958323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626285</v>
+        <v>127626321</v>
       </c>
       <c r="B19" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581551</v>
+        <v>581718</v>
       </c>
       <c r="R19" t="n">
-        <v>6958485</v>
+        <v>6958467</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,32 +2521,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626336</v>
+        <v>127626285</v>
       </c>
       <c r="B20" t="n">
-        <v>80161</v>
+        <v>91350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582065</v>
+        <v>581551</v>
       </c>
       <c r="R20" t="n">
-        <v>6958323</v>
+        <v>6958485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
         <v>127626283</v>
       </c>
       <c r="B24" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>127626291</v>
       </c>
       <c r="B26" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626340</v>
+        <v>127626302</v>
       </c>
       <c r="B30" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581474</v>
+        <v>582050</v>
       </c>
       <c r="R30" t="n">
-        <v>6958474</v>
+        <v>6958390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3587,6 +3587,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3613,7 +3618,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626302</v>
+        <v>127626305</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3648,10 +3653,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582050</v>
+        <v>581928</v>
       </c>
       <c r="R31" t="n">
-        <v>6958390</v>
+        <v>6958485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626305</v>
+        <v>127626318</v>
       </c>
       <c r="B32" t="n">
         <v>57672</v>
@@ -3750,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581928</v>
+        <v>581380</v>
       </c>
       <c r="R32" t="n">
-        <v>6958485</v>
+        <v>6958472</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,7 +3795,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,7 +3822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626318</v>
+        <v>127626324</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -3852,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581380</v>
+        <v>581807</v>
       </c>
       <c r="R33" t="n">
-        <v>6958472</v>
+        <v>6958490</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3897,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,7 +3924,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626324</v>
+        <v>127626295</v>
       </c>
       <c r="B34" t="n">
         <v>57672</v>
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581807</v>
+        <v>581885</v>
       </c>
       <c r="R34" t="n">
-        <v>6958490</v>
+        <v>6958529</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,7 +3999,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,10 +4026,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626295</v>
+        <v>127626340</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4037,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4061,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581885</v>
+        <v>581474</v>
       </c>
       <c r="R35" t="n">
-        <v>6958529</v>
+        <v>6958474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,11 +4097,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127626292</v>
+        <v>127626325</v>
       </c>
       <c r="B36" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581696</v>
+        <v>581819</v>
       </c>
       <c r="R36" t="n">
-        <v>6958457</v>
+        <v>6958488</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4194,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4220,10 +4225,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626354</v>
+        <v>127626299</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4231,21 +4236,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582103</v>
+        <v>582073</v>
       </c>
       <c r="R37" t="n">
-        <v>6958332</v>
+        <v>6958325</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,6 +4296,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4317,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626347</v>
+        <v>127626300</v>
       </c>
       <c r="B38" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582104</v>
+        <v>582063</v>
       </c>
       <c r="R38" t="n">
-        <v>6958386</v>
+        <v>6958321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,6 +4398,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4414,10 +4429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626325</v>
+        <v>127626292</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4425,21 +4440,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4449,10 +4464,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581819</v>
+        <v>581696</v>
       </c>
       <c r="R39" t="n">
-        <v>6958488</v>
+        <v>6958457</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4485,11 +4500,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,32 +4526,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626299</v>
+        <v>127626347</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4561,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582073</v>
+        <v>582104</v>
       </c>
       <c r="R40" t="n">
-        <v>6958325</v>
+        <v>6958386</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4597,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4623,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626300</v>
+        <v>127626354</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4634,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4658,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582063</v>
+        <v>582103</v>
       </c>
       <c r="R41" t="n">
-        <v>6958321</v>
+        <v>6958332</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,11 +4694,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626342</v>
+        <v>127626284</v>
       </c>
       <c r="B42" t="n">
-        <v>91645</v>
+        <v>91350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581440</v>
+        <v>581922</v>
       </c>
       <c r="R42" t="n">
-        <v>6958403</v>
+        <v>6958467</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626284</v>
+        <v>127626297</v>
       </c>
       <c r="B43" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581922</v>
+        <v>582085</v>
       </c>
       <c r="R43" t="n">
-        <v>6958467</v>
+        <v>6958383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4914,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626350</v>
+        <v>127626327</v>
       </c>
       <c r="B44" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4930,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581948</v>
+        <v>581824</v>
       </c>
       <c r="R44" t="n">
-        <v>6958486</v>
+        <v>6958505</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4990,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,7 +5021,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626297</v>
+        <v>127626316</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5046,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582085</v>
+        <v>581480</v>
       </c>
       <c r="R45" t="n">
-        <v>6958383</v>
+        <v>6958548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,10 +5123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626327</v>
+        <v>127626342</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5124,21 +5134,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581824</v>
+        <v>581440</v>
       </c>
       <c r="R46" t="n">
-        <v>6958505</v>
+        <v>6958403</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,11 +5194,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5215,10 +5220,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626316</v>
+        <v>127626350</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5226,21 +5231,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5250,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581480</v>
+        <v>581948</v>
       </c>
       <c r="R47" t="n">
-        <v>6958548</v>
+        <v>6958486</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,11 +5291,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626345</v>
+        <v>127626296</v>
       </c>
       <c r="B48" t="n">
-        <v>91645</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581775</v>
+        <v>581882</v>
       </c>
       <c r="R48" t="n">
-        <v>6958475</v>
+        <v>6958519</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5388,6 +5388,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5414,10 +5419,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626296</v>
+        <v>127626345</v>
       </c>
       <c r="B49" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5425,21 +5430,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581882</v>
+        <v>581775</v>
       </c>
       <c r="R49" t="n">
-        <v>6958519</v>
+        <v>6958475</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,11 +5490,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5519,7 +5519,7 @@
         <v>127626351</v>
       </c>
       <c r="B50" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>127626282</v>
       </c>
       <c r="B51" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626303</v>
+        <v>127626339</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>582006</v>
+        <v>581484</v>
       </c>
       <c r="R52" t="n">
-        <v>6958447</v>
+        <v>6958540</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,11 +5781,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626339</v>
+        <v>127626352</v>
       </c>
       <c r="B53" t="n">
-        <v>91645</v>
+        <v>91368</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581484</v>
+        <v>581490</v>
       </c>
       <c r="R53" t="n">
-        <v>6958540</v>
+        <v>6958524</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5909,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127620475</v>
+        <v>127626290</v>
       </c>
       <c r="B54" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5940,14 +5935,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581829</v>
+        <v>581438</v>
       </c>
       <c r="R54" t="n">
-        <v>6958465</v>
+        <v>6958399</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6006,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626352</v>
+        <v>127620475</v>
       </c>
       <c r="B55" t="n">
-        <v>91367</v>
+        <v>91350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,34 +6012,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581490</v>
+        <v>581829</v>
       </c>
       <c r="R55" t="n">
-        <v>6958524</v>
+        <v>6958465</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626290</v>
+        <v>127626329</v>
       </c>
       <c r="B56" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,21 +6109,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6138,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581438</v>
+        <v>581831</v>
       </c>
       <c r="R56" t="n">
-        <v>6958399</v>
+        <v>6958455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6174,6 +6169,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6200,7 +6200,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626329</v>
+        <v>127626303</v>
       </c>
       <c r="B57" t="n">
         <v>57672</v>
@@ -6235,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581831</v>
+        <v>582006</v>
       </c>
       <c r="R57" t="n">
-        <v>6958455</v>
+        <v>6958447</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6407,7 +6407,7 @@
         <v>127626343</v>
       </c>
       <c r="B59" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>127626294</v>
       </c>
       <c r="B60" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R63" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6899,7 +6894,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626301</v>
+        <v>127626298</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -6934,10 +6929,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582037</v>
+        <v>582124</v>
       </c>
       <c r="R64" t="n">
-        <v>6958341</v>
+        <v>6958327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7001,32 +6996,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626358</v>
+        <v>127626301</v>
       </c>
       <c r="B65" t="n">
-        <v>98384</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7031,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582087</v>
+        <v>582037</v>
       </c>
       <c r="R65" t="n">
-        <v>6958421</v>
+        <v>6958341</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,6 +7067,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626328</v>
+        <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581823</v>
+        <v>581497</v>
       </c>
       <c r="R66" t="n">
-        <v>6958452</v>
+        <v>6958542</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,11 +7169,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B67" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R67" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7266,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626341</v>
+        <v>127626288</v>
       </c>
       <c r="B73" t="n">
-        <v>91645</v>
+        <v>91350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581425</v>
+        <v>581468</v>
       </c>
       <c r="R73" t="n">
-        <v>6958396</v>
+        <v>6958479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,10 +7903,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626288</v>
+        <v>127626311</v>
       </c>
       <c r="B74" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7914,21 +7914,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581468</v>
+        <v>581684</v>
       </c>
       <c r="R74" t="n">
-        <v>6958479</v>
+        <v>6958471</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7974,6 +7974,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8000,7 +8005,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8035,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R75" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8075,7 +8080,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8102,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626304</v>
+        <v>127626341</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8113,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8137,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581961</v>
+        <v>581425</v>
       </c>
       <c r="R76" t="n">
-        <v>6958482</v>
+        <v>6958396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8173,11 +8178,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92019</v>
+        <v>92020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91550</v>
+        <v>91551</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127703408</v>
+        <v>127708953</v>
       </c>
       <c r="B82" t="n">
-        <v>91349</v>
+        <v>88753</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581481</v>
+        <v>581497</v>
       </c>
       <c r="R82" t="n">
-        <v>6958339</v>
+        <v>6958369</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708919</v>
+        <v>127708929</v>
       </c>
       <c r="B83" t="n">
-        <v>91349</v>
+        <v>92047</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581468</v>
+        <v>581702</v>
       </c>
       <c r="R83" t="n">
-        <v>6958461</v>
+        <v>6958462</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708929</v>
+        <v>127702065</v>
       </c>
       <c r="B84" t="n">
-        <v>92046</v>
+        <v>91760</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3298</v>
+        <v>4217</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581702</v>
+        <v>581516</v>
       </c>
       <c r="R84" t="n">
-        <v>6958462</v>
+        <v>6958469</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,32 +8997,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127702065</v>
+        <v>127703408</v>
       </c>
       <c r="B85" t="n">
-        <v>91759</v>
+        <v>91350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581516</v>
+        <v>581481</v>
       </c>
       <c r="R85" t="n">
-        <v>6958469</v>
+        <v>6958339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,10 +9094,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708953</v>
+        <v>127708919</v>
       </c>
       <c r="B86" t="n">
-        <v>88752</v>
+        <v>91350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9105,21 +9105,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581497</v>
+        <v>581468</v>
       </c>
       <c r="R86" t="n">
-        <v>6958369</v>
+        <v>6958461</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B87" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9202,43 +9202,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R87" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9271,6 +9262,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9297,10 +9293,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127708940</v>
+        <v>127700444</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9308,34 +9304,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581551</v>
+        <v>581826</v>
       </c>
       <c r="R88" t="n">
-        <v>6958433</v>
+        <v>6958437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9368,11 +9373,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9402,7 +9402,7 @@
         <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>127702448</v>
       </c>
       <c r="B91" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>127708951</v>
       </c>
       <c r="B92" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9792,10 +9792,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708921</v>
+        <v>127708935</v>
       </c>
       <c r="B93" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9803,21 +9803,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581549</v>
+        <v>581452</v>
       </c>
       <c r="R93" t="n">
-        <v>6958437</v>
+        <v>6958446</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,6 +9863,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,10 +9894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708935</v>
+        <v>127708921</v>
       </c>
       <c r="B94" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9900,21 +9905,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581452</v>
+        <v>581549</v>
       </c>
       <c r="R94" t="n">
-        <v>6958446</v>
+        <v>6958437</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9960,11 +9965,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127708917</v>
+        <v>127700375</v>
       </c>
       <c r="B95" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,34 +10002,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581459</v>
+        <v>581797</v>
       </c>
       <c r="R95" t="n">
-        <v>6958547</v>
+        <v>6958452</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10062,6 +10070,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10088,10 +10101,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708944</v>
+        <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91645</v>
+        <v>91350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,21 +10112,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10123,10 +10136,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581469</v>
+        <v>581459</v>
       </c>
       <c r="R96" t="n">
-        <v>6958479</v>
+        <v>6958547</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10185,10 +10198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127700375</v>
+        <v>127708944</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10196,42 +10209,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581797</v>
+        <v>581469</v>
       </c>
       <c r="R97" t="n">
-        <v>6958452</v>
+        <v>6958479</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10264,11 +10269,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10295,45 +10295,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708916</v>
+        <v>127701709</v>
       </c>
       <c r="B98" t="n">
-        <v>91349</v>
+        <v>92047</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581451</v>
+        <v>581590</v>
       </c>
       <c r="R98" t="n">
-        <v>6958466</v>
+        <v>6958438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127701709</v>
+        <v>127708916</v>
       </c>
       <c r="B99" t="n">
-        <v>92046</v>
+        <v>91350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581590</v>
+        <v>581451</v>
       </c>
       <c r="R99" t="n">
-        <v>6958438</v>
+        <v>6958466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
         <v>127708945</v>
       </c>
       <c r="B100" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10586,32 +10586,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127708915</v>
+        <v>127708924</v>
       </c>
       <c r="B101" t="n">
-        <v>91349</v>
+        <v>92047</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>581387</v>
+        <v>581607</v>
       </c>
       <c r="R101" t="n">
-        <v>6958453</v>
+        <v>6958406</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10683,10 +10683,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127708920</v>
+        <v>127708915</v>
       </c>
       <c r="B102" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>581517</v>
+        <v>581387</v>
       </c>
       <c r="R102" t="n">
-        <v>6958471</v>
+        <v>6958453</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127708924</v>
+        <v>127708920</v>
       </c>
       <c r="B103" t="n">
-        <v>92046</v>
+        <v>91350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>581607</v>
+        <v>581517</v>
       </c>
       <c r="R103" t="n">
-        <v>6958406</v>
+        <v>6958471</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127702553</v>
+        <v>127708942</v>
       </c>
       <c r="B104" t="n">
-        <v>91550</v>
+        <v>91646</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581423</v>
+        <v>581396</v>
       </c>
       <c r="R104" t="n">
-        <v>6958511</v>
+        <v>6958454</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10977,7 +10977,7 @@
         <v>127708946</v>
       </c>
       <c r="B105" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708942</v>
+        <v>127702553</v>
       </c>
       <c r="B106" t="n">
-        <v>91645</v>
+        <v>91551</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581396</v>
+        <v>581423</v>
       </c>
       <c r="R106" t="n">
-        <v>6958454</v>
+        <v>6958511</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708912</v>
+        <v>127708947</v>
       </c>
       <c r="B109" t="n">
-        <v>91349</v>
+        <v>91646</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581558</v>
+        <v>581574</v>
       </c>
       <c r="R109" t="n">
-        <v>6958357</v>
+        <v>6958443</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708947</v>
+        <v>127708912</v>
       </c>
       <c r="B110" t="n">
-        <v>91645</v>
+        <v>91350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581574</v>
+        <v>581558</v>
       </c>
       <c r="R110" t="n">
-        <v>6958443</v>
+        <v>6958357</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B112" t="n">
-        <v>91349</v>
+        <v>57672</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R112" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,6 +11734,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11760,10 +11765,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11771,21 +11776,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11795,10 +11800,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R113" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11831,11 +11836,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127703591</v>
+        <v>127708941</v>
       </c>
       <c r="B114" t="n">
-        <v>91707</v>
+        <v>91646</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581485</v>
+        <v>581486</v>
       </c>
       <c r="R114" t="n">
-        <v>6958325</v>
+        <v>6958333</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11962,7 +11962,7 @@
         <v>127702456</v>
       </c>
       <c r="B115" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127708926</v>
+        <v>127703591</v>
       </c>
       <c r="B116" t="n">
-        <v>92046</v>
+        <v>91708</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581513</v>
+        <v>581485</v>
       </c>
       <c r="R116" t="n">
-        <v>6958336</v>
+        <v>6958325</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127708941</v>
+        <v>127708926</v>
       </c>
       <c r="B117" t="n">
-        <v>91645</v>
+        <v>92047</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581486</v>
+        <v>581513</v>
       </c>
       <c r="R117" t="n">
-        <v>6958333</v>
+        <v>6958336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>57832</v>
+        <v>91350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R118" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,10 +12347,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B119" t="n">
-        <v>91349</v>
+        <v>57832</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12363,34 +12358,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R119" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12847,32 +12847,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127708909</v>
+        <v>127708950</v>
       </c>
       <c r="B124" t="n">
-        <v>91349</v>
+        <v>98385</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>581606</v>
+        <v>581502</v>
       </c>
       <c r="R124" t="n">
-        <v>6958438</v>
+        <v>6958332</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12944,32 +12944,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127708950</v>
+        <v>127708909</v>
       </c>
       <c r="B125" t="n">
-        <v>98384</v>
+        <v>91350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>581502</v>
+        <v>581606</v>
       </c>
       <c r="R125" t="n">
-        <v>6958332</v>
+        <v>6958438</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13041,32 +13041,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708927</v>
+        <v>127708959</v>
       </c>
       <c r="B126" t="n">
-        <v>92046</v>
+        <v>92020</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>898</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581489</v>
+        <v>581595</v>
       </c>
       <c r="R126" t="n">
-        <v>6958369</v>
+        <v>6958389</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13138,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708959</v>
+        <v>127708939</v>
       </c>
       <c r="B127" t="n">
-        <v>92019</v>
+        <v>57672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581595</v>
+        <v>581490</v>
       </c>
       <c r="R127" t="n">
-        <v>6958389</v>
+        <v>6958459</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13209,6 +13209,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13342,32 +13347,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708939</v>
+        <v>127708927</v>
       </c>
       <c r="B129" t="n">
-        <v>57672</v>
+        <v>92047</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581490</v>
+        <v>581489</v>
       </c>
       <c r="R129" t="n">
-        <v>6958459</v>
+        <v>6958369</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13413,11 +13418,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13447,7 +13447,7 @@
         <v>127708949</v>
       </c>
       <c r="B130" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B131" t="n">
-        <v>91349</v>
+        <v>91646</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R131" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13641,7 +13641,7 @@
         <v>127708952</v>
       </c>
       <c r="B132" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13735,10 +13735,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B133" t="n">
-        <v>91645</v>
+        <v>91350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13746,21 +13746,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R133" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626360</v>
+        <v>127626319</v>
       </c>
       <c r="B7" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581836</v>
+        <v>581409</v>
       </c>
       <c r="R7" t="n">
-        <v>6958416</v>
+        <v>6958406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1306,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R9" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626320</v>
+        <v>127626355</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581658</v>
+        <v>581582</v>
       </c>
       <c r="R10" t="n">
-        <v>6958452</v>
+        <v>6958488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127626355</v>
+        <v>127626320</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581582</v>
+        <v>581658</v>
       </c>
       <c r="R12" t="n">
-        <v>6958488</v>
+        <v>6958452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R13" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R14" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +1995,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626283</v>
+        <v>127626309</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582010</v>
+        <v>581870</v>
       </c>
       <c r="R24" t="n">
-        <v>6958445</v>
+        <v>6958478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,6 +2990,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3016,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,21 +3032,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R25" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,6 +3092,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B26" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,21 +3134,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3148,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R26" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,6 +3194,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3210,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,21 +3236,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3245,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R27" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,11 +3296,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3312,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R28" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,11 +3393,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,10 +3419,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,21 +3430,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R29" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,11 +3490,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3516,10 +3516,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127626302</v>
+        <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582050</v>
+        <v>581474</v>
       </c>
       <c r="R30" t="n">
-        <v>6958390</v>
+        <v>6958474</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3587,11 +3587,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,7 +3613,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626305</v>
+        <v>127626302</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3653,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581928</v>
+        <v>582050</v>
       </c>
       <c r="R31" t="n">
-        <v>6958485</v>
+        <v>6958390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626318</v>
+        <v>127626305</v>
       </c>
       <c r="B32" t="n">
         <v>57672</v>
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581380</v>
+        <v>581928</v>
       </c>
       <c r="R32" t="n">
-        <v>6958472</v>
+        <v>6958485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3795,7 +3790,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626324</v>
+        <v>127626318</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -3857,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581807</v>
+        <v>581380</v>
       </c>
       <c r="R33" t="n">
-        <v>6958490</v>
+        <v>6958472</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3924,7 +3919,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626295</v>
+        <v>127626324</v>
       </c>
       <c r="B34" t="n">
         <v>57672</v>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581885</v>
+        <v>581807</v>
       </c>
       <c r="R34" t="n">
-        <v>6958529</v>
+        <v>6958490</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4026,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626340</v>
+        <v>127626295</v>
       </c>
       <c r="B35" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4037,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4061,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581474</v>
+        <v>581885</v>
       </c>
       <c r="R35" t="n">
-        <v>6958474</v>
+        <v>6958529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,6 +4092,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127626325</v>
+        <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581819</v>
+        <v>581696</v>
       </c>
       <c r="R36" t="n">
-        <v>6958488</v>
+        <v>6958457</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4225,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626299</v>
+        <v>127626347</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4260,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582073</v>
+        <v>582104</v>
       </c>
       <c r="R37" t="n">
-        <v>6958325</v>
+        <v>6958386</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,11 +4291,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4327,7 +4317,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626300</v>
+        <v>127626325</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4362,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582063</v>
+        <v>581819</v>
       </c>
       <c r="R38" t="n">
-        <v>6958321</v>
+        <v>6958488</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626292</v>
+        <v>127626299</v>
       </c>
       <c r="B39" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4440,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4464,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581696</v>
+        <v>582073</v>
       </c>
       <c r="R39" t="n">
-        <v>6958457</v>
+        <v>6958325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4500,6 +4490,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4526,32 +4521,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626347</v>
+        <v>127626300</v>
       </c>
       <c r="B40" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4561,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582104</v>
+        <v>582063</v>
       </c>
       <c r="R40" t="n">
-        <v>6958386</v>
+        <v>6958321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4597,6 +4592,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626284</v>
+        <v>127626297</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581922</v>
+        <v>582085</v>
       </c>
       <c r="R42" t="n">
-        <v>6958467</v>
+        <v>6958383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,6 +4791,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4817,7 +4822,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626297</v>
+        <v>127626327</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -4852,10 +4857,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582085</v>
+        <v>581824</v>
       </c>
       <c r="R43" t="n">
-        <v>6958383</v>
+        <v>6958505</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4919,7 +4924,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626327</v>
+        <v>127626316</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581824</v>
+        <v>581480</v>
       </c>
       <c r="R44" t="n">
-        <v>6958505</v>
+        <v>6958548</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5021,10 +5026,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626316</v>
+        <v>127626342</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5032,21 +5037,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5056,10 +5061,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581480</v>
+        <v>581440</v>
       </c>
       <c r="R45" t="n">
-        <v>6958548</v>
+        <v>6958403</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5092,11 +5097,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5123,10 +5123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626342</v>
+        <v>127626284</v>
       </c>
       <c r="B46" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,21 +5134,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581440</v>
+        <v>581922</v>
       </c>
       <c r="R46" t="n">
-        <v>6958403</v>
+        <v>6958467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91646</v>
+        <v>91368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5430,21 +5430,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R49" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>91368</v>
+        <v>91315</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R50" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5613,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626282</v>
+        <v>127626345</v>
       </c>
       <c r="B51" t="n">
-        <v>91315</v>
+        <v>91646</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581658</v>
+        <v>581775</v>
       </c>
       <c r="R51" t="n">
-        <v>6958442</v>
+        <v>6958475</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626339</v>
+        <v>127626329</v>
       </c>
       <c r="B52" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581484</v>
+        <v>581831</v>
       </c>
       <c r="R52" t="n">
-        <v>6958540</v>
+        <v>6958455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,6 +5781,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5807,10 +5812,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626352</v>
+        <v>127626303</v>
       </c>
       <c r="B53" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5823,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581490</v>
+        <v>582006</v>
       </c>
       <c r="R53" t="n">
-        <v>6958524</v>
+        <v>6958447</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5883,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6098,10 +6108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626329</v>
+        <v>127626352</v>
       </c>
       <c r="B56" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6109,21 +6119,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6143,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581831</v>
+        <v>581490</v>
       </c>
       <c r="R56" t="n">
-        <v>6958455</v>
+        <v>6958524</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6169,11 +6179,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6200,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626303</v>
+        <v>127626339</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6216,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6240,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582006</v>
+        <v>581484</v>
       </c>
       <c r="R57" t="n">
-        <v>6958447</v>
+        <v>6958540</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,11 +6276,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B59" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R59" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B60" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R60" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B61" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R61" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,6 +6669,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6695,10 +6700,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6706,21 +6711,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6730,10 +6735,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R62" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,11 +6771,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626358</v>
+        <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582087</v>
+        <v>582124</v>
       </c>
       <c r="R63" t="n">
-        <v>6958421</v>
+        <v>6958327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,7 +6899,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626298</v>
+        <v>127626301</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -6929,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582124</v>
+        <v>582037</v>
       </c>
       <c r="R64" t="n">
-        <v>6958327</v>
+        <v>6958341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6996,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626301</v>
+        <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7031,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582037</v>
+        <v>582087</v>
       </c>
       <c r="R65" t="n">
-        <v>6958341</v>
+        <v>6958421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7067,11 +7072,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B66" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R66" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,6 +7169,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7195,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626328</v>
+        <v>127626286</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581823</v>
+        <v>581497</v>
       </c>
       <c r="R67" t="n">
-        <v>6958452</v>
+        <v>6958542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,11 +7271,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127708953</v>
+        <v>127703408</v>
       </c>
       <c r="B82" t="n">
-        <v>88753</v>
+        <v>91350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581497</v>
+        <v>581481</v>
       </c>
       <c r="R82" t="n">
-        <v>6958369</v>
+        <v>6958339</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708929</v>
+        <v>127708919</v>
       </c>
       <c r="B83" t="n">
-        <v>92047</v>
+        <v>91350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581702</v>
+        <v>581468</v>
       </c>
       <c r="R83" t="n">
-        <v>6958462</v>
+        <v>6958461</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127702065</v>
+        <v>127708953</v>
       </c>
       <c r="B84" t="n">
-        <v>91760</v>
+        <v>88753</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4217</v>
+        <v>510</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581516</v>
+        <v>581497</v>
       </c>
       <c r="R84" t="n">
-        <v>6958469</v>
+        <v>6958369</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127703408</v>
+        <v>127700444</v>
       </c>
       <c r="B85" t="n">
-        <v>91350</v>
+        <v>57832</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9008,34 +9008,43 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581481</v>
+        <v>581826</v>
       </c>
       <c r="R85" t="n">
-        <v>6958339</v>
+        <v>6958437</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,32 +9103,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708919</v>
+        <v>127708929</v>
       </c>
       <c r="B86" t="n">
-        <v>91350</v>
+        <v>92047</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9138,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581468</v>
+        <v>581702</v>
       </c>
       <c r="R86" t="n">
-        <v>6958461</v>
+        <v>6958462</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9191,32 +9200,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708940</v>
+        <v>127702065</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>91760</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9226,10 +9235,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581551</v>
+        <v>581516</v>
       </c>
       <c r="R87" t="n">
-        <v>6958433</v>
+        <v>6958469</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9262,11 +9271,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9293,10 +9297,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B88" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9304,43 +9308,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R88" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,6 +9368,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9593,10 +9593,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127702448</v>
+        <v>127708935</v>
       </c>
       <c r="B91" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581480</v>
+        <v>581452</v>
       </c>
       <c r="R91" t="n">
-        <v>6958518</v>
+        <v>6958446</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,6 +9664,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9690,32 +9695,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708951</v>
+        <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>92640</v>
+        <v>91350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9730,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581943</v>
+        <v>581549</v>
       </c>
       <c r="R92" t="n">
-        <v>6958445</v>
+        <v>6958437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,11 +9766,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9792,10 +9792,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708935</v>
+        <v>127702448</v>
       </c>
       <c r="B93" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9803,21 +9803,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581452</v>
+        <v>581480</v>
       </c>
       <c r="R93" t="n">
-        <v>6958446</v>
+        <v>6958518</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,11 +9863,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9894,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708921</v>
+        <v>127708951</v>
       </c>
       <c r="B94" t="n">
-        <v>91350</v>
+        <v>92640</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9929,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581549</v>
+        <v>581943</v>
       </c>
       <c r="R94" t="n">
-        <v>6958437</v>
+        <v>6958445</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9965,6 +9960,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127700375</v>
+        <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>91646</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,42 +10002,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581797</v>
+        <v>581469</v>
       </c>
       <c r="R95" t="n">
-        <v>6958452</v>
+        <v>6958479</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,11 +10062,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10101,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708917</v>
+        <v>127700375</v>
       </c>
       <c r="B96" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10112,34 +10099,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581459</v>
+        <v>581797</v>
       </c>
       <c r="R96" t="n">
-        <v>6958547</v>
+        <v>6958452</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10172,6 +10167,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10198,10 +10198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127708944</v>
+        <v>127708917</v>
       </c>
       <c r="B97" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10209,21 +10209,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581469</v>
+        <v>581459</v>
       </c>
       <c r="R97" t="n">
-        <v>6958479</v>
+        <v>6958547</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10295,45 +10295,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127701709</v>
+        <v>127708945</v>
       </c>
       <c r="B98" t="n">
-        <v>92047</v>
+        <v>91646</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581590</v>
+        <v>581512</v>
       </c>
       <c r="R98" t="n">
-        <v>6958438</v>
+        <v>6958472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708945</v>
+        <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>91646</v>
+        <v>92047</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581512</v>
+        <v>581590</v>
       </c>
       <c r="R100" t="n">
-        <v>6958472</v>
+        <v>6958438</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10586,32 +10586,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127708924</v>
+        <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>92047</v>
+        <v>91350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>581607</v>
+        <v>581387</v>
       </c>
       <c r="R101" t="n">
-        <v>6958406</v>
+        <v>6958453</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10683,7 +10683,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127708915</v>
+        <v>127708920</v>
       </c>
       <c r="B102" t="n">
         <v>91350</v>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>581387</v>
+        <v>581517</v>
       </c>
       <c r="R102" t="n">
-        <v>6958453</v>
+        <v>6958471</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127708920</v>
+        <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>91350</v>
+        <v>92047</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>581517</v>
+        <v>581607</v>
       </c>
       <c r="R103" t="n">
-        <v>6958471</v>
+        <v>6958406</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127708942</v>
+        <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>91646</v>
+        <v>91551</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581396</v>
+        <v>581423</v>
       </c>
       <c r="R104" t="n">
-        <v>6958454</v>
+        <v>6958511</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,7 +10974,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708946</v>
+        <v>127708942</v>
       </c>
       <c r="B105" t="n">
         <v>91646</v>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581559</v>
+        <v>581396</v>
       </c>
       <c r="R105" t="n">
-        <v>6958443</v>
+        <v>6958454</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127702553</v>
+        <v>127708946</v>
       </c>
       <c r="B106" t="n">
-        <v>91551</v>
+        <v>91646</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581423</v>
+        <v>581559</v>
       </c>
       <c r="R106" t="n">
-        <v>6958511</v>
+        <v>6958443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R112" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,11 +11734,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11765,10 +11760,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11776,21 +11771,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11800,10 +11795,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R113" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11836,6 +11831,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127708941</v>
+        <v>127703591</v>
       </c>
       <c r="B114" t="n">
-        <v>91646</v>
+        <v>91708</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581486</v>
+        <v>581485</v>
       </c>
       <c r="R114" t="n">
-        <v>6958333</v>
+        <v>6958325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,32 +11959,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127702456</v>
+        <v>127708926</v>
       </c>
       <c r="B115" t="n">
-        <v>91350</v>
+        <v>92047</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581480</v>
+        <v>581513</v>
       </c>
       <c r="R115" t="n">
-        <v>6958518</v>
+        <v>6958336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127703591</v>
+        <v>127708941</v>
       </c>
       <c r="B116" t="n">
-        <v>91708</v>
+        <v>91646</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581485</v>
+        <v>581486</v>
       </c>
       <c r="R116" t="n">
-        <v>6958325</v>
+        <v>6958333</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127708926</v>
+        <v>127702456</v>
       </c>
       <c r="B117" t="n">
-        <v>92047</v>
+        <v>91350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581513</v>
+        <v>581480</v>
       </c>
       <c r="R117" t="n">
-        <v>6958336</v>
+        <v>6958518</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B118" t="n">
-        <v>91350</v>
+        <v>57832</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R118" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12347,10 +12352,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B119" t="n">
-        <v>57832</v>
+        <v>91350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12358,39 +12363,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R119" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12847,32 +12847,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127708950</v>
+        <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>98385</v>
+        <v>91350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>581502</v>
+        <v>581606</v>
       </c>
       <c r="R124" t="n">
-        <v>6958332</v>
+        <v>6958438</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12944,32 +12944,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127708909</v>
+        <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>91350</v>
+        <v>98385</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>581606</v>
+        <v>581502</v>
       </c>
       <c r="R125" t="n">
-        <v>6958438</v>
+        <v>6958332</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13138,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708939</v>
+        <v>127708927</v>
       </c>
       <c r="B127" t="n">
-        <v>57672</v>
+        <v>92047</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581490</v>
+        <v>581489</v>
       </c>
       <c r="R127" t="n">
-        <v>6958459</v>
+        <v>6958369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13209,11 +13209,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13240,7 +13235,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127701827</v>
+        <v>127708939</v>
       </c>
       <c r="B128" t="n">
         <v>57672</v>
@@ -13269,21 +13264,16 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581564</v>
+        <v>581490</v>
       </c>
       <c r="R128" t="n">
-        <v>6958463</v>
+        <v>6958459</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13320,7 +13310,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,45 +13337,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708927</v>
+        <v>127701827</v>
       </c>
       <c r="B129" t="n">
-        <v>92047</v>
+        <v>57672</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581489</v>
+        <v>581564</v>
       </c>
       <c r="R129" t="n">
-        <v>6958369</v>
+        <v>6958463</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13418,6 +13413,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R131" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,32 +13638,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708952</v>
+        <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>92640</v>
+        <v>91646</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581959</v>
+        <v>581472</v>
       </c>
       <c r="R132" t="n">
-        <v>6958445</v>
+        <v>6958521</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,32 +13735,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708914</v>
+        <v>127708952</v>
       </c>
       <c r="B133" t="n">
-        <v>91350</v>
+        <v>92640</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581433</v>
+        <v>581959</v>
       </c>
       <c r="R133" t="n">
-        <v>6958423</v>
+        <v>6958445</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1340,7 +1340,7 @@
         <v>127626338</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>91647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R10" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B11" t="n">
-        <v>91646</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R11" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
         <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>91351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R15" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626289</v>
+        <v>127626348</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581425</v>
+        <v>582065</v>
       </c>
       <c r="R16" t="n">
-        <v>6958401</v>
+        <v>6958321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626336</v>
+        <v>127626321</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582065</v>
+        <v>581718</v>
       </c>
       <c r="R18" t="n">
-        <v>6958323</v>
+        <v>6958467</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,6 +2393,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626321</v>
+        <v>127626285</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581718</v>
+        <v>581551</v>
       </c>
       <c r="R19" t="n">
-        <v>6958467</v>
+        <v>6958485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,32 +2521,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626285</v>
+        <v>127626336</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>80161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581551</v>
+        <v>582065</v>
       </c>
       <c r="R20" t="n">
-        <v>6958485</v>
+        <v>6958323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626322</v>
+        <v>127626356</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581761</v>
+        <v>581795</v>
       </c>
       <c r="R21" t="n">
-        <v>6958462</v>
+        <v>6958432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626306</v>
+        <v>127626322</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2755,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581878</v>
+        <v>581761</v>
       </c>
       <c r="R22" t="n">
-        <v>6958484</v>
+        <v>6958462</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626356</v>
+        <v>127626306</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581795</v>
+        <v>581878</v>
       </c>
       <c r="R23" t="n">
-        <v>6958432</v>
+        <v>6958484</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2888,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3228,7 +3228,7 @@
         <v>127626283</v>
       </c>
       <c r="B27" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>127626293</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>127626291</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4220,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626347</v>
+        <v>127626354</v>
       </c>
       <c r="B37" t="n">
-        <v>80160</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582104</v>
+        <v>582103</v>
       </c>
       <c r="R37" t="n">
-        <v>6958386</v>
+        <v>6958332</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,32 +4317,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626325</v>
+        <v>127626347</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581819</v>
+        <v>582104</v>
       </c>
       <c r="R38" t="n">
-        <v>6958488</v>
+        <v>6958386</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,11 +4388,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4419,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626299</v>
+        <v>127626325</v>
       </c>
       <c r="B39" t="n">
         <v>57672</v>
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582073</v>
+        <v>581819</v>
       </c>
       <c r="R39" t="n">
-        <v>6958325</v>
+        <v>6958488</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4494,7 +4489,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4521,7 +4516,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626300</v>
+        <v>127626299</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4556,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582063</v>
+        <v>582073</v>
       </c>
       <c r="R40" t="n">
-        <v>6958321</v>
+        <v>6958325</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4596,7 +4591,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4623,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626354</v>
+        <v>127626300</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4634,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4658,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582103</v>
+        <v>582063</v>
       </c>
       <c r="R41" t="n">
-        <v>6958332</v>
+        <v>6958321</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4694,6 +4689,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626297</v>
+        <v>127626342</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582085</v>
+        <v>581440</v>
       </c>
       <c r="R42" t="n">
-        <v>6958383</v>
+        <v>6958403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4791,11 +4791,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4822,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626327</v>
+        <v>127626284</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4833,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581824</v>
+        <v>581922</v>
       </c>
       <c r="R43" t="n">
-        <v>6958505</v>
+        <v>6958467</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4893,11 +4888,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4924,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626316</v>
+        <v>127626350</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4935,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4959,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581480</v>
+        <v>581948</v>
       </c>
       <c r="R44" t="n">
-        <v>6958548</v>
+        <v>6958486</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,11 +4985,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5026,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626342</v>
+        <v>127626297</v>
       </c>
       <c r="B45" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5037,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5061,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581440</v>
+        <v>582085</v>
       </c>
       <c r="R45" t="n">
-        <v>6958403</v>
+        <v>6958383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5097,6 +5082,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5123,10 +5113,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626284</v>
+        <v>127626327</v>
       </c>
       <c r="B46" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5134,21 +5124,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5158,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581922</v>
+        <v>581824</v>
       </c>
       <c r="R46" t="n">
-        <v>6958467</v>
+        <v>6958505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5194,6 +5184,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5220,10 +5215,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626350</v>
+        <v>127626316</v>
       </c>
       <c r="B47" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5231,21 +5226,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5255,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581948</v>
+        <v>581480</v>
       </c>
       <c r="R47" t="n">
-        <v>6958486</v>
+        <v>6958548</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5291,6 +5286,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626296</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581882</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958519</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5388,11 +5388,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5422,7 +5417,7 @@
         <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5519,7 +5514,7 @@
         <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5613,10 +5608,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127626345</v>
+        <v>127626296</v>
       </c>
       <c r="B51" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5619,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581775</v>
+        <v>581882</v>
       </c>
       <c r="R51" t="n">
-        <v>6958475</v>
+        <v>6958519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5684,6 +5679,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626329</v>
+        <v>127626339</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581831</v>
+        <v>581484</v>
       </c>
       <c r="R52" t="n">
-        <v>6958455</v>
+        <v>6958540</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,11 +5781,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5812,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626303</v>
+        <v>127626290</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5823,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5847,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>582006</v>
+        <v>581438</v>
       </c>
       <c r="R53" t="n">
-        <v>6958447</v>
+        <v>6958399</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5883,11 +5878,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5914,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626290</v>
+        <v>127620475</v>
       </c>
       <c r="B54" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5945,14 +5935,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581438</v>
+        <v>581829</v>
       </c>
       <c r="R54" t="n">
-        <v>6958399</v>
+        <v>6958465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6011,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127620475</v>
+        <v>127626352</v>
       </c>
       <c r="B55" t="n">
-        <v>91350</v>
+        <v>91369</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6022,34 +6012,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581829</v>
+        <v>581490</v>
       </c>
       <c r="R55" t="n">
-        <v>6958465</v>
+        <v>6958524</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626352</v>
+        <v>127626329</v>
       </c>
       <c r="B56" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6119,21 +6109,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6143,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581490</v>
+        <v>581831</v>
       </c>
       <c r="R56" t="n">
-        <v>6958524</v>
+        <v>6958455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6179,6 +6169,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6205,10 +6200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626339</v>
+        <v>127626303</v>
       </c>
       <c r="B57" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,21 +6211,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6240,10 +6235,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581484</v>
+        <v>582006</v>
       </c>
       <c r="R57" t="n">
-        <v>6958540</v>
+        <v>6958447</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6276,6 +6271,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B59" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R59" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B60" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R60" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
         <v>127626353</v>
       </c>
       <c r="B62" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R63" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6899,7 +6894,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626301</v>
+        <v>127626298</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -6934,10 +6929,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582037</v>
+        <v>582124</v>
       </c>
       <c r="R64" t="n">
-        <v>6958341</v>
+        <v>6958327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7001,32 +6996,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626358</v>
+        <v>127626301</v>
       </c>
       <c r="B65" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7031,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582087</v>
+        <v>582037</v>
       </c>
       <c r="R65" t="n">
-        <v>6958421</v>
+        <v>6958341</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,6 +7067,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R66" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B67" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R67" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7271,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7302,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7313,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R68" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,11 +7373,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626288</v>
+        <v>127626311</v>
       </c>
       <c r="B73" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581468</v>
+        <v>581684</v>
       </c>
       <c r="R73" t="n">
-        <v>6958479</v>
+        <v>6958471</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7877,6 +7877,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7903,7 +7908,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B74" t="n">
         <v>57672</v>
@@ -7938,10 +7943,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R74" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7978,7 +7983,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8005,10 +8010,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626304</v>
+        <v>127626288</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8016,21 +8021,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8040,10 +8045,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581961</v>
+        <v>581468</v>
       </c>
       <c r="R75" t="n">
-        <v>6958482</v>
+        <v>6958479</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8076,11 +8081,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8110,7 +8110,7 @@
         <v>127626341</v>
       </c>
       <c r="B76" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127703408</v>
+        <v>127700444</v>
       </c>
       <c r="B82" t="n">
-        <v>91350</v>
+        <v>57832</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,34 +8717,43 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581481</v>
+        <v>581826</v>
       </c>
       <c r="R82" t="n">
-        <v>6958339</v>
+        <v>6958437</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8803,32 +8812,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708919</v>
+        <v>127702065</v>
       </c>
       <c r="B83" t="n">
-        <v>91350</v>
+        <v>91761</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8847,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581468</v>
+        <v>581516</v>
       </c>
       <c r="R83" t="n">
-        <v>6958461</v>
+        <v>6958469</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,7 +8912,7 @@
         <v>127708953</v>
       </c>
       <c r="B84" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8997,10 +9006,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127700444</v>
+        <v>127703408</v>
       </c>
       <c r="B85" t="n">
-        <v>57832</v>
+        <v>91351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9008,43 +9017,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581826</v>
+        <v>581481</v>
       </c>
       <c r="R85" t="n">
-        <v>6958437</v>
+        <v>6958339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9103,32 +9103,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708929</v>
+        <v>127708919</v>
       </c>
       <c r="B86" t="n">
-        <v>92047</v>
+        <v>91351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581702</v>
+        <v>581468</v>
       </c>
       <c r="R86" t="n">
-        <v>6958462</v>
+        <v>6958461</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9200,10 +9200,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127702065</v>
+        <v>127708929</v>
       </c>
       <c r="B87" t="n">
-        <v>91760</v>
+        <v>92048</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9211,21 +9211,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581516</v>
+        <v>581702</v>
       </c>
       <c r="R87" t="n">
-        <v>6958469</v>
+        <v>6958462</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127708911</v>
+        <v>127708910</v>
       </c>
       <c r="B89" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>581597</v>
+        <v>581604</v>
       </c>
       <c r="R89" t="n">
-        <v>6958391</v>
+        <v>6958417</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9496,10 +9496,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127708910</v>
+        <v>127708911</v>
       </c>
       <c r="B90" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>581604</v>
+        <v>581597</v>
       </c>
       <c r="R90" t="n">
-        <v>6958417</v>
+        <v>6958391</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9593,32 +9593,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708935</v>
+        <v>127708951</v>
       </c>
       <c r="B91" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581452</v>
+        <v>581943</v>
       </c>
       <c r="R91" t="n">
-        <v>6958446</v>
+        <v>6958445</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9695,10 +9695,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708921</v>
+        <v>127702448</v>
       </c>
       <c r="B92" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9706,21 +9706,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581549</v>
+        <v>581480</v>
       </c>
       <c r="R92" t="n">
-        <v>6958437</v>
+        <v>6958518</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9792,10 +9792,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127702448</v>
+        <v>127708921</v>
       </c>
       <c r="B93" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9803,21 +9803,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581480</v>
+        <v>581549</v>
       </c>
       <c r="R93" t="n">
-        <v>6958518</v>
+        <v>6958437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708951</v>
+        <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581943</v>
+        <v>581452</v>
       </c>
       <c r="R94" t="n">
-        <v>6958445</v>
+        <v>6958446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127708944</v>
+        <v>127700375</v>
       </c>
       <c r="B95" t="n">
-        <v>91646</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,34 +10002,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581469</v>
+        <v>581797</v>
       </c>
       <c r="R95" t="n">
-        <v>6958479</v>
+        <v>6958452</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10062,6 +10070,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10088,10 +10101,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127700375</v>
+        <v>127708944</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>91647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,42 +10112,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581797</v>
+        <v>581469</v>
       </c>
       <c r="R96" t="n">
-        <v>6958452</v>
+        <v>6958479</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10167,11 +10172,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10201,7 +10201,7 @@
         <v>127708917</v>
       </c>
       <c r="B97" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B98" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R98" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B99" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10403,21 +10403,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R99" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
         <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10877,32 +10877,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127702553</v>
+        <v>127708946</v>
       </c>
       <c r="B104" t="n">
-        <v>91551</v>
+        <v>91647</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581423</v>
+        <v>581559</v>
       </c>
       <c r="R104" t="n">
-        <v>6958511</v>
+        <v>6958443</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10977,7 +10977,7 @@
         <v>127708942</v>
       </c>
       <c r="B105" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11071,32 +11071,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708946</v>
+        <v>127702553</v>
       </c>
       <c r="B106" t="n">
-        <v>91646</v>
+        <v>91552</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581559</v>
+        <v>581423</v>
       </c>
       <c r="R106" t="n">
-        <v>6958443</v>
+        <v>6958511</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>127708947</v>
       </c>
       <c r="B109" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127708912</v>
       </c>
       <c r="B110" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127703591</v>
+        <v>127702456</v>
       </c>
       <c r="B114" t="n">
-        <v>91708</v>
+        <v>91351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581485</v>
+        <v>581480</v>
       </c>
       <c r="R114" t="n">
-        <v>6958325</v>
+        <v>6958518</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,32 +11959,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708926</v>
+        <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>92047</v>
+        <v>91647</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581513</v>
+        <v>581486</v>
       </c>
       <c r="R115" t="n">
-        <v>6958336</v>
+        <v>6958333</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127708941</v>
+        <v>127708926</v>
       </c>
       <c r="B116" t="n">
-        <v>91646</v>
+        <v>92048</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581486</v>
+        <v>581513</v>
       </c>
       <c r="R116" t="n">
-        <v>6958333</v>
+        <v>6958336</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127702456</v>
+        <v>127703591</v>
       </c>
       <c r="B117" t="n">
-        <v>91350</v>
+        <v>91709</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581480</v>
+        <v>581485</v>
       </c>
       <c r="R117" t="n">
-        <v>6958518</v>
+        <v>6958325</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>57832</v>
+        <v>91351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R118" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,10 +12347,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B119" t="n">
-        <v>91350</v>
+        <v>57832</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12363,34 +12358,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R119" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>127708959</v>
       </c>
       <c r="B126" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>127708927</v>
       </c>
       <c r="B127" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708939</v>
+        <v>127701827</v>
       </c>
       <c r="B128" t="n">
         <v>57672</v>
@@ -13264,16 +13264,21 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581490</v>
+        <v>581564</v>
       </c>
       <c r="R128" t="n">
-        <v>6958459</v>
+        <v>6958463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13310,7 +13315,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Äldre ringhack på fallen död gran</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13337,50 +13342,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127701827</v>
+        <v>127708949</v>
       </c>
       <c r="B129" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581564</v>
+        <v>581598</v>
       </c>
       <c r="R129" t="n">
-        <v>6958463</v>
+        <v>6958396</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13413,11 +13413,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13444,32 +13439,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708949</v>
+        <v>127708939</v>
       </c>
       <c r="B130" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13479,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581598</v>
+        <v>581490</v>
       </c>
       <c r="R130" t="n">
-        <v>6958396</v>
+        <v>6958459</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13515,6 +13510,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13544,7 +13544,7 @@
         <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>127708952</v>
       </c>
       <c r="B133" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626319</v>
+        <v>127626338</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581409</v>
+        <v>581544</v>
       </c>
       <c r="R7" t="n">
-        <v>6958406</v>
+        <v>6958500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,11 +1306,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626338</v>
+        <v>127626360</v>
       </c>
       <c r="B8" t="n">
-        <v>91647</v>
+        <v>98387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581544</v>
+        <v>581836</v>
       </c>
       <c r="R8" t="n">
-        <v>6958500</v>
+        <v>6958416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626360</v>
+        <v>127626319</v>
       </c>
       <c r="B9" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581836</v>
+        <v>581409</v>
       </c>
       <c r="R9" t="n">
-        <v>6958416</v>
+        <v>6958406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B10" t="n">
-        <v>91647</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R10" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R11" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B13" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R13" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R14" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626289</v>
+        <v>127626348</v>
       </c>
       <c r="B15" t="n">
-        <v>91351</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581425</v>
+        <v>582065</v>
       </c>
       <c r="R15" t="n">
-        <v>6958401</v>
+        <v>6958321</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626348</v>
+        <v>127626323</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582065</v>
+        <v>581803</v>
       </c>
       <c r="R16" t="n">
-        <v>6958321</v>
+        <v>6958429</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626323</v>
+        <v>127626289</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2231,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581803</v>
+        <v>581425</v>
       </c>
       <c r="R17" t="n">
-        <v>6958429</v>
+        <v>6958401</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626321</v>
+        <v>127626336</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581718</v>
+        <v>582065</v>
       </c>
       <c r="R18" t="n">
-        <v>6958467</v>
+        <v>6958323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626285</v>
+        <v>127626321</v>
       </c>
       <c r="B19" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581551</v>
+        <v>581718</v>
       </c>
       <c r="R19" t="n">
-        <v>6958485</v>
+        <v>6958467</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2495,6 +2490,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,32 +2521,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626336</v>
+        <v>127626285</v>
       </c>
       <c r="B20" t="n">
-        <v>80161</v>
+        <v>91352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582065</v>
+        <v>581551</v>
       </c>
       <c r="R20" t="n">
-        <v>6958323</v>
+        <v>6958485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R24" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,11 +2990,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,21 +3027,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R25" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,21 +3124,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R26" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,11 +3184,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,10 +3210,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626283</v>
+        <v>127626333</v>
       </c>
       <c r="B27" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,21 +3221,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3260,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582010</v>
+        <v>581835</v>
       </c>
       <c r="R27" t="n">
-        <v>6958445</v>
+        <v>6958440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,6 +3281,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3322,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626293</v>
+        <v>127626309</v>
       </c>
       <c r="B28" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3323,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581771</v>
+        <v>581870</v>
       </c>
       <c r="R28" t="n">
-        <v>6958476</v>
+        <v>6958478</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,6 +3383,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3419,10 +3414,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B29" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3454,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R29" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3485,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3519,7 @@
         <v>127626340</v>
       </c>
       <c r="B30" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626302</v>
+        <v>127626318</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582050</v>
+        <v>581380</v>
       </c>
       <c r="R31" t="n">
-        <v>6958390</v>
+        <v>6958472</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626305</v>
+        <v>127626295</v>
       </c>
       <c r="B32" t="n">
         <v>57672</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581928</v>
+        <v>581885</v>
       </c>
       <c r="R32" t="n">
-        <v>6958485</v>
+        <v>6958529</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626318</v>
+        <v>127626305</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581380</v>
+        <v>581928</v>
       </c>
       <c r="R33" t="n">
-        <v>6958472</v>
+        <v>6958485</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,7 +3919,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626324</v>
+        <v>127626302</v>
       </c>
       <c r="B34" t="n">
         <v>57672</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581807</v>
+        <v>582050</v>
       </c>
       <c r="R34" t="n">
-        <v>6958490</v>
+        <v>6958390</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,7 +4021,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626295</v>
+        <v>127626324</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581885</v>
+        <v>581807</v>
       </c>
       <c r="R35" t="n">
-        <v>6958529</v>
+        <v>6958490</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4126,7 +4126,7 @@
         <v>127626292</v>
       </c>
       <c r="B36" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626325</v>
+        <v>127626300</v>
       </c>
       <c r="B39" t="n">
         <v>57672</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581819</v>
+        <v>582063</v>
       </c>
       <c r="R39" t="n">
-        <v>6958488</v>
+        <v>6958321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626300</v>
+        <v>127626325</v>
       </c>
       <c r="B41" t="n">
         <v>57672</v>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582063</v>
+        <v>581819</v>
       </c>
       <c r="R41" t="n">
-        <v>6958321</v>
+        <v>6958488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626342</v>
+        <v>127626284</v>
       </c>
       <c r="B42" t="n">
-        <v>91647</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581440</v>
+        <v>581922</v>
       </c>
       <c r="R42" t="n">
-        <v>6958403</v>
+        <v>6958467</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626284</v>
+        <v>127626342</v>
       </c>
       <c r="B43" t="n">
-        <v>91351</v>
+        <v>91648</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581922</v>
+        <v>581440</v>
       </c>
       <c r="R43" t="n">
-        <v>6958467</v>
+        <v>6958403</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
         <v>127626350</v>
       </c>
       <c r="B44" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626297</v>
+        <v>127626316</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582085</v>
+        <v>581480</v>
       </c>
       <c r="R45" t="n">
-        <v>6958383</v>
+        <v>6958548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626327</v>
+        <v>127626297</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581824</v>
+        <v>582085</v>
       </c>
       <c r="R46" t="n">
-        <v>6958505</v>
+        <v>6958383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5215,7 +5215,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626316</v>
+        <v>127626327</v>
       </c>
       <c r="B47" t="n">
         <v>57672</v>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581480</v>
+        <v>581824</v>
       </c>
       <c r="R47" t="n">
-        <v>6958548</v>
+        <v>6958505</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B48" t="n">
-        <v>91647</v>
+        <v>91370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R48" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B49" t="n">
-        <v>91369</v>
+        <v>91317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R49" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626282</v>
+        <v>127626345</v>
       </c>
       <c r="B50" t="n">
-        <v>91316</v>
+        <v>91648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581658</v>
+        <v>581775</v>
       </c>
       <c r="R50" t="n">
-        <v>6958442</v>
+        <v>6958475</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127626339</v>
+        <v>127626290</v>
       </c>
       <c r="B52" t="n">
-        <v>91647</v>
+        <v>91352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581484</v>
+        <v>581438</v>
       </c>
       <c r="R52" t="n">
-        <v>6958540</v>
+        <v>6958399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127626290</v>
+        <v>127620475</v>
       </c>
       <c r="B53" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5838,14 +5838,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581438</v>
+        <v>581829</v>
       </c>
       <c r="R53" t="n">
-        <v>6958399</v>
+        <v>6958465</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127620475</v>
+        <v>127626352</v>
       </c>
       <c r="B54" t="n">
-        <v>91351</v>
+        <v>91370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,34 +5915,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581829</v>
+        <v>581490</v>
       </c>
       <c r="R54" t="n">
-        <v>6958465</v>
+        <v>6958524</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626352</v>
+        <v>127626339</v>
       </c>
       <c r="B55" t="n">
-        <v>91369</v>
+        <v>91648</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581490</v>
+        <v>581484</v>
       </c>
       <c r="R55" t="n">
-        <v>6958524</v>
+        <v>6958540</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
         <v>127626343</v>
       </c>
       <c r="B59" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>127626294</v>
       </c>
       <c r="B60" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R61" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,11 +6669,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6700,10 +6695,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6711,21 +6706,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,10 +6730,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R62" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6800,7 +6800,7 @@
         <v>127626358</v>
       </c>
       <c r="B63" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127626298</v>
+        <v>127626301</v>
       </c>
       <c r="B64" t="n">
         <v>57672</v>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582124</v>
+        <v>582037</v>
       </c>
       <c r="R64" t="n">
-        <v>6958327</v>
+        <v>6958341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626301</v>
+        <v>127626298</v>
       </c>
       <c r="B65" t="n">
         <v>57672</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582037</v>
+        <v>582124</v>
       </c>
       <c r="R65" t="n">
-        <v>6958341</v>
+        <v>6958327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7305,7 +7305,7 @@
         <v>127626286</v>
       </c>
       <c r="B68" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127622082</v>
+        <v>127626326</v>
       </c>
       <c r="B69" t="n">
         <v>57672</v>
@@ -7427,26 +7427,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581489</v>
+        <v>581814</v>
       </c>
       <c r="R69" t="n">
-        <v>6958404</v>
+        <v>6958498</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7479,6 +7470,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7505,7 +7501,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127626326</v>
+        <v>127622082</v>
       </c>
       <c r="B70" t="n">
         <v>57672</v>
@@ -7533,17 +7529,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581814</v>
+        <v>581489</v>
       </c>
       <c r="R70" t="n">
-        <v>6958498</v>
+        <v>6958404</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7576,11 +7581,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7712,7 +7712,7 @@
         <v>127626346</v>
       </c>
       <c r="B72" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626311</v>
+        <v>127626304</v>
       </c>
       <c r="B73" t="n">
         <v>57672</v>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581684</v>
+        <v>581961</v>
       </c>
       <c r="R73" t="n">
-        <v>6958471</v>
+        <v>6958482</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7908,7 +7908,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127626304</v>
+        <v>127626311</v>
       </c>
       <c r="B74" t="n">
         <v>57672</v>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581961</v>
+        <v>581684</v>
       </c>
       <c r="R74" t="n">
-        <v>6958482</v>
+        <v>6958471</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8013,7 +8013,7 @@
         <v>127626288</v>
       </c>
       <c r="B75" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>127626341</v>
       </c>
       <c r="B76" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92021</v>
+        <v>92022</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8706,54 +8706,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127700444</v>
+        <v>127708929</v>
       </c>
       <c r="B82" t="n">
-        <v>57832</v>
+        <v>92049</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581826</v>
+        <v>581702</v>
       </c>
       <c r="R82" t="n">
-        <v>6958437</v>
+        <v>6958462</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8815,7 +8806,7 @@
         <v>127702065</v>
       </c>
       <c r="B83" t="n">
-        <v>91761</v>
+        <v>91762</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8909,10 +8900,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708953</v>
+        <v>127708940</v>
       </c>
       <c r="B84" t="n">
-        <v>88754</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8920,21 +8911,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8944,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581497</v>
+        <v>581551</v>
       </c>
       <c r="R84" t="n">
-        <v>6958369</v>
+        <v>6958433</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8980,6 +8971,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9009,7 +9005,7 @@
         <v>127703408</v>
       </c>
       <c r="B85" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9106,7 +9102,7 @@
         <v>127708919</v>
       </c>
       <c r="B86" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9200,32 +9196,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708929</v>
+        <v>127708953</v>
       </c>
       <c r="B87" t="n">
-        <v>92048</v>
+        <v>88755</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9235,10 +9231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581702</v>
+        <v>581497</v>
       </c>
       <c r="R87" t="n">
-        <v>6958462</v>
+        <v>6958369</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9297,10 +9293,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127708940</v>
+        <v>127700444</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9308,34 +9304,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581551</v>
+        <v>581826</v>
       </c>
       <c r="R88" t="n">
-        <v>6958433</v>
+        <v>6958437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9368,11 +9373,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9399,10 +9399,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127708910</v>
+        <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>581604</v>
+        <v>581597</v>
       </c>
       <c r="R89" t="n">
-        <v>6958417</v>
+        <v>6958391</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9496,10 +9496,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127708911</v>
+        <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>581597</v>
+        <v>581604</v>
       </c>
       <c r="R90" t="n">
-        <v>6958391</v>
+        <v>6958417</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9593,32 +9593,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708951</v>
+        <v>127708921</v>
       </c>
       <c r="B91" t="n">
-        <v>92641</v>
+        <v>91352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581943</v>
+        <v>581549</v>
       </c>
       <c r="R91" t="n">
-        <v>6958445</v>
+        <v>6958437</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,11 +9664,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9698,7 +9693,7 @@
         <v>127702448</v>
       </c>
       <c r="B92" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9792,32 +9787,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708921</v>
+        <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>91351</v>
+        <v>92642</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581549</v>
+        <v>581943</v>
       </c>
       <c r="R93" t="n">
-        <v>6958437</v>
+        <v>6958445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,6 +9858,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127700375</v>
+        <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,42 +10002,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581797</v>
+        <v>581469</v>
       </c>
       <c r="R95" t="n">
-        <v>6958452</v>
+        <v>6958479</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,11 +10062,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10101,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708944</v>
+        <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91647</v>
+        <v>91352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10112,21 +10099,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10136,10 +10123,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581469</v>
+        <v>581459</v>
       </c>
       <c r="R96" t="n">
-        <v>6958479</v>
+        <v>6958547</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10198,10 +10185,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127708917</v>
+        <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10209,34 +10196,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581459</v>
+        <v>581797</v>
       </c>
       <c r="R97" t="n">
-        <v>6958547</v>
+        <v>6958452</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10269,6 +10264,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10295,45 +10295,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708916</v>
+        <v>127701709</v>
       </c>
       <c r="B98" t="n">
-        <v>91351</v>
+        <v>92049</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581451</v>
+        <v>581590</v>
       </c>
       <c r="R98" t="n">
-        <v>6958466</v>
+        <v>6958438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
         <v>127708945</v>
       </c>
       <c r="B99" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127701709</v>
+        <v>127708916</v>
       </c>
       <c r="B100" t="n">
-        <v>92048</v>
+        <v>91352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581590</v>
+        <v>581451</v>
       </c>
       <c r="R100" t="n">
-        <v>6958438</v>
+        <v>6958466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10586,32 +10586,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127708915</v>
+        <v>127708924</v>
       </c>
       <c r="B101" t="n">
-        <v>91351</v>
+        <v>92049</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>581387</v>
+        <v>581607</v>
       </c>
       <c r="R101" t="n">
-        <v>6958453</v>
+        <v>6958406</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10683,10 +10683,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127708920</v>
+        <v>127708915</v>
       </c>
       <c r="B102" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>581517</v>
+        <v>581387</v>
       </c>
       <c r="R102" t="n">
-        <v>6958471</v>
+        <v>6958453</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127708924</v>
+        <v>127708920</v>
       </c>
       <c r="B103" t="n">
-        <v>92048</v>
+        <v>91352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>581607</v>
+        <v>581517</v>
       </c>
       <c r="R103" t="n">
-        <v>6958406</v>
+        <v>6958471</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10877,10 +10877,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127708946</v>
+        <v>127700450</v>
       </c>
       <c r="B104" t="n">
-        <v>91647</v>
+        <v>57832</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10888,34 +10888,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581559</v>
+        <v>581789</v>
       </c>
       <c r="R104" t="n">
-        <v>6958443</v>
+        <v>6958477</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,32 +10979,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708942</v>
+        <v>127702553</v>
       </c>
       <c r="B105" t="n">
-        <v>91647</v>
+        <v>91553</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11009,10 +11014,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581396</v>
+        <v>581423</v>
       </c>
       <c r="R105" t="n">
-        <v>6958454</v>
+        <v>6958511</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,32 +11076,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127702553</v>
+        <v>127708942</v>
       </c>
       <c r="B106" t="n">
-        <v>91552</v>
+        <v>91648</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581423</v>
+        <v>581396</v>
       </c>
       <c r="R106" t="n">
-        <v>6958511</v>
+        <v>6958454</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127700450</v>
+        <v>127708946</v>
       </c>
       <c r="B107" t="n">
-        <v>57832</v>
+        <v>91648</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11179,39 +11184,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581789</v>
+        <v>581559</v>
       </c>
       <c r="R107" t="n">
-        <v>6958477</v>
+        <v>6958443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>127708947</v>
       </c>
       <c r="B109" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>127708912</v>
       </c>
       <c r="B110" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127702456</v>
+        <v>127703591</v>
       </c>
       <c r="B114" t="n">
-        <v>91351</v>
+        <v>91710</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581480</v>
+        <v>581485</v>
       </c>
       <c r="R114" t="n">
-        <v>6958518</v>
+        <v>6958325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11962,7 +11962,7 @@
         <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127708926</v>
+        <v>127702456</v>
       </c>
       <c r="B116" t="n">
-        <v>92048</v>
+        <v>91352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581513</v>
+        <v>581480</v>
       </c>
       <c r="R116" t="n">
-        <v>6958336</v>
+        <v>6958518</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12153,32 +12153,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127703591</v>
+        <v>127708926</v>
       </c>
       <c r="B117" t="n">
-        <v>91709</v>
+        <v>92049</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2062</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>581485</v>
+        <v>581513</v>
       </c>
       <c r="R117" t="n">
-        <v>6958325</v>
+        <v>6958336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12253,7 +12253,7 @@
         <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13041,32 +13041,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708959</v>
+        <v>127708927</v>
       </c>
       <c r="B126" t="n">
-        <v>92021</v>
+        <v>92049</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>898</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581595</v>
+        <v>581489</v>
       </c>
       <c r="R126" t="n">
-        <v>6958389</v>
+        <v>6958369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13138,10 +13138,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708927</v>
+        <v>127708949</v>
       </c>
       <c r="B127" t="n">
-        <v>92048</v>
+        <v>98387</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13149,21 +13149,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3298</v>
+        <v>219790</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581489</v>
+        <v>581598</v>
       </c>
       <c r="R127" t="n">
-        <v>6958369</v>
+        <v>6958396</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13235,50 +13235,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127701827</v>
+        <v>127708959</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>92022</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R128" t="n">
-        <v>6958463</v>
+        <v>6958389</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13311,11 +13306,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13342,45 +13332,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708949</v>
+        <v>127701827</v>
       </c>
       <c r="B129" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581598</v>
+        <v>581564</v>
       </c>
       <c r="R129" t="n">
-        <v>6958396</v>
+        <v>6958463</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13413,6 +13408,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13541,32 +13541,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708914</v>
+        <v>127708952</v>
       </c>
       <c r="B131" t="n">
-        <v>91351</v>
+        <v>92642</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581433</v>
+        <v>581959</v>
       </c>
       <c r="R131" t="n">
-        <v>6958423</v>
+        <v>6958445</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B132" t="n">
-        <v>91647</v>
+        <v>91352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R132" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,32 +13735,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708952</v>
+        <v>127708943</v>
       </c>
       <c r="B133" t="n">
-        <v>92641</v>
+        <v>91648</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581959</v>
+        <v>581472</v>
       </c>
       <c r="R133" t="n">
-        <v>6958445</v>
+        <v>6958521</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626360</v>
+        <v>127626319</v>
       </c>
       <c r="B8" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581836</v>
+        <v>581409</v>
       </c>
       <c r="R8" t="n">
-        <v>6958416</v>
+        <v>6958406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R9" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127626355</v>
+        <v>127626344</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581582</v>
+        <v>581534</v>
       </c>
       <c r="R10" t="n">
-        <v>6958488</v>
+        <v>6958399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127626344</v>
+        <v>127626355</v>
       </c>
       <c r="B11" t="n">
-        <v>91648</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581534</v>
+        <v>581582</v>
       </c>
       <c r="R11" t="n">
-        <v>6958399</v>
+        <v>6958488</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127626348</v>
+        <v>127626289</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>91352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582065</v>
+        <v>581425</v>
       </c>
       <c r="R15" t="n">
-        <v>6958321</v>
+        <v>6958401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127626323</v>
+        <v>127626348</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581803</v>
+        <v>582065</v>
       </c>
       <c r="R16" t="n">
-        <v>6958429</v>
+        <v>6958321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127626289</v>
+        <v>127626323</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581425</v>
+        <v>581803</v>
       </c>
       <c r="R17" t="n">
-        <v>6958401</v>
+        <v>6958429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127626336</v>
+        <v>127626285</v>
       </c>
       <c r="B18" t="n">
-        <v>80161</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582065</v>
+        <v>581551</v>
       </c>
       <c r="R18" t="n">
-        <v>6958323</v>
+        <v>6958485</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127626321</v>
+        <v>127626336</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581718</v>
+        <v>582065</v>
       </c>
       <c r="R19" t="n">
-        <v>6958467</v>
+        <v>6958323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,11 +2490,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127626285</v>
+        <v>127626321</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581551</v>
+        <v>581718</v>
       </c>
       <c r="R20" t="n">
-        <v>6958485</v>
+        <v>6958467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2592,6 +2587,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626356</v>
+        <v>127626322</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581795</v>
+        <v>581761</v>
       </c>
       <c r="R21" t="n">
-        <v>6958432</v>
+        <v>6958462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2689,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,7 +2720,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626322</v>
+        <v>127626306</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2750,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581761</v>
+        <v>581878</v>
       </c>
       <c r="R22" t="n">
-        <v>6958462</v>
+        <v>6958484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626306</v>
+        <v>127626356</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581878</v>
+        <v>581795</v>
       </c>
       <c r="R23" t="n">
-        <v>6958484</v>
+        <v>6958432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2888,11 +2893,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3210,7 +3210,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626333</v>
+        <v>127626309</v>
       </c>
       <c r="B27" t="n">
         <v>57672</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581835</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6958440</v>
+        <v>6958478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626309</v>
+        <v>127626333</v>
       </c>
       <c r="B28" t="n">
         <v>57672</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581870</v>
+        <v>581835</v>
       </c>
       <c r="R28" t="n">
-        <v>6958478</v>
+        <v>6958440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127626318</v>
+        <v>127626302</v>
       </c>
       <c r="B31" t="n">
         <v>57672</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581380</v>
+        <v>582050</v>
       </c>
       <c r="R31" t="n">
-        <v>6958472</v>
+        <v>6958390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127626295</v>
+        <v>127626305</v>
       </c>
       <c r="B32" t="n">
         <v>57672</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581885</v>
+        <v>581928</v>
       </c>
       <c r="R32" t="n">
-        <v>6958529</v>
+        <v>6958485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127626305</v>
+        <v>127626318</v>
       </c>
       <c r="B33" t="n">
         <v>57672</v>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581928</v>
+        <v>581380</v>
       </c>
       <c r="R33" t="n">
-        <v>6958485</v>
+        <v>6958472</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3919,7 +3919,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127626302</v>
+        <v>127626324</v>
       </c>
       <c r="B34" t="n">
         <v>57672</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582050</v>
+        <v>581807</v>
       </c>
       <c r="R34" t="n">
-        <v>6958390</v>
+        <v>6958490</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,7 +4021,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127626324</v>
+        <v>127626295</v>
       </c>
       <c r="B35" t="n">
         <v>57672</v>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581807</v>
+        <v>581885</v>
       </c>
       <c r="R35" t="n">
-        <v>6958490</v>
+        <v>6958529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4414,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626300</v>
+        <v>127626325</v>
       </c>
       <c r="B39" t="n">
         <v>57672</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582063</v>
+        <v>581819</v>
       </c>
       <c r="R39" t="n">
-        <v>6958321</v>
+        <v>6958488</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4618,7 +4618,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626325</v>
+        <v>127626300</v>
       </c>
       <c r="B41" t="n">
         <v>57672</v>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581819</v>
+        <v>582063</v>
       </c>
       <c r="R41" t="n">
-        <v>6958488</v>
+        <v>6958321</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626284</v>
+        <v>127626342</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581922</v>
+        <v>581440</v>
       </c>
       <c r="R42" t="n">
-        <v>6958467</v>
+        <v>6958403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626342</v>
+        <v>127626350</v>
       </c>
       <c r="B43" t="n">
-        <v>91648</v>
+        <v>91370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581440</v>
+        <v>581948</v>
       </c>
       <c r="R43" t="n">
-        <v>6958403</v>
+        <v>6958486</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626350</v>
+        <v>127626284</v>
       </c>
       <c r="B44" t="n">
-        <v>91370</v>
+        <v>91352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581948</v>
+        <v>581922</v>
       </c>
       <c r="R44" t="n">
-        <v>6958486</v>
+        <v>6958467</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626316</v>
+        <v>127626297</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581480</v>
+        <v>582085</v>
       </c>
       <c r="R45" t="n">
-        <v>6958548</v>
+        <v>6958383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626297</v>
+        <v>127626327</v>
       </c>
       <c r="B46" t="n">
         <v>57672</v>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>582085</v>
+        <v>581824</v>
       </c>
       <c r="R46" t="n">
-        <v>6958383</v>
+        <v>6958505</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5215,7 +5215,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626327</v>
+        <v>127626316</v>
       </c>
       <c r="B47" t="n">
         <v>57672</v>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581824</v>
+        <v>581480</v>
       </c>
       <c r="R47" t="n">
-        <v>6958505</v>
+        <v>6958548</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127626352</v>
+        <v>127626339</v>
       </c>
       <c r="B54" t="n">
-        <v>91370</v>
+        <v>91648</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,21 +5915,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581490</v>
+        <v>581484</v>
       </c>
       <c r="R54" t="n">
-        <v>6958524</v>
+        <v>6958540</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127626339</v>
+        <v>127626329</v>
       </c>
       <c r="B55" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581484</v>
+        <v>581831</v>
       </c>
       <c r="R55" t="n">
-        <v>6958540</v>
+        <v>6958455</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6072,6 +6072,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6098,7 +6103,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127626329</v>
+        <v>127626303</v>
       </c>
       <c r="B56" t="n">
         <v>57672</v>
@@ -6133,10 +6138,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581831</v>
+        <v>582006</v>
       </c>
       <c r="R56" t="n">
-        <v>6958455</v>
+        <v>6958447</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6173,7 +6178,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6200,10 +6205,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127626303</v>
+        <v>127626352</v>
       </c>
       <c r="B57" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,21 +6216,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6235,10 +6240,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582006</v>
+        <v>581490</v>
       </c>
       <c r="R57" t="n">
-        <v>6958447</v>
+        <v>6958524</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6271,11 +6276,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B61" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R61" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,6 +6669,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6695,10 +6700,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6706,21 +6711,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6730,10 +6735,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R62" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,11 +6771,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127626358</v>
+        <v>127626298</v>
       </c>
       <c r="B63" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582087</v>
+        <v>582124</v>
       </c>
       <c r="R63" t="n">
-        <v>6958421</v>
+        <v>6958327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6996,32 +7001,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127626298</v>
+        <v>127626358</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7031,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582124</v>
+        <v>582087</v>
       </c>
       <c r="R65" t="n">
-        <v>6958327</v>
+        <v>6958421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7067,11 +7072,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R66" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,11 +7169,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R67" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,7 +7270,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7302,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B68" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7313,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7337,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R68" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7373,6 +7368,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7399,7 +7399,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127626326</v>
+        <v>127622082</v>
       </c>
       <c r="B69" t="n">
         <v>57672</v>
@@ -7427,17 +7427,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581814</v>
+        <v>581489</v>
       </c>
       <c r="R69" t="n">
-        <v>6958498</v>
+        <v>6958404</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,11 +7479,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7501,7 +7505,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127622082</v>
+        <v>127626326</v>
       </c>
       <c r="B70" t="n">
         <v>57672</v>
@@ -7529,26 +7533,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581489</v>
+        <v>581814</v>
       </c>
       <c r="R70" t="n">
-        <v>6958404</v>
+        <v>6958498</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7581,6 +7576,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7607,32 +7607,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127626307</v>
+        <v>127626346</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>97347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7642,10 +7642,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581874</v>
+        <v>581833</v>
       </c>
       <c r="R71" t="n">
-        <v>6958490</v>
+        <v>6958501</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7678,11 +7678,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7709,32 +7704,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127626346</v>
+        <v>127626307</v>
       </c>
       <c r="B72" t="n">
-        <v>97347</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7744,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581833</v>
+        <v>581874</v>
       </c>
       <c r="R72" t="n">
-        <v>6958501</v>
+        <v>6958490</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7780,6 +7775,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626304</v>
+        <v>127626288</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581961</v>
+        <v>581468</v>
       </c>
       <c r="R73" t="n">
-        <v>6958482</v>
+        <v>6958479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7877,11 +7877,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8010,10 +8005,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127626288</v>
+        <v>127626304</v>
       </c>
       <c r="B75" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8021,21 +8016,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8045,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581468</v>
+        <v>581961</v>
       </c>
       <c r="R75" t="n">
-        <v>6958479</v>
+        <v>6958482</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8081,6 +8076,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8706,32 +8706,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127708929</v>
+        <v>127708953</v>
       </c>
       <c r="B82" t="n">
-        <v>92049</v>
+        <v>88755</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581702</v>
+        <v>581497</v>
       </c>
       <c r="R82" t="n">
-        <v>6958462</v>
+        <v>6958369</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127702065</v>
+        <v>127703408</v>
       </c>
       <c r="B83" t="n">
-        <v>91762</v>
+        <v>91352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581516</v>
+        <v>581481</v>
       </c>
       <c r="R83" t="n">
-        <v>6958469</v>
+        <v>6958339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708940</v>
+        <v>127708919</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581551</v>
+        <v>581468</v>
       </c>
       <c r="R84" t="n">
-        <v>6958433</v>
+        <v>6958461</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8971,11 +8971,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9002,32 +8997,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127703408</v>
+        <v>127708929</v>
       </c>
       <c r="B85" t="n">
-        <v>91352</v>
+        <v>92049</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9037,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581481</v>
+        <v>581702</v>
       </c>
       <c r="R85" t="n">
-        <v>6958339</v>
+        <v>6958462</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9099,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708919</v>
+        <v>127702065</v>
       </c>
       <c r="B86" t="n">
-        <v>91352</v>
+        <v>91762</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9134,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581468</v>
+        <v>581516</v>
       </c>
       <c r="R86" t="n">
-        <v>6958461</v>
+        <v>6958469</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9196,10 +9191,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708953</v>
+        <v>127708940</v>
       </c>
       <c r="B87" t="n">
-        <v>88755</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9207,21 +9202,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9231,10 +9226,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581497</v>
+        <v>581551</v>
       </c>
       <c r="R87" t="n">
-        <v>6958369</v>
+        <v>6958433</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9267,6 +9262,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9593,10 +9593,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708921</v>
+        <v>127702448</v>
       </c>
       <c r="B91" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581549</v>
+        <v>581480</v>
       </c>
       <c r="R91" t="n">
-        <v>6958437</v>
+        <v>6958518</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127702448</v>
+        <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581480</v>
+        <v>581549</v>
       </c>
       <c r="R92" t="n">
-        <v>6958518</v>
+        <v>6958437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10295,45 +10295,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127701709</v>
+        <v>127708945</v>
       </c>
       <c r="B98" t="n">
-        <v>92049</v>
+        <v>91648</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581590</v>
+        <v>581512</v>
       </c>
       <c r="R98" t="n">
-        <v>6958438</v>
+        <v>6958472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127708945</v>
+        <v>127701709</v>
       </c>
       <c r="B99" t="n">
-        <v>91648</v>
+        <v>92049</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581512</v>
+        <v>581590</v>
       </c>
       <c r="R99" t="n">
-        <v>6958472</v>
+        <v>6958438</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10586,32 +10586,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127708924</v>
+        <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>92049</v>
+        <v>91352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>581607</v>
+        <v>581387</v>
       </c>
       <c r="R101" t="n">
-        <v>6958406</v>
+        <v>6958453</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10683,7 +10683,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127708915</v>
+        <v>127708920</v>
       </c>
       <c r="B102" t="n">
         <v>91352</v>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>581387</v>
+        <v>581517</v>
       </c>
       <c r="R102" t="n">
-        <v>6958453</v>
+        <v>6958471</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10780,32 +10780,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127708920</v>
+        <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>91352</v>
+        <v>92049</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>581517</v>
+        <v>581607</v>
       </c>
       <c r="R103" t="n">
-        <v>6958471</v>
+        <v>6958406</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10877,50 +10877,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127700450</v>
+        <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>57832</v>
+        <v>91553</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581789</v>
+        <v>581423</v>
       </c>
       <c r="R104" t="n">
-        <v>6958477</v>
+        <v>6958511</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10979,45 +10974,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127702553</v>
+        <v>127700450</v>
       </c>
       <c r="B105" t="n">
-        <v>91553</v>
+        <v>57832</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581423</v>
+        <v>581789</v>
       </c>
       <c r="R105" t="n">
-        <v>6958511</v>
+        <v>6958477</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127703591</v>
+        <v>127708941</v>
       </c>
       <c r="B114" t="n">
-        <v>91710</v>
+        <v>91648</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581485</v>
+        <v>581486</v>
       </c>
       <c r="R114" t="n">
-        <v>6958325</v>
+        <v>6958333</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708941</v>
+        <v>127702456</v>
       </c>
       <c r="B115" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11970,21 +11970,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581486</v>
+        <v>581480</v>
       </c>
       <c r="R115" t="n">
-        <v>6958333</v>
+        <v>6958518</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127702456</v>
+        <v>127703591</v>
       </c>
       <c r="B116" t="n">
-        <v>91352</v>
+        <v>91710</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581480</v>
+        <v>581485</v>
       </c>
       <c r="R116" t="n">
-        <v>6958518</v>
+        <v>6958325</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B118" t="n">
-        <v>91352</v>
+        <v>57832</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R118" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12347,10 +12352,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B119" t="n">
-        <v>57832</v>
+        <v>91352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12358,39 +12363,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R119" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13138,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708949</v>
+        <v>127708939</v>
       </c>
       <c r="B127" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581598</v>
+        <v>581490</v>
       </c>
       <c r="R127" t="n">
-        <v>6958396</v>
+        <v>6958459</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13209,6 +13209,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13235,45 +13240,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708959</v>
+        <v>127701827</v>
       </c>
       <c r="B128" t="n">
-        <v>92022</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R128" t="n">
-        <v>6958389</v>
+        <v>6958463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13306,6 +13316,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13332,50 +13347,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127701827</v>
+        <v>127708949</v>
       </c>
       <c r="B129" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581564</v>
+        <v>581598</v>
       </c>
       <c r="R129" t="n">
-        <v>6958463</v>
+        <v>6958396</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13408,11 +13418,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13439,32 +13444,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708939</v>
+        <v>127708959</v>
       </c>
       <c r="B130" t="n">
-        <v>57672</v>
+        <v>92022</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13479,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581490</v>
+        <v>581595</v>
       </c>
       <c r="R130" t="n">
-        <v>6958459</v>
+        <v>6958389</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13510,11 +13515,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13541,32 +13541,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708952</v>
+        <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>92642</v>
+        <v>91352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581959</v>
+        <v>581433</v>
       </c>
       <c r="R131" t="n">
-        <v>6958445</v>
+        <v>6958423</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R132" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,32 +13735,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708943</v>
+        <v>127708952</v>
       </c>
       <c r="B133" t="n">
-        <v>91648</v>
+        <v>92642</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581472</v>
+        <v>581959</v>
       </c>
       <c r="R133" t="n">
-        <v>6958521</v>
+        <v>6958445</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127626338</v>
+        <v>127626319</v>
       </c>
       <c r="B7" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581544</v>
+        <v>581409</v>
       </c>
       <c r="R7" t="n">
-        <v>6958500</v>
+        <v>6958406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1306,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127626319</v>
+        <v>127626360</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581409</v>
+        <v>581836</v>
       </c>
       <c r="R8" t="n">
-        <v>6958406</v>
+        <v>6958416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1408,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127626360</v>
+        <v>127626338</v>
       </c>
       <c r="B9" t="n">
-        <v>98387</v>
+        <v>91648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581836</v>
+        <v>581544</v>
       </c>
       <c r="R9" t="n">
-        <v>6958416</v>
+        <v>6958500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R13" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R14" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +1995,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626351</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>91370</v>
+        <v>91648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581501</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958530</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626282</v>
+        <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91317</v>
+        <v>91370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581658</v>
+        <v>581501</v>
       </c>
       <c r="R49" t="n">
-        <v>6958442</v>
+        <v>6958530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626345</v>
+        <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>91648</v>
+        <v>91317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581775</v>
+        <v>581658</v>
       </c>
       <c r="R50" t="n">
-        <v>6958475</v>
+        <v>6958442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127626343</v>
+        <v>127626294</v>
       </c>
       <c r="B59" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6415,21 +6415,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581513</v>
+        <v>581835</v>
       </c>
       <c r="R59" t="n">
-        <v>6958410</v>
+        <v>6958427</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127626294</v>
+        <v>127626343</v>
       </c>
       <c r="B60" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6512,21 +6512,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581835</v>
+        <v>581513</v>
       </c>
       <c r="R60" t="n">
-        <v>6958427</v>
+        <v>6958410</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R61" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,11 +6669,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6700,10 +6695,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6711,21 +6706,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,10 +6730,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R62" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708921</v>
+        <v>127708935</v>
       </c>
       <c r="B92" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581549</v>
+        <v>581452</v>
       </c>
       <c r="R92" t="n">
-        <v>6958437</v>
+        <v>6958446</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,6 +9761,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9787,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708951</v>
+        <v>127708921</v>
       </c>
       <c r="B93" t="n">
-        <v>92642</v>
+        <v>91352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581943</v>
+        <v>581549</v>
       </c>
       <c r="R93" t="n">
-        <v>6958445</v>
+        <v>6958437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9863,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708935</v>
+        <v>127708951</v>
       </c>
       <c r="B94" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581452</v>
+        <v>581943</v>
       </c>
       <c r="R94" t="n">
-        <v>6958446</v>
+        <v>6958445</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B98" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R98" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B100" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10500,21 +10500,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R100" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626283</v>
+        <v>127626309</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582010</v>
+        <v>581870</v>
       </c>
       <c r="R24" t="n">
-        <v>6958445</v>
+        <v>6958478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,6 +2990,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3016,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B25" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,21 +3032,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R25" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,6 +3092,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3113,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B26" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,21 +3134,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3148,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R26" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,6 +3194,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3210,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,21 +3236,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3245,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R27" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,11 +3296,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3312,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3323,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,10 +3357,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R28" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,11 +3393,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,10 +3419,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,21 +3430,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R29" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,11 +3490,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4220,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626354</v>
+        <v>127626347</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>80160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582103</v>
+        <v>582104</v>
       </c>
       <c r="R37" t="n">
-        <v>6958332</v>
+        <v>6958386</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,32 +4317,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626347</v>
+        <v>127626325</v>
       </c>
       <c r="B38" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582104</v>
+        <v>581819</v>
       </c>
       <c r="R38" t="n">
-        <v>6958386</v>
+        <v>6958488</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,6 +4388,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4414,7 +4419,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626325</v>
+        <v>127626299</v>
       </c>
       <c r="B39" t="n">
         <v>57672</v>
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581819</v>
+        <v>582073</v>
       </c>
       <c r="R39" t="n">
-        <v>6958488</v>
+        <v>6958325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,7 +4494,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,7 +4521,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626299</v>
+        <v>127626300</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4551,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582073</v>
+        <v>582063</v>
       </c>
       <c r="R40" t="n">
-        <v>6958325</v>
+        <v>6958321</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,7 +4596,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4623,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626300</v>
+        <v>127626354</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4634,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4658,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582063</v>
+        <v>582103</v>
       </c>
       <c r="R41" t="n">
-        <v>6958321</v>
+        <v>6958332</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,11 +4694,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626345</v>
+        <v>127626351</v>
       </c>
       <c r="B48" t="n">
-        <v>91648</v>
+        <v>91370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581775</v>
+        <v>581501</v>
       </c>
       <c r="R48" t="n">
-        <v>6958475</v>
+        <v>6958530</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626351</v>
+        <v>127626282</v>
       </c>
       <c r="B49" t="n">
-        <v>91370</v>
+        <v>91317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581501</v>
+        <v>581658</v>
       </c>
       <c r="R49" t="n">
-        <v>6958530</v>
+        <v>6958442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626282</v>
+        <v>127626345</v>
       </c>
       <c r="B50" t="n">
-        <v>91317</v>
+        <v>91648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581658</v>
+        <v>581775</v>
       </c>
       <c r="R50" t="n">
-        <v>6958442</v>
+        <v>6958475</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626286</v>
+        <v>127626328</v>
       </c>
       <c r="B66" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581497</v>
+        <v>581823</v>
       </c>
       <c r="R66" t="n">
-        <v>6958542</v>
+        <v>6958452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,6 +7169,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7195,10 +7200,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626357</v>
+        <v>127626286</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,10 +7235,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581828</v>
+        <v>581497</v>
       </c>
       <c r="R67" t="n">
-        <v>6958421</v>
+        <v>6958542</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,11 +7271,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626328</v>
+        <v>127626357</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581823</v>
+        <v>581828</v>
       </c>
       <c r="R68" t="n">
-        <v>6958452</v>
+        <v>6958421</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708935</v>
+        <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581452</v>
+        <v>581549</v>
       </c>
       <c r="R92" t="n">
-        <v>6958446</v>
+        <v>6958437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,11 +9761,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9792,32 +9787,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708921</v>
+        <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>91352</v>
+        <v>92642</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581549</v>
+        <v>581943</v>
       </c>
       <c r="R93" t="n">
-        <v>6958437</v>
+        <v>6958445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,6 +9858,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708951</v>
+        <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581943</v>
+        <v>581452</v>
       </c>
       <c r="R94" t="n">
-        <v>6958445</v>
+        <v>6958446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127700450</v>
+        <v>127708942</v>
       </c>
       <c r="B105" t="n">
-        <v>57832</v>
+        <v>91648</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,39 +10985,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581789</v>
+        <v>581396</v>
       </c>
       <c r="R105" t="n">
-        <v>6958477</v>
+        <v>6958454</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11076,7 +11071,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708942</v>
+        <v>127708946</v>
       </c>
       <c r="B106" t="n">
         <v>91648</v>
@@ -11111,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581396</v>
+        <v>581559</v>
       </c>
       <c r="R106" t="n">
-        <v>6958454</v>
+        <v>6958443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127708946</v>
+        <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>91648</v>
+        <v>57832</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11184,34 +11179,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581559</v>
+        <v>581789</v>
       </c>
       <c r="R107" t="n">
-        <v>6958443</v>
+        <v>6958477</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13041,10 +13041,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708927</v>
+        <v>127708949</v>
       </c>
       <c r="B126" t="n">
-        <v>92049</v>
+        <v>98387</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>219790</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581489</v>
+        <v>581598</v>
       </c>
       <c r="R126" t="n">
-        <v>6958369</v>
+        <v>6958396</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13138,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708939</v>
+        <v>127708959</v>
       </c>
       <c r="B127" t="n">
-        <v>57672</v>
+        <v>92022</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581490</v>
+        <v>581595</v>
       </c>
       <c r="R127" t="n">
-        <v>6958459</v>
+        <v>6958389</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13209,11 +13209,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13240,50 +13235,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127701827</v>
+        <v>127708927</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>92049</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581564</v>
+        <v>581489</v>
       </c>
       <c r="R128" t="n">
-        <v>6958463</v>
+        <v>6958369</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13316,11 +13306,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,32 +13332,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708949</v>
+        <v>127708939</v>
       </c>
       <c r="B129" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13382,10 +13367,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581598</v>
+        <v>581490</v>
       </c>
       <c r="R129" t="n">
-        <v>6958396</v>
+        <v>6958459</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13418,6 +13403,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13444,45 +13434,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708959</v>
+        <v>127701827</v>
       </c>
       <c r="B130" t="n">
-        <v>92022</v>
+        <v>57672</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R130" t="n">
-        <v>6958389</v>
+        <v>6958463</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13515,6 +13510,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B131" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R131" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B132" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R132" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127626287</v>
+        <v>127626332</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581481</v>
+        <v>581833</v>
       </c>
       <c r="R13" t="n">
-        <v>6958554</v>
+        <v>6958448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127626332</v>
+        <v>127626287</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581833</v>
+        <v>581481</v>
       </c>
       <c r="R14" t="n">
-        <v>6958448</v>
+        <v>6958554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4220,32 +4220,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127626347</v>
+        <v>127626354</v>
       </c>
       <c r="B37" t="n">
-        <v>80160</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582104</v>
+        <v>582103</v>
       </c>
       <c r="R37" t="n">
-        <v>6958386</v>
+        <v>6958332</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,32 +4317,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127626325</v>
+        <v>127626347</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>80160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581819</v>
+        <v>582104</v>
       </c>
       <c r="R38" t="n">
-        <v>6958488</v>
+        <v>6958386</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,11 +4388,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4419,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127626299</v>
+        <v>127626325</v>
       </c>
       <c r="B39" t="n">
         <v>57672</v>
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582073</v>
+        <v>581819</v>
       </c>
       <c r="R39" t="n">
-        <v>6958325</v>
+        <v>6958488</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4494,7 +4489,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4521,7 +4516,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127626300</v>
+        <v>127626299</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4556,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582063</v>
+        <v>582073</v>
       </c>
       <c r="R40" t="n">
-        <v>6958321</v>
+        <v>6958325</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4596,7 +4591,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4623,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127626354</v>
+        <v>127626300</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4634,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4658,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582103</v>
+        <v>582063</v>
       </c>
       <c r="R41" t="n">
-        <v>6958332</v>
+        <v>6958321</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4694,6 +4689,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626288</v>
+        <v>127626341</v>
       </c>
       <c r="B73" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581468</v>
+        <v>581425</v>
       </c>
       <c r="R73" t="n">
-        <v>6958479</v>
+        <v>6958396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626341</v>
+        <v>127626288</v>
       </c>
       <c r="B76" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581425</v>
+        <v>581468</v>
       </c>
       <c r="R76" t="n">
-        <v>6958396</v>
+        <v>6958479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127703408</v>
+        <v>127708929</v>
       </c>
       <c r="B83" t="n">
-        <v>91352</v>
+        <v>92049</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581481</v>
+        <v>581702</v>
       </c>
       <c r="R83" t="n">
-        <v>6958339</v>
+        <v>6958462</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708919</v>
+        <v>127702065</v>
       </c>
       <c r="B84" t="n">
-        <v>91352</v>
+        <v>91762</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581468</v>
+        <v>581516</v>
       </c>
       <c r="R84" t="n">
-        <v>6958461</v>
+        <v>6958469</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,32 +8997,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127708929</v>
+        <v>127703408</v>
       </c>
       <c r="B85" t="n">
-        <v>92049</v>
+        <v>91352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581702</v>
+        <v>581481</v>
       </c>
       <c r="R85" t="n">
-        <v>6958462</v>
+        <v>6958339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127702065</v>
+        <v>127708919</v>
       </c>
       <c r="B86" t="n">
-        <v>91762</v>
+        <v>91352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581516</v>
+        <v>581468</v>
       </c>
       <c r="R86" t="n">
-        <v>6958469</v>
+        <v>6958461</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708940</v>
+        <v>127700444</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9202,34 +9202,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581551</v>
+        <v>581826</v>
       </c>
       <c r="R87" t="n">
-        <v>6958433</v>
+        <v>6958437</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9262,11 +9271,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9293,10 +9297,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B88" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9304,43 +9308,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R88" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,6 +9368,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708921</v>
+        <v>127708935</v>
       </c>
       <c r="B92" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581549</v>
+        <v>581452</v>
       </c>
       <c r="R92" t="n">
-        <v>6958437</v>
+        <v>6958446</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,6 +9761,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9787,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708951</v>
+        <v>127708921</v>
       </c>
       <c r="B93" t="n">
-        <v>92642</v>
+        <v>91352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581943</v>
+        <v>581549</v>
       </c>
       <c r="R93" t="n">
-        <v>6958445</v>
+        <v>6958437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9863,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708935</v>
+        <v>127708951</v>
       </c>
       <c r="B94" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581452</v>
+        <v>581943</v>
       </c>
       <c r="R94" t="n">
-        <v>6958446</v>
+        <v>6958445</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B98" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R98" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B100" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10500,21 +10500,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R100" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708947</v>
+        <v>127708912</v>
       </c>
       <c r="B109" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581574</v>
+        <v>581558</v>
       </c>
       <c r="R109" t="n">
-        <v>6958443</v>
+        <v>6958357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B110" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R110" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11535,6 +11535,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11561,10 +11566,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708937</v>
+        <v>127708947</v>
       </c>
       <c r="B111" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11572,21 +11577,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11596,10 +11601,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581457</v>
+        <v>581574</v>
       </c>
       <c r="R111" t="n">
-        <v>6958514</v>
+        <v>6958443</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11632,11 +11637,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13041,10 +13041,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708949</v>
+        <v>127708927</v>
       </c>
       <c r="B126" t="n">
-        <v>98387</v>
+        <v>92049</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219790</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581598</v>
+        <v>581489</v>
       </c>
       <c r="R126" t="n">
-        <v>6958396</v>
+        <v>6958369</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13138,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708959</v>
+        <v>127708939</v>
       </c>
       <c r="B127" t="n">
-        <v>92022</v>
+        <v>57672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13173,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581595</v>
+        <v>581490</v>
       </c>
       <c r="R127" t="n">
-        <v>6958389</v>
+        <v>6958459</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13209,6 +13209,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13235,45 +13240,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708927</v>
+        <v>127701827</v>
       </c>
       <c r="B128" t="n">
-        <v>92049</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581489</v>
+        <v>581564</v>
       </c>
       <c r="R128" t="n">
-        <v>6958369</v>
+        <v>6958463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13306,6 +13316,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13332,32 +13347,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708939</v>
+        <v>127708949</v>
       </c>
       <c r="B129" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13367,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581490</v>
+        <v>581598</v>
       </c>
       <c r="R129" t="n">
-        <v>6958459</v>
+        <v>6958396</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13403,11 +13418,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13434,50 +13444,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127701827</v>
+        <v>127708959</v>
       </c>
       <c r="B130" t="n">
-        <v>57672</v>
+        <v>92022</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R130" t="n">
-        <v>6958463</v>
+        <v>6958389</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13510,11 +13515,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R131" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R132" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -4720,10 +4720,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127626342</v>
+        <v>127626350</v>
       </c>
       <c r="B42" t="n">
-        <v>91648</v>
+        <v>91370</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581440</v>
+        <v>581948</v>
       </c>
       <c r="R42" t="n">
-        <v>6958403</v>
+        <v>6958486</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127626350</v>
+        <v>127626297</v>
       </c>
       <c r="B43" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581948</v>
+        <v>582085</v>
       </c>
       <c r="R43" t="n">
-        <v>6958486</v>
+        <v>6958383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4888,6 +4888,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4914,10 +4919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127626284</v>
+        <v>127626327</v>
       </c>
       <c r="B44" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4925,21 +4930,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581922</v>
+        <v>581824</v>
       </c>
       <c r="R44" t="n">
-        <v>6958467</v>
+        <v>6958505</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4985,6 +4990,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5011,7 +5021,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127626297</v>
+        <v>127626316</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5046,10 +5056,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>582085</v>
+        <v>581480</v>
       </c>
       <c r="R45" t="n">
-        <v>6958383</v>
+        <v>6958548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,10 +5123,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127626327</v>
+        <v>127626284</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5124,21 +5134,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5148,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581824</v>
+        <v>581922</v>
       </c>
       <c r="R46" t="n">
-        <v>6958505</v>
+        <v>6958467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,11 +5194,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5215,10 +5220,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127626316</v>
+        <v>127626342</v>
       </c>
       <c r="B47" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5226,21 +5231,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5250,10 +5255,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581480</v>
+        <v>581440</v>
       </c>
       <c r="R47" t="n">
-        <v>6958548</v>
+        <v>6958403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5286,11 +5291,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B61" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R61" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,6 +6669,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6695,10 +6700,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6706,21 +6711,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6730,10 +6735,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R62" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,11 +6771,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626341</v>
+        <v>127626288</v>
       </c>
       <c r="B73" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581425</v>
+        <v>581468</v>
       </c>
       <c r="R73" t="n">
-        <v>6958396</v>
+        <v>6958479</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626288</v>
+        <v>127626341</v>
       </c>
       <c r="B76" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581468</v>
+        <v>581425</v>
       </c>
       <c r="R76" t="n">
-        <v>6958479</v>
+        <v>6958396</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708935</v>
+        <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581452</v>
+        <v>581549</v>
       </c>
       <c r="R92" t="n">
-        <v>6958446</v>
+        <v>6958437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,11 +9761,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9792,32 +9787,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708921</v>
+        <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>91352</v>
+        <v>92642</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581549</v>
+        <v>581943</v>
       </c>
       <c r="R93" t="n">
-        <v>6958437</v>
+        <v>6958445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,6 +9858,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708951</v>
+        <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581943</v>
+        <v>581452</v>
       </c>
       <c r="R94" t="n">
-        <v>6958445</v>
+        <v>6958446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127708944</v>
+        <v>127700375</v>
       </c>
       <c r="B95" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,34 +10002,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581469</v>
+        <v>581797</v>
       </c>
       <c r="R95" t="n">
-        <v>6958479</v>
+        <v>6958452</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10062,6 +10070,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10088,10 +10101,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708917</v>
+        <v>127708944</v>
       </c>
       <c r="B96" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10099,21 +10112,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10123,10 +10136,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581459</v>
+        <v>581469</v>
       </c>
       <c r="R96" t="n">
-        <v>6958547</v>
+        <v>6958479</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10185,10 +10198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127700375</v>
+        <v>127708917</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10196,42 +10209,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581797</v>
+        <v>581459</v>
       </c>
       <c r="R97" t="n">
-        <v>6958452</v>
+        <v>6958547</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10264,11 +10269,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B98" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R98" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B100" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10500,21 +10500,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R100" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708942</v>
+        <v>127700450</v>
       </c>
       <c r="B105" t="n">
-        <v>91648</v>
+        <v>57832</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,34 +10985,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581396</v>
+        <v>581789</v>
       </c>
       <c r="R105" t="n">
-        <v>6958454</v>
+        <v>6958477</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,7 +11076,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708946</v>
+        <v>127708942</v>
       </c>
       <c r="B106" t="n">
         <v>91648</v>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581559</v>
+        <v>581396</v>
       </c>
       <c r="R106" t="n">
-        <v>6958443</v>
+        <v>6958454</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127700450</v>
+        <v>127708946</v>
       </c>
       <c r="B107" t="n">
-        <v>57832</v>
+        <v>91648</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11179,39 +11184,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581789</v>
+        <v>581559</v>
       </c>
       <c r="R107" t="n">
-        <v>6958477</v>
+        <v>6958443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708912</v>
+        <v>127708947</v>
       </c>
       <c r="B109" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581558</v>
+        <v>581574</v>
       </c>
       <c r="R109" t="n">
-        <v>6958357</v>
+        <v>6958443</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708937</v>
+        <v>127708912</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581457</v>
+        <v>581558</v>
       </c>
       <c r="R110" t="n">
-        <v>6958514</v>
+        <v>6958357</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11535,11 +11535,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11566,10 +11561,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708947</v>
+        <v>127708937</v>
       </c>
       <c r="B111" t="n">
-        <v>91648</v>
+        <v>57672</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11577,21 +11572,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11601,10 +11596,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581574</v>
+        <v>581457</v>
       </c>
       <c r="R111" t="n">
-        <v>6958443</v>
+        <v>6958514</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11637,6 +11632,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B131" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R131" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B132" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R132" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127626322</v>
+        <v>127626356</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581761</v>
+        <v>581795</v>
       </c>
       <c r="R21" t="n">
-        <v>6958462</v>
+        <v>6958432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127626306</v>
+        <v>127626322</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2755,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581878</v>
+        <v>581761</v>
       </c>
       <c r="R22" t="n">
-        <v>6958484</v>
+        <v>6958462</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127626356</v>
+        <v>127626306</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581795</v>
+        <v>581878</v>
       </c>
       <c r="R23" t="n">
-        <v>6958432</v>
+        <v>6958484</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2888,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127626309</v>
+        <v>127626283</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581870</v>
+        <v>582010</v>
       </c>
       <c r="R24" t="n">
-        <v>6958478</v>
+        <v>6958445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,11 +2990,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127626333</v>
+        <v>127626293</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,21 +3027,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3051,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581835</v>
+        <v>581771</v>
       </c>
       <c r="R25" t="n">
-        <v>6958440</v>
+        <v>6958476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3092,11 +3087,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,10 +3113,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127626312</v>
+        <v>127626291</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3134,21 +3124,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3148,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581642</v>
+        <v>581538</v>
       </c>
       <c r="R26" t="n">
-        <v>6958463</v>
+        <v>6958404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,11 +3184,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3225,10 +3210,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127626283</v>
+        <v>127626309</v>
       </c>
       <c r="B27" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,21 +3221,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3260,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582010</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6958445</v>
+        <v>6958478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3296,6 +3281,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3322,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127626293</v>
+        <v>127626333</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3323,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3357,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581771</v>
+        <v>581835</v>
       </c>
       <c r="R28" t="n">
-        <v>6958476</v>
+        <v>6958440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3393,6 +3383,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3419,10 +3414,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127626291</v>
+        <v>127626312</v>
       </c>
       <c r="B29" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3454,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581538</v>
+        <v>581642</v>
       </c>
       <c r="R29" t="n">
-        <v>6958404</v>
+        <v>6958463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3490,6 +3485,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5317,10 +5317,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127626351</v>
+        <v>127626345</v>
       </c>
       <c r="B48" t="n">
-        <v>91370</v>
+        <v>91648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581501</v>
+        <v>581775</v>
       </c>
       <c r="R48" t="n">
-        <v>6958530</v>
+        <v>6958475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,32 +5414,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127626282</v>
+        <v>127626351</v>
       </c>
       <c r="B49" t="n">
-        <v>91317</v>
+        <v>91370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581658</v>
+        <v>581501</v>
       </c>
       <c r="R49" t="n">
-        <v>6958442</v>
+        <v>6958530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,32 +5511,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127626345</v>
+        <v>127626282</v>
       </c>
       <c r="B50" t="n">
-        <v>91648</v>
+        <v>91317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5546,10 +5546,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581775</v>
+        <v>581658</v>
       </c>
       <c r="R50" t="n">
-        <v>6958475</v>
+        <v>6958442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127626314</v>
+        <v>127626353</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581570</v>
+        <v>581843</v>
       </c>
       <c r="R61" t="n">
-        <v>6958491</v>
+        <v>6958404</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,11 +6669,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6700,10 +6695,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127626353</v>
+        <v>127626314</v>
       </c>
       <c r="B62" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6711,21 +6706,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,10 +6730,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581843</v>
+        <v>581570</v>
       </c>
       <c r="R62" t="n">
-        <v>6958404</v>
+        <v>6958491</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127626328</v>
+        <v>127626286</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581823</v>
+        <v>581497</v>
       </c>
       <c r="R66" t="n">
-        <v>6958452</v>
+        <v>6958542</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7169,11 +7169,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7200,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127626286</v>
+        <v>127626357</v>
       </c>
       <c r="B67" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7211,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7235,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581497</v>
+        <v>581828</v>
       </c>
       <c r="R67" t="n">
-        <v>6958542</v>
+        <v>6958421</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7271,6 +7266,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7297,10 +7297,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127626357</v>
+        <v>127626328</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7308,21 +7308,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581828</v>
+        <v>581823</v>
       </c>
       <c r="R68" t="n">
-        <v>6958421</v>
+        <v>6958452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7806,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127626288</v>
+        <v>127626341</v>
       </c>
       <c r="B73" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581468</v>
+        <v>581425</v>
       </c>
       <c r="R73" t="n">
-        <v>6958479</v>
+        <v>6958396</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8107,10 +8107,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127626341</v>
+        <v>127626288</v>
       </c>
       <c r="B76" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,21 +8118,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8142,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581425</v>
+        <v>581468</v>
       </c>
       <c r="R76" t="n">
-        <v>6958396</v>
+        <v>6958479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8803,32 +8803,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127708929</v>
+        <v>127703408</v>
       </c>
       <c r="B83" t="n">
-        <v>92049</v>
+        <v>91352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581702</v>
+        <v>581481</v>
       </c>
       <c r="R83" t="n">
-        <v>6958462</v>
+        <v>6958339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,32 +8900,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127702065</v>
+        <v>127708919</v>
       </c>
       <c r="B84" t="n">
-        <v>91762</v>
+        <v>91352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581516</v>
+        <v>581468</v>
       </c>
       <c r="R84" t="n">
-        <v>6958469</v>
+        <v>6958461</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,32 +8997,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127703408</v>
+        <v>127708929</v>
       </c>
       <c r="B85" t="n">
-        <v>91352</v>
+        <v>92049</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581481</v>
+        <v>581702</v>
       </c>
       <c r="R85" t="n">
-        <v>6958339</v>
+        <v>6958462</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708919</v>
+        <v>127702065</v>
       </c>
       <c r="B86" t="n">
-        <v>91352</v>
+        <v>91762</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581468</v>
+        <v>581516</v>
       </c>
       <c r="R86" t="n">
-        <v>6958461</v>
+        <v>6958469</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9191,10 +9191,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B87" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9202,43 +9202,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R87" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9271,6 +9262,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9297,10 +9293,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127708940</v>
+        <v>127700444</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9308,34 +9304,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581551</v>
+        <v>581826</v>
       </c>
       <c r="R88" t="n">
-        <v>6958433</v>
+        <v>6958437</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9368,11 +9373,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127700450</v>
+        <v>127708942</v>
       </c>
       <c r="B105" t="n">
-        <v>57832</v>
+        <v>91648</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,39 +10985,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581789</v>
+        <v>581396</v>
       </c>
       <c r="R105" t="n">
-        <v>6958477</v>
+        <v>6958454</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11076,7 +11071,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708942</v>
+        <v>127708946</v>
       </c>
       <c r="B106" t="n">
         <v>91648</v>
@@ -11111,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581396</v>
+        <v>581559</v>
       </c>
       <c r="R106" t="n">
-        <v>6958454</v>
+        <v>6958443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11173,10 +11168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127708946</v>
+        <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>91648</v>
+        <v>57832</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11184,34 +11179,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581559</v>
+        <v>581789</v>
       </c>
       <c r="R107" t="n">
-        <v>6958443</v>
+        <v>6958477</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708947</v>
+        <v>127708912</v>
       </c>
       <c r="B109" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581574</v>
+        <v>581558</v>
       </c>
       <c r="R109" t="n">
-        <v>6958443</v>
+        <v>6958357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11464,10 +11464,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B110" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R110" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11535,6 +11535,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11561,10 +11566,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708937</v>
+        <v>127708947</v>
       </c>
       <c r="B111" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11572,21 +11577,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11596,10 +11601,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581457</v>
+        <v>581574</v>
       </c>
       <c r="R111" t="n">
-        <v>6958514</v>
+        <v>6958443</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11632,11 +11637,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -9991,10 +9991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127700375</v>
+        <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>91648</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10002,42 +10002,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>581797</v>
+        <v>581469</v>
       </c>
       <c r="R95" t="n">
-        <v>6958452</v>
+        <v>6958479</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10070,11 +10062,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10101,10 +10088,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127708944</v>
+        <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10112,21 +10099,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10136,10 +10123,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>581469</v>
+        <v>581459</v>
       </c>
       <c r="R96" t="n">
-        <v>6958479</v>
+        <v>6958547</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10198,10 +10185,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127708917</v>
+        <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10209,34 +10196,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>581459</v>
+        <v>581797</v>
       </c>
       <c r="R97" t="n">
-        <v>6958547</v>
+        <v>6958452</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10269,6 +10264,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Tre misstänkta bohål för tretåig hackspett i toppbruten gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10974,10 +10974,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127708942</v>
+        <v>127700450</v>
       </c>
       <c r="B105" t="n">
-        <v>91648</v>
+        <v>57832</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,34 +10985,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581396</v>
+        <v>581789</v>
       </c>
       <c r="R105" t="n">
-        <v>6958454</v>
+        <v>6958477</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,7 +11076,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708946</v>
+        <v>127708942</v>
       </c>
       <c r="B106" t="n">
         <v>91648</v>
@@ -11106,10 +11111,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581559</v>
+        <v>581396</v>
       </c>
       <c r="R106" t="n">
-        <v>6958443</v>
+        <v>6958454</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,10 +11173,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127700450</v>
+        <v>127708946</v>
       </c>
       <c r="B107" t="n">
-        <v>57832</v>
+        <v>91648</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11179,39 +11184,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581789</v>
+        <v>581559</v>
       </c>
       <c r="R107" t="n">
-        <v>6958477</v>
+        <v>6958443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -8317,7 +8317,7 @@
         <v>127622592</v>
       </c>
       <c r="B78" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>127626337</v>
       </c>
       <c r="B79" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>127626361</v>
       </c>
       <c r="B80" t="n">
-        <v>92022</v>
+        <v>92030</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>127627415</v>
       </c>
       <c r="B81" t="n">
-        <v>91553</v>
+        <v>91561</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>127708953</v>
       </c>
       <c r="B82" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>127703408</v>
       </c>
       <c r="B83" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>127708919</v>
       </c>
       <c r="B84" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127708929</v>
+        <v>127702065</v>
       </c>
       <c r="B85" t="n">
-        <v>92049</v>
+        <v>91770</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>4217</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581702</v>
+        <v>581516</v>
       </c>
       <c r="R85" t="n">
-        <v>6958462</v>
+        <v>6958469</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127702065</v>
+        <v>127708940</v>
       </c>
       <c r="B86" t="n">
-        <v>91762</v>
+        <v>57673</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581516</v>
+        <v>581551</v>
       </c>
       <c r="R86" t="n">
-        <v>6958469</v>
+        <v>6958433</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9165,6 +9165,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9191,32 +9196,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708940</v>
+        <v>127708929</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>92057</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9226,10 +9231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581551</v>
+        <v>581702</v>
       </c>
       <c r="R87" t="n">
-        <v>6958433</v>
+        <v>6958462</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9262,11 +9267,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9296,7 +9296,7 @@
         <v>127700444</v>
       </c>
       <c r="B88" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9593,10 +9593,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127702448</v>
+        <v>127708935</v>
       </c>
       <c r="B91" t="n">
-        <v>91648</v>
+        <v>57673</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581480</v>
+        <v>581452</v>
       </c>
       <c r="R91" t="n">
-        <v>6958518</v>
+        <v>6958446</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,6 +9664,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9693,7 +9698,7 @@
         <v>127708921</v>
       </c>
       <c r="B92" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9787,32 +9792,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708951</v>
+        <v>127702448</v>
       </c>
       <c r="B93" t="n">
-        <v>92642</v>
+        <v>91656</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9827,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581943</v>
+        <v>581480</v>
       </c>
       <c r="R93" t="n">
-        <v>6958445</v>
+        <v>6958518</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9863,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708935</v>
+        <v>127708951</v>
       </c>
       <c r="B94" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581452</v>
+        <v>581943</v>
       </c>
       <c r="R94" t="n">
-        <v>6958446</v>
+        <v>6958445</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9994,7 +9994,7 @@
         <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B98" t="n">
-        <v>91352</v>
+        <v>91656</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R98" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,45 +10392,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127701709</v>
+        <v>127708916</v>
       </c>
       <c r="B99" t="n">
-        <v>92049</v>
+        <v>91360</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581590</v>
+        <v>581451</v>
       </c>
       <c r="R99" t="n">
-        <v>6958438</v>
+        <v>6958466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10489,45 +10489,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127708945</v>
+        <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>91648</v>
+        <v>92057</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>581512</v>
+        <v>581590</v>
       </c>
       <c r="R100" t="n">
-        <v>6958472</v>
+        <v>6958438</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10877,45 +10877,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127702553</v>
+        <v>127700450</v>
       </c>
       <c r="B104" t="n">
-        <v>91553</v>
+        <v>57833</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581423</v>
+        <v>581789</v>
       </c>
       <c r="R104" t="n">
-        <v>6958511</v>
+        <v>6958477</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,10 +10979,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127700450</v>
+        <v>127708942</v>
       </c>
       <c r="B105" t="n">
-        <v>57832</v>
+        <v>91656</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,39 +10990,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>581789</v>
+        <v>581396</v>
       </c>
       <c r="R105" t="n">
-        <v>6958477</v>
+        <v>6958454</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11076,10 +11076,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127708942</v>
+        <v>127708946</v>
       </c>
       <c r="B106" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>581396</v>
+        <v>581559</v>
       </c>
       <c r="R106" t="n">
-        <v>6958454</v>
+        <v>6958443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11173,32 +11173,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127708946</v>
+        <v>127702553</v>
       </c>
       <c r="B107" t="n">
-        <v>91648</v>
+        <v>91561</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11208,10 +11208,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581559</v>
+        <v>581423</v>
       </c>
       <c r="R107" t="n">
-        <v>6958443</v>
+        <v>6958511</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B109" t="n">
-        <v>91352</v>
+        <v>57673</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R109" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11438,6 +11438,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11464,10 +11469,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127708937</v>
+        <v>127708947</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>91656</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11475,21 +11480,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11499,10 +11504,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>581457</v>
+        <v>581574</v>
       </c>
       <c r="R110" t="n">
-        <v>6958514</v>
+        <v>6958443</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11535,11 +11540,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11566,10 +11566,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708947</v>
+        <v>127708912</v>
       </c>
       <c r="B111" t="n">
-        <v>91648</v>
+        <v>91360</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11577,21 +11577,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581574</v>
+        <v>581558</v>
       </c>
       <c r="R111" t="n">
-        <v>6958443</v>
+        <v>6958357</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B112" t="n">
-        <v>91352</v>
+        <v>57673</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R112" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,6 +11734,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11760,10 +11765,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>91360</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11771,21 +11776,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11795,10 +11800,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R113" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11831,11 +11836,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127708941</v>
+        <v>127703591</v>
       </c>
       <c r="B114" t="n">
-        <v>91648</v>
+        <v>91718</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581486</v>
+        <v>581485</v>
       </c>
       <c r="R114" t="n">
-        <v>6958333</v>
+        <v>6958325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127702456</v>
+        <v>127708941</v>
       </c>
       <c r="B115" t="n">
-        <v>91352</v>
+        <v>91656</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11970,21 +11970,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581480</v>
+        <v>581486</v>
       </c>
       <c r="R115" t="n">
-        <v>6958518</v>
+        <v>6958333</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127703591</v>
+        <v>127702456</v>
       </c>
       <c r="B116" t="n">
-        <v>91710</v>
+        <v>91360</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581485</v>
+        <v>581480</v>
       </c>
       <c r="R116" t="n">
-        <v>6958325</v>
+        <v>6958518</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12156,7 +12156,7 @@
         <v>127708926</v>
       </c>
       <c r="B117" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>127703413</v>
       </c>
       <c r="B118" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>127708922</v>
       </c>
       <c r="B119" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>127708930</v>
       </c>
       <c r="B120" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>127703745</v>
       </c>
       <c r="B122" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13041,45 +13041,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127708927</v>
+        <v>127701827</v>
       </c>
       <c r="B126" t="n">
-        <v>92049</v>
+        <v>57673</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581489</v>
+        <v>581564</v>
       </c>
       <c r="R126" t="n">
-        <v>6958369</v>
+        <v>6958463</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13112,6 +13117,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13141,7 +13151,7 @@
         <v>127708939</v>
       </c>
       <c r="B127" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13240,50 +13250,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127701827</v>
+        <v>127708959</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>92030</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R128" t="n">
-        <v>6958463</v>
+        <v>6958389</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13316,11 +13321,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,10 +13347,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708949</v>
+        <v>127708927</v>
       </c>
       <c r="B129" t="n">
-        <v>98387</v>
+        <v>92057</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13358,21 +13358,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219790</v>
+        <v>3298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581598</v>
+        <v>581489</v>
       </c>
       <c r="R129" t="n">
-        <v>6958396</v>
+        <v>6958369</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13444,32 +13444,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127708959</v>
+        <v>127708949</v>
       </c>
       <c r="B130" t="n">
-        <v>92022</v>
+        <v>98395</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>898</v>
+        <v>219790</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>581595</v>
+        <v>581598</v>
       </c>
       <c r="R130" t="n">
-        <v>6958389</v>
+        <v>6958396</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708943</v>
+        <v>127708914</v>
       </c>
       <c r="B131" t="n">
-        <v>91648</v>
+        <v>91360</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581472</v>
+        <v>581433</v>
       </c>
       <c r="R131" t="n">
-        <v>6958521</v>
+        <v>6958423</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,10 +13638,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B132" t="n">
-        <v>91352</v>
+        <v>91656</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13649,21 +13649,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R132" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13738,7 +13738,7 @@
         <v>127708952</v>
       </c>
       <c r="B133" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>127702695</v>
       </c>
       <c r="B134" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>127708934</v>
       </c>
       <c r="B135" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -9593,10 +9593,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708935</v>
+        <v>127708921</v>
       </c>
       <c r="B91" t="n">
-        <v>57673</v>
+        <v>91360</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581452</v>
+        <v>581549</v>
       </c>
       <c r="R91" t="n">
-        <v>6958446</v>
+        <v>6958437</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,11 +9664,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9695,10 +9690,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127708921</v>
+        <v>127702448</v>
       </c>
       <c r="B92" t="n">
-        <v>91360</v>
+        <v>91656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9706,21 +9701,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9730,10 +9725,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581549</v>
+        <v>581480</v>
       </c>
       <c r="R92" t="n">
-        <v>6958437</v>
+        <v>6958518</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9792,32 +9787,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127702448</v>
+        <v>127708951</v>
       </c>
       <c r="B93" t="n">
-        <v>91656</v>
+        <v>92650</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9827,10 +9822,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581480</v>
+        <v>581943</v>
       </c>
       <c r="R93" t="n">
-        <v>6958518</v>
+        <v>6958445</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9863,6 +9858,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,32 +9889,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708951</v>
+        <v>127708935</v>
       </c>
       <c r="B94" t="n">
-        <v>92650</v>
+        <v>57673</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581943</v>
+        <v>581452</v>
       </c>
       <c r="R94" t="n">
-        <v>6958445</v>
+        <v>6958446</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10877,50 +10877,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127700450</v>
+        <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>57833</v>
+        <v>91561</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>48</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>581789</v>
+        <v>581423</v>
       </c>
       <c r="R104" t="n">
-        <v>6958477</v>
+        <v>6958511</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11173,45 +11168,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127702553</v>
+        <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>91561</v>
+        <v>57833</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>581423</v>
+        <v>581789</v>
       </c>
       <c r="R107" t="n">
-        <v>6958511</v>
+        <v>6958477</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11663,10 +11663,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127708932</v>
+        <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>57673</v>
+        <v>91360</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11674,21 +11674,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>581817</v>
+        <v>581472</v>
       </c>
       <c r="R112" t="n">
-        <v>6958438</v>
+        <v>6958523</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11734,11 +11734,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11765,10 +11760,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127708918</v>
+        <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>91360</v>
+        <v>57673</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11776,21 +11771,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11800,10 +11795,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>581472</v>
+        <v>581817</v>
       </c>
       <c r="R113" t="n">
-        <v>6958523</v>
+        <v>6958438</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11836,6 +11831,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127703413</v>
+        <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>57833</v>
+        <v>91360</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>581481</v>
+        <v>581560</v>
       </c>
       <c r="R118" t="n">
-        <v>6958339</v>
+        <v>6958445</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12352,10 +12347,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127708922</v>
+        <v>127703413</v>
       </c>
       <c r="B119" t="n">
-        <v>91360</v>
+        <v>57833</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12363,34 +12358,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>581560</v>
+        <v>581481</v>
       </c>
       <c r="R119" t="n">
-        <v>6958445</v>
+        <v>6958339</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -8706,10 +8706,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127708953</v>
+        <v>127703408</v>
       </c>
       <c r="B82" t="n">
-        <v>88761</v>
+        <v>91371</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>581497</v>
+        <v>581481</v>
       </c>
       <c r="R82" t="n">
-        <v>6958369</v>
+        <v>6958339</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8803,10 +8803,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127703408</v>
+        <v>127708919</v>
       </c>
       <c r="B83" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>581481</v>
+        <v>581468</v>
       </c>
       <c r="R83" t="n">
-        <v>6958339</v>
+        <v>6958461</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8900,10 +8900,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127708919</v>
+        <v>127708953</v>
       </c>
       <c r="B84" t="n">
-        <v>91360</v>
+        <v>88772</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8911,21 +8911,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>581468</v>
+        <v>581497</v>
       </c>
       <c r="R84" t="n">
-        <v>6958461</v>
+        <v>6958369</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127702065</v>
+        <v>127708929</v>
       </c>
       <c r="B85" t="n">
-        <v>91770</v>
+        <v>92068</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9008,21 +9008,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9032,10 +9032,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>581516</v>
+        <v>581702</v>
       </c>
       <c r="R85" t="n">
-        <v>6958469</v>
+        <v>6958462</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9094,32 +9094,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127708940</v>
+        <v>127702065</v>
       </c>
       <c r="B86" t="n">
-        <v>57673</v>
+        <v>91781</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>581551</v>
+        <v>581516</v>
       </c>
       <c r="R86" t="n">
-        <v>6958433</v>
+        <v>6958469</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9165,11 +9165,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9196,45 +9191,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127708929</v>
+        <v>127700444</v>
       </c>
       <c r="B87" t="n">
-        <v>92057</v>
+        <v>57844</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>581702</v>
+        <v>581826</v>
       </c>
       <c r="R87" t="n">
-        <v>6958462</v>
+        <v>6958437</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9293,10 +9297,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127700444</v>
+        <v>127708940</v>
       </c>
       <c r="B88" t="n">
-        <v>57833</v>
+        <v>57684</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9304,43 +9308,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>581826</v>
+        <v>581551</v>
       </c>
       <c r="R88" t="n">
-        <v>6958437</v>
+        <v>6958433</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,6 +9368,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9402,7 +9402,7 @@
         <v>127708911</v>
       </c>
       <c r="B89" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>127708910</v>
       </c>
       <c r="B90" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9593,32 +9593,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127708921</v>
+        <v>127708951</v>
       </c>
       <c r="B91" t="n">
-        <v>91360</v>
+        <v>92661</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>581549</v>
+        <v>581943</v>
       </c>
       <c r="R91" t="n">
-        <v>6958437</v>
+        <v>6958445</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9664,6 +9664,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9690,10 +9695,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127702448</v>
+        <v>127708935</v>
       </c>
       <c r="B92" t="n">
-        <v>91656</v>
+        <v>57684</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9701,21 +9706,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9725,10 +9730,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>581480</v>
+        <v>581452</v>
       </c>
       <c r="R92" t="n">
-        <v>6958518</v>
+        <v>6958446</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9761,6 +9766,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9787,32 +9797,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127708951</v>
+        <v>127708921</v>
       </c>
       <c r="B93" t="n">
-        <v>92650</v>
+        <v>91371</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9822,10 +9832,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>581943</v>
+        <v>581549</v>
       </c>
       <c r="R93" t="n">
-        <v>6958445</v>
+        <v>6958437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9858,11 +9868,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9889,10 +9894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127708935</v>
+        <v>127702448</v>
       </c>
       <c r="B94" t="n">
-        <v>57673</v>
+        <v>91667</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9900,21 +9905,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9924,10 +9929,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>581452</v>
+        <v>581480</v>
       </c>
       <c r="R94" t="n">
-        <v>6958446</v>
+        <v>6958518</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9960,11 +9965,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9994,7 +9994,7 @@
         <v>127708944</v>
       </c>
       <c r="B95" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>127708917</v>
       </c>
       <c r="B96" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127708945</v>
+        <v>127708916</v>
       </c>
       <c r="B98" t="n">
-        <v>91656</v>
+        <v>91371</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,21 +10306,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>581512</v>
+        <v>581451</v>
       </c>
       <c r="R98" t="n">
-        <v>6958472</v>
+        <v>6958466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127708916</v>
+        <v>127708945</v>
       </c>
       <c r="B99" t="n">
-        <v>91360</v>
+        <v>91667</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10403,21 +10403,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>581451</v>
+        <v>581512</v>
       </c>
       <c r="R99" t="n">
-        <v>6958466</v>
+        <v>6958472</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
         <v>127701709</v>
       </c>
       <c r="B100" t="n">
-        <v>92057</v>
+        <v>92068</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>127708915</v>
       </c>
       <c r="B101" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>127708920</v>
       </c>
       <c r="B102" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>127708924</v>
       </c>
       <c r="B103" t="n">
-        <v>92057</v>
+        <v>92068</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>127702553</v>
       </c>
       <c r="B104" t="n">
-        <v>91561</v>
+        <v>91572</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>127708942</v>
       </c>
       <c r="B105" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>127708946</v>
       </c>
       <c r="B106" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>127700450</v>
       </c>
       <c r="B107" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>127708913</v>
       </c>
       <c r="B108" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127708937</v>
+        <v>127708912</v>
       </c>
       <c r="B109" t="n">
-        <v>57673</v>
+        <v>91371</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11378,21 +11378,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11402,10 +11402,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>581457</v>
+        <v>581558</v>
       </c>
       <c r="R109" t="n">
-        <v>6958514</v>
+        <v>6958357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11438,11 +11438,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11472,7 +11467,7 @@
         <v>127708947</v>
       </c>
       <c r="B110" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11566,10 +11561,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127708912</v>
+        <v>127708937</v>
       </c>
       <c r="B111" t="n">
-        <v>91360</v>
+        <v>57684</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11577,21 +11572,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11601,10 +11596,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>581558</v>
+        <v>581457</v>
       </c>
       <c r="R111" t="n">
-        <v>6958357</v>
+        <v>6958514</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11637,6 +11632,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran. Lite kåda/sav finns fortfarande kvar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11666,7 +11666,7 @@
         <v>127708918</v>
       </c>
       <c r="B112" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>127708932</v>
       </c>
       <c r="B113" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11862,32 +11862,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127703591</v>
+        <v>127708941</v>
       </c>
       <c r="B114" t="n">
-        <v>91718</v>
+        <v>91667</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11897,10 +11897,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>581485</v>
+        <v>581486</v>
       </c>
       <c r="R114" t="n">
-        <v>6958325</v>
+        <v>6958333</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11959,10 +11959,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127708941</v>
+        <v>127702456</v>
       </c>
       <c r="B115" t="n">
-        <v>91656</v>
+        <v>91371</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11970,21 +11970,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>581486</v>
+        <v>581480</v>
       </c>
       <c r="R115" t="n">
-        <v>6958333</v>
+        <v>6958518</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12056,32 +12056,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127702456</v>
+        <v>127703591</v>
       </c>
       <c r="B116" t="n">
-        <v>91360</v>
+        <v>91729</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>581480</v>
+        <v>581485</v>
       </c>
       <c r="R116" t="n">
-        <v>6958518</v>
+        <v>6958325</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12156,7 +12156,7 @@
         <v>127708926</v>
       </c>
       <c r="B117" t="n">
-        <v>92057</v>
+        <v>92068</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>127708922</v>
       </c>
       <c r="B118" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>127703413</v>
       </c>
       <c r="B119" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>127708930</v>
       </c>
       <c r="B120" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>127708948</v>
       </c>
       <c r="B121" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>127703745</v>
       </c>
       <c r="B122" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>127708923</v>
       </c>
       <c r="B123" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>127708909</v>
       </c>
       <c r="B124" t="n">
-        <v>91360</v>
+        <v>91371</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>127708950</v>
       </c>
       <c r="B125" t="n">
-        <v>98395</v>
+        <v>98407</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13041,50 +13041,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127701827</v>
+        <v>127708959</v>
       </c>
       <c r="B126" t="n">
-        <v>57673</v>
+        <v>92041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Dåvamyan, Mpd</t>
+          <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R126" t="n">
-        <v>6958463</v>
+        <v>6958389</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13117,11 +13112,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13148,32 +13138,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127708939</v>
+        <v>127708927</v>
       </c>
       <c r="B127" t="n">
-        <v>57673</v>
+        <v>92068</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13183,10 +13173,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>581490</v>
+        <v>581489</v>
       </c>
       <c r="R127" t="n">
-        <v>6958459</v>
+        <v>6958369</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13219,11 +13209,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13250,32 +13235,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127708959</v>
+        <v>127708939</v>
       </c>
       <c r="B128" t="n">
-        <v>92030</v>
+        <v>57684</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13285,10 +13270,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>581595</v>
+        <v>581490</v>
       </c>
       <c r="R128" t="n">
-        <v>6958389</v>
+        <v>6958459</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13321,6 +13306,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på fallen död gran</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13347,45 +13337,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127708927</v>
+        <v>127701827</v>
       </c>
       <c r="B129" t="n">
-        <v>92057</v>
+        <v>57684</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Dåvamyran, Mpd</t>
+          <t>Dåvamyan, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>581489</v>
+        <v>581564</v>
       </c>
       <c r="R129" t="n">
-        <v>6958369</v>
+        <v>6958463</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13418,6 +13413,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13447,7 +13447,7 @@
         <v>127708949</v>
       </c>
       <c r="B130" t="n">
-        <v>98395</v>
+        <v>98407</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127708914</v>
+        <v>127708943</v>
       </c>
       <c r="B131" t="n">
-        <v>91360</v>
+        <v>91667</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13552,21 +13552,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>581433</v>
+        <v>581472</v>
       </c>
       <c r="R131" t="n">
-        <v>6958423</v>
+        <v>6958521</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13638,32 +13638,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127708943</v>
+        <v>127708952</v>
       </c>
       <c r="B132" t="n">
-        <v>91656</v>
+        <v>92661</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13673,10 +13673,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>581472</v>
+        <v>581959</v>
       </c>
       <c r="R132" t="n">
-        <v>6958521</v>
+        <v>6958445</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13735,32 +13735,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127708952</v>
+        <v>127708914</v>
       </c>
       <c r="B133" t="n">
-        <v>92650</v>
+        <v>91371</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>581959</v>
+        <v>581433</v>
       </c>
       <c r="R133" t="n">
-        <v>6958445</v>
+        <v>6958423</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13835,7 +13835,7 @@
         <v>127702695</v>
       </c>
       <c r="B134" t="n">
-        <v>80135</v>
+        <v>80146</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>127708934</v>
       </c>
       <c r="B135" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91718</v>
+        <v>91810</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91810</v>
+        <v>91822</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -14038,7 +14038,7 @@
         <v>127701708</v>
       </c>
       <c r="B136" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -8207,7 +8207,7 @@
         <v>127626317</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>57684</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>127701827</v>
       </c>
       <c r="B129" t="n">
-        <v>57684</v>
+        <v>57736</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -8207,7 +8207,7 @@
         <v>127626317</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>127700375</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>127701827</v>
       </c>
       <c r="B129" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 14677-2022 artfynd.xlsx
+++ b/artfynd/A 14677-2022 artfynd.xlsx
@@ -14132,32 +14132,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132986266</v>
+        <v>132985375</v>
       </c>
       <c r="B137" t="n">
-        <v>92217</v>
+        <v>92132</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14167,13 +14167,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>581915</v>
+        <v>581918</v>
       </c>
       <c r="R137" t="n">
-        <v>6958491</v>
+        <v>6958475</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14212,12 +14212,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>3 stycken</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14244,32 +14239,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132985375</v>
+        <v>132985353</v>
       </c>
       <c r="B138" t="n">
-        <v>92132</v>
+        <v>83307</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>48</v>
+        <v>308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14279,13 +14274,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>581918</v>
+        <v>582054</v>
       </c>
       <c r="R138" t="n">
-        <v>6958475</v>
+        <v>6958370</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14314,7 +14309,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14324,7 +14319,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14351,10 +14346,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132985353</v>
+        <v>132986266</v>
       </c>
       <c r="B139" t="n">
-        <v>83307</v>
+        <v>92217</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14362,21 +14357,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14386,13 +14381,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>582054</v>
+        <v>581915</v>
       </c>
       <c r="R139" t="n">
-        <v>6958370</v>
+        <v>6958491</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14421,7 +14416,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14431,7 +14426,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>3 stycken</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14899,10 +14899,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132985283</v>
+        <v>132986222</v>
       </c>
       <c r="B144" t="n">
-        <v>83307</v>
+        <v>83315</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14910,21 +14910,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14934,13 +14934,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>581835</v>
+        <v>581837</v>
       </c>
       <c r="R144" t="n">
-        <v>6958415</v>
+        <v>6958418</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15006,10 +15006,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132985362</v>
+        <v>132985373</v>
       </c>
       <c r="B145" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15017,21 +15017,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>582014</v>
+        <v>581945</v>
       </c>
       <c r="R145" t="n">
-        <v>6958416</v>
+        <v>6958491</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15113,10 +15113,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132986227</v>
+        <v>132985283</v>
       </c>
       <c r="B146" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15124,21 +15124,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>581637</v>
+        <v>581835</v>
       </c>
       <c r="R146" t="n">
-        <v>6958404</v>
+        <v>6958415</v>
       </c>
       <c r="S146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15327,10 +15327,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132986228</v>
+        <v>132985362</v>
       </c>
       <c r="B148" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15338,49 +15338,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>581606</v>
+        <v>582014</v>
       </c>
       <c r="R148" t="n">
-        <v>6958444</v>
+        <v>6958416</v>
       </c>
       <c r="S148" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15409,7 +15397,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15419,12 +15407,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Två videofilmer bifogas. På ena syns en trummande hane. På den andra videon syns en individ födosöka. Möjligen är det frågan om två olika individer då jag inte kan se något gult på huvudet på den som födosöker.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15451,10 +15434,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132985336</v>
+        <v>132986227</v>
       </c>
       <c r="B149" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15462,45 +15445,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>582098</v>
+        <v>581637</v>
       </c>
       <c r="R149" t="n">
-        <v>6958338</v>
+        <v>6958404</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15529,7 +15504,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -15539,12 +15514,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15571,10 +15541,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132986222</v>
+        <v>132986228</v>
       </c>
       <c r="B150" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15582,34 +15552,46 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>581837</v>
+        <v>581606</v>
       </c>
       <c r="R150" t="n">
-        <v>6958418</v>
+        <v>6958444</v>
       </c>
       <c r="S150" t="n">
         <v>3</v>
@@ -15641,7 +15623,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -15651,7 +15633,12 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Två videofilmer bifogas. På ena syns en trummande hane. På den andra videon syns en individ födosöka. Möjligen är det frågan om två olika individer då jag inte kan se något gult på huvudet på den som födosöker.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15678,10 +15665,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132985373</v>
+        <v>132985336</v>
       </c>
       <c r="B151" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15689,34 +15676,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>581945</v>
+        <v>582098</v>
       </c>
       <c r="R151" t="n">
-        <v>6958491</v>
+        <v>6958338</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -15748,7 +15743,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -15758,7 +15753,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15785,10 +15785,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132986231</v>
+        <v>132985356</v>
       </c>
       <c r="B152" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15796,37 +15796,45 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>581607</v>
+        <v>582036</v>
       </c>
       <c r="R152" t="n">
-        <v>6958283</v>
+        <v>6958368</v>
       </c>
       <c r="S152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -15855,7 +15863,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -15865,7 +15873,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15892,10 +15905,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132985335</v>
+        <v>132986238</v>
       </c>
       <c r="B153" t="n">
-        <v>83181</v>
+        <v>56522</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15903,37 +15916,45 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1312</v>
+        <v>206004</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>582073</v>
+        <v>581602</v>
       </c>
       <c r="R153" t="n">
-        <v>6958322</v>
+        <v>6958276</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -15962,7 +15983,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -15972,7 +15993,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -15999,7 +16020,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132985298</v>
+        <v>132986231</v>
       </c>
       <c r="B154" t="n">
         <v>91918</v>
@@ -16034,13 +16055,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>581668</v>
+        <v>581607</v>
       </c>
       <c r="R154" t="n">
-        <v>6958434</v>
+        <v>6958283</v>
       </c>
       <c r="S154" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16069,7 +16090,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16079,7 +16100,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16106,10 +16127,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132985356</v>
+        <v>132985335</v>
       </c>
       <c r="B155" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16117,42 +16138,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>582036</v>
+        <v>582073</v>
       </c>
       <c r="R155" t="n">
-        <v>6958368</v>
+        <v>6958322</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -16184,7 +16197,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16194,12 +16207,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16226,10 +16234,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132986238</v>
+        <v>132985298</v>
       </c>
       <c r="B156" t="n">
-        <v>56522</v>
+        <v>91918</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16237,45 +16245,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>581602</v>
+        <v>581668</v>
       </c>
       <c r="R156" t="n">
-        <v>6958276</v>
+        <v>6958434</v>
       </c>
       <c r="S156" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16555,10 +16555,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132985305</v>
+        <v>132985312</v>
       </c>
       <c r="B159" t="n">
-        <v>83307</v>
+        <v>83181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16566,21 +16566,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16590,13 +16590,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>581574</v>
+        <v>581552</v>
       </c>
       <c r="R159" t="n">
-        <v>6958332</v>
+        <v>6958291</v>
       </c>
       <c r="S159" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16662,10 +16662,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132985312</v>
+        <v>132985303</v>
       </c>
       <c r="B160" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16673,21 +16673,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16697,10 +16697,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>581552</v>
+        <v>581614</v>
       </c>
       <c r="R160" t="n">
-        <v>6958291</v>
+        <v>6958384</v>
       </c>
       <c r="S160" t="n">
         <v>6</v>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16769,10 +16769,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132985303</v>
+        <v>132985305</v>
       </c>
       <c r="B161" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16780,21 +16780,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16804,13 +16804,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>581614</v>
+        <v>581574</v>
       </c>
       <c r="R161" t="n">
-        <v>6958384</v>
+        <v>6958332</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16876,56 +16876,48 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132986236</v>
+        <v>132985379</v>
       </c>
       <c r="B162" t="n">
-        <v>57958</v>
+        <v>79589</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>581608</v>
+        <v>581852</v>
       </c>
       <c r="R162" t="n">
-        <v>6958280</v>
+        <v>6958518</v>
       </c>
       <c r="S162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16954,7 +16946,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -16964,12 +16956,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Ringhack på Tall färska spår</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -16996,48 +16983,56 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132985379</v>
+        <v>132986236</v>
       </c>
       <c r="B163" t="n">
-        <v>79589</v>
+        <v>57958</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>581852</v>
+        <v>581608</v>
       </c>
       <c r="R163" t="n">
-        <v>6958518</v>
+        <v>6958280</v>
       </c>
       <c r="S163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17066,7 +17061,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17076,7 +17071,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ringhack på Tall färska spår</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17103,10 +17103,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132986264</v>
+        <v>132985361</v>
       </c>
       <c r="B164" t="n">
-        <v>57958</v>
+        <v>83307</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17114,45 +17114,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>582007</v>
+        <v>582027</v>
       </c>
       <c r="R164" t="n">
-        <v>6958428</v>
+        <v>6958404</v>
       </c>
       <c r="S164" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17181,7 +17173,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17191,12 +17183,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran ( nedfallet).</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17223,10 +17210,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>132985279</v>
+        <v>132986233</v>
       </c>
       <c r="B165" t="n">
-        <v>78345</v>
+        <v>91918</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17234,21 +17221,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17258,13 +17245,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>581847</v>
+        <v>581603</v>
       </c>
       <c r="R165" t="n">
-        <v>6958390</v>
+        <v>6958292</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17293,7 +17280,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17303,7 +17290,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17330,10 +17317,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>132985361</v>
+        <v>132986243</v>
       </c>
       <c r="B166" t="n">
-        <v>83307</v>
+        <v>91918</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17341,21 +17328,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17365,13 +17352,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>582027</v>
+        <v>581531</v>
       </c>
       <c r="R166" t="n">
-        <v>6958404</v>
+        <v>6958265</v>
       </c>
       <c r="S166" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17400,7 +17387,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17410,7 +17397,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17437,10 +17424,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>132986233</v>
+        <v>132985358</v>
       </c>
       <c r="B167" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17448,21 +17435,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17472,13 +17459,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>581603</v>
+        <v>582012</v>
       </c>
       <c r="R167" t="n">
-        <v>6958292</v>
+        <v>6958394</v>
       </c>
       <c r="S167" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17507,7 +17494,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17517,7 +17504,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17544,10 +17531,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>132986243</v>
+        <v>132985366</v>
       </c>
       <c r="B168" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17555,21 +17542,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17579,13 +17566,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>581531</v>
+        <v>582028</v>
       </c>
       <c r="R168" t="n">
-        <v>6958265</v>
+        <v>6958419</v>
       </c>
       <c r="S168" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17614,7 +17601,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -17624,7 +17611,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17771,10 +17758,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>132985358</v>
+        <v>132986264</v>
       </c>
       <c r="B170" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17782,37 +17769,45 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>582012</v>
+        <v>582007</v>
       </c>
       <c r="R170" t="n">
-        <v>6958394</v>
+        <v>6958428</v>
       </c>
       <c r="S170" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17841,7 +17836,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -17851,7 +17846,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran ( nedfallet).</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17878,10 +17878,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>132985366</v>
+        <v>132985279</v>
       </c>
       <c r="B171" t="n">
-        <v>83315</v>
+        <v>78345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17889,21 +17889,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>582028</v>
+        <v>581847</v>
       </c>
       <c r="R171" t="n">
-        <v>6958419</v>
+        <v>6958390</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17985,10 +17985,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>132986226</v>
+        <v>132985360</v>
       </c>
       <c r="B172" t="n">
-        <v>89300</v>
+        <v>83181</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17996,21 +17996,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18020,13 +18020,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>581692</v>
+        <v>582015</v>
       </c>
       <c r="R172" t="n">
-        <v>6958446</v>
+        <v>6958407</v>
       </c>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18092,10 +18092,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>132985360</v>
+        <v>132986226</v>
       </c>
       <c r="B173" t="n">
-        <v>83181</v>
+        <v>89300</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18103,21 +18103,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18127,13 +18127,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>582015</v>
+        <v>581692</v>
       </c>
       <c r="R173" t="n">
-        <v>6958407</v>
+        <v>6958446</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18559,10 +18559,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>132985297</v>
+        <v>132985300</v>
       </c>
       <c r="B177" t="n">
-        <v>83307</v>
+        <v>83181</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18570,21 +18570,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18594,10 +18594,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>581663</v>
+        <v>581671</v>
       </c>
       <c r="R177" t="n">
-        <v>6958433</v>
+        <v>6958406</v>
       </c>
       <c r="S177" t="n">
         <v>6</v>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18666,7 +18666,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>132985300</v>
+        <v>132986225</v>
       </c>
       <c r="B178" t="n">
         <v>83181</v>
@@ -18701,13 +18701,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>581671</v>
+        <v>581768</v>
       </c>
       <c r="R178" t="n">
-        <v>6958406</v>
+        <v>6958470</v>
       </c>
       <c r="S178" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18773,10 +18773,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>132986225</v>
+        <v>132985297</v>
       </c>
       <c r="B179" t="n">
-        <v>83181</v>
+        <v>83307</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18784,21 +18784,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18808,13 +18808,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>581768</v>
+        <v>581663</v>
       </c>
       <c r="R179" t="n">
-        <v>6958470</v>
+        <v>6958433</v>
       </c>
       <c r="S179" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18983,10 +18983,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>132985296</v>
+        <v>132985314</v>
       </c>
       <c r="B181" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18994,37 +18994,45 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>581683</v>
+        <v>581581</v>
       </c>
       <c r="R181" t="n">
-        <v>6958438</v>
+        <v>6958251</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19053,7 +19061,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19063,7 +19071,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19090,10 +19103,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>132985314</v>
+        <v>132985296</v>
       </c>
       <c r="B182" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19101,45 +19114,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>581581</v>
+        <v>581683</v>
       </c>
       <c r="R182" t="n">
-        <v>6958251</v>
+        <v>6958438</v>
       </c>
       <c r="S182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19168,7 +19173,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19178,12 +19183,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20400,10 +20400,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>132985345</v>
+        <v>132986255</v>
       </c>
       <c r="B194" t="n">
-        <v>57958</v>
+        <v>91938</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20411,45 +20411,33 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>582106</v>
+        <v>582132</v>
       </c>
       <c r="R194" t="n">
-        <v>6958351</v>
+        <v>6958326</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20478,7 +20466,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20488,12 +20476,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20520,10 +20503,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>132986255</v>
+        <v>132985281</v>
       </c>
       <c r="B195" t="n">
-        <v>91938</v>
+        <v>83315</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20531,19 +20514,23 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -20551,13 +20538,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>582132</v>
+        <v>581836</v>
       </c>
       <c r="R195" t="n">
-        <v>6958326</v>
+        <v>6958399</v>
       </c>
       <c r="S195" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20586,7 +20573,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20596,7 +20583,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20623,10 +20610,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>132985281</v>
+        <v>132985345</v>
       </c>
       <c r="B196" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20634,34 +20621,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>581836</v>
+        <v>582106</v>
       </c>
       <c r="R196" t="n">
-        <v>6958399</v>
+        <v>6958351</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -20693,7 +20688,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20703,7 +20698,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20730,10 +20730,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>132985370</v>
+        <v>132985369</v>
       </c>
       <c r="B197" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20741,42 +20741,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>582038</v>
+        <v>582036</v>
       </c>
       <c r="R197" t="n">
-        <v>6958470</v>
+        <v>6958464</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -20808,7 +20800,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -20818,12 +20810,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20850,10 +20837,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>132986248</v>
+        <v>132985351</v>
       </c>
       <c r="B198" t="n">
-        <v>57958</v>
+        <v>89300</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20861,45 +20848,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>581525</v>
+        <v>582085</v>
       </c>
       <c r="R198" t="n">
-        <v>6958253</v>
+        <v>6958352</v>
       </c>
       <c r="S198" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20928,7 +20907,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -20938,12 +20917,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Ringhack på Tall färska spår</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20970,10 +20944,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>132985337</v>
+        <v>132985292</v>
       </c>
       <c r="B199" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20981,42 +20955,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>582133</v>
+        <v>581708</v>
       </c>
       <c r="R199" t="n">
-        <v>6958330</v>
+        <v>6958443</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21048,7 +21014,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21058,19 +21024,14 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål som inte är helt färdigställt. Bohålskammare saknas. Hålet sitter omkring 2.5 m ovan mark. Ser ut att vara relativt färskt. Grantickerötad gran. Innerdiameter på hålet runt 4.5 cm. Biotopen är lämplig för tretåig hackspett.</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG199" t="b">
         <v>0</v>
@@ -21090,32 +21051,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>132985369</v>
+        <v>132985376</v>
       </c>
       <c r="B200" t="n">
-        <v>83181</v>
+        <v>92378</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21125,13 +21086,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>582036</v>
+        <v>581914</v>
       </c>
       <c r="R200" t="n">
-        <v>6958464</v>
+        <v>6958497</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21160,7 +21121,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21170,7 +21131,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21197,10 +21158,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>132985351</v>
+        <v>132985291</v>
       </c>
       <c r="B201" t="n">
-        <v>89300</v>
+        <v>83307</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21208,21 +21169,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21232,13 +21193,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>582085</v>
+        <v>581765</v>
       </c>
       <c r="R201" t="n">
-        <v>6958352</v>
+        <v>6958472</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21267,7 +21228,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21277,7 +21238,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21304,10 +21265,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>132985292</v>
+        <v>132985370</v>
       </c>
       <c r="B202" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21315,34 +21276,42 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>581708</v>
+        <v>582038</v>
       </c>
       <c r="R202" t="n">
-        <v>6958443</v>
+        <v>6958470</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -21374,7 +21343,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21384,7 +21353,12 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21411,48 +21385,56 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>132985376</v>
+        <v>132986248</v>
       </c>
       <c r="B203" t="n">
-        <v>92378</v>
+        <v>57958</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>581914</v>
+        <v>581525</v>
       </c>
       <c r="R203" t="n">
-        <v>6958497</v>
+        <v>6958253</v>
       </c>
       <c r="S203" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21481,7 +21463,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21491,7 +21473,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Ringhack på Tall färska spår</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21518,10 +21505,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>132985291</v>
+        <v>132985337</v>
       </c>
       <c r="B204" t="n">
-        <v>83307</v>
+        <v>57958</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21529,37 +21516,45 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>581765</v>
+        <v>582133</v>
       </c>
       <c r="R204" t="n">
-        <v>6958472</v>
+        <v>6958330</v>
       </c>
       <c r="S204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21588,7 +21583,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21598,14 +21593,19 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål som inte är helt färdigställt. Bohålskammare saknas. Hålet sitter omkring 2.5 m ovan mark. Ser ut att vara relativt färskt. Grantickerötad gran. Innerdiameter på hålet runt 4.5 cm. Biotopen är lämplig för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
       <c r="AE204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -21625,10 +21625,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>132986267</v>
+        <v>132985348</v>
       </c>
       <c r="B205" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21636,37 +21636,45 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>581915</v>
+        <v>582093</v>
       </c>
       <c r="R205" t="n">
-        <v>6958491</v>
+        <v>6958359</v>
       </c>
       <c r="S205" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21695,7 +21703,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21705,7 +21713,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21732,7 +21745,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>132985302</v>
+        <v>132986267</v>
       </c>
       <c r="B206" t="n">
         <v>91918</v>
@@ -21767,13 +21780,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>581632</v>
+        <v>581915</v>
       </c>
       <c r="R206" t="n">
-        <v>6958399</v>
+        <v>6958491</v>
       </c>
       <c r="S206" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21802,7 +21815,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -21812,7 +21825,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21839,10 +21852,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>132985348</v>
+        <v>132985302</v>
       </c>
       <c r="B207" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21850,45 +21863,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>582093</v>
+        <v>581632</v>
       </c>
       <c r="R207" t="n">
-        <v>6958359</v>
+        <v>6958399</v>
       </c>
       <c r="S207" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21917,7 +21922,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -21927,12 +21932,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22601,10 +22601,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>132985334</v>
+        <v>132986242</v>
       </c>
       <c r="B214" t="n">
-        <v>57958</v>
+        <v>91938</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22612,45 +22612,33 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>582088</v>
+        <v>581555</v>
       </c>
       <c r="R214" t="n">
-        <v>6958317</v>
+        <v>6958290</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22679,7 +22667,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -22689,12 +22677,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22721,10 +22704,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>132986242</v>
+        <v>132985334</v>
       </c>
       <c r="B215" t="n">
-        <v>91938</v>
+        <v>57958</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22732,33 +22715,45 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>581555</v>
+        <v>582088</v>
       </c>
       <c r="R215" t="n">
-        <v>6958290</v>
+        <v>6958317</v>
       </c>
       <c r="S215" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22787,7 +22782,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22797,7 +22792,12 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22824,10 +22824,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>132986254</v>
+        <v>132985299</v>
       </c>
       <c r="B216" t="n">
-        <v>83315</v>
+        <v>92217</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22835,21 +22835,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22859,13 +22859,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>582084</v>
+        <v>581664</v>
       </c>
       <c r="R216" t="n">
-        <v>6958300</v>
+        <v>6958424</v>
       </c>
       <c r="S216" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -22931,10 +22931,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>132985299</v>
+        <v>132985341</v>
       </c>
       <c r="B217" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22942,21 +22942,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>581664</v>
+        <v>582141</v>
       </c>
       <c r="R217" t="n">
-        <v>6958424</v>
+        <v>6958341</v>
       </c>
       <c r="S217" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23038,32 +23038,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>132985341</v>
+        <v>132985307</v>
       </c>
       <c r="B218" t="n">
-        <v>91932</v>
+        <v>92614</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23073,10 +23073,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>582141</v>
+        <v>581573</v>
       </c>
       <c r="R218" t="n">
-        <v>6958341</v>
+        <v>6958335</v>
       </c>
       <c r="S218" t="n">
         <v>6</v>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23145,32 +23145,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>132985307</v>
+        <v>132986254</v>
       </c>
       <c r="B219" t="n">
-        <v>92614</v>
+        <v>83315</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>898</v>
+        <v>6440</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23180,13 +23180,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>581573</v>
+        <v>582084</v>
       </c>
       <c r="R219" t="n">
-        <v>6958335</v>
+        <v>6958300</v>
       </c>
       <c r="S219" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23372,10 +23372,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>132985378</v>
+        <v>132985308</v>
       </c>
       <c r="B221" t="n">
-        <v>83181</v>
+        <v>78345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23383,21 +23383,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23407,13 +23407,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>581855</v>
+        <v>581576</v>
       </c>
       <c r="R221" t="n">
-        <v>6958512</v>
+        <v>6958325</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23479,10 +23479,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>132985340</v>
+        <v>132985280</v>
       </c>
       <c r="B222" t="n">
-        <v>83181</v>
+        <v>78345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23490,21 +23490,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23514,13 +23514,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>582139</v>
+        <v>581836</v>
       </c>
       <c r="R222" t="n">
-        <v>6958322</v>
+        <v>6958405</v>
       </c>
       <c r="S222" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23586,7 +23586,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>132985374</v>
+        <v>132985378</v>
       </c>
       <c r="B223" t="n">
         <v>83181</v>
@@ -23621,10 +23621,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>581933</v>
+        <v>581855</v>
       </c>
       <c r="R223" t="n">
-        <v>6958490</v>
+        <v>6958512</v>
       </c>
       <c r="S223" t="n">
         <v>5</v>
@@ -23656,7 +23656,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23693,7 +23693,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>132985295</v>
+        <v>132985340</v>
       </c>
       <c r="B224" t="n">
         <v>83181</v>
@@ -23728,10 +23728,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>581689</v>
+        <v>582139</v>
       </c>
       <c r="R224" t="n">
-        <v>6958438</v>
+        <v>6958322</v>
       </c>
       <c r="S224" t="n">
         <v>6</v>
@@ -23763,7 +23763,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -23773,7 +23773,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23800,10 +23800,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>132985352</v>
+        <v>132985374</v>
       </c>
       <c r="B225" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23811,21 +23811,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23835,10 +23835,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>582068</v>
+        <v>581933</v>
       </c>
       <c r="R225" t="n">
-        <v>6958370</v>
+        <v>6958490</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -23870,7 +23870,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23907,10 +23907,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>132985308</v>
+        <v>132985295</v>
       </c>
       <c r="B226" t="n">
-        <v>78345</v>
+        <v>83181</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23918,21 +23918,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23942,13 +23942,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>581576</v>
+        <v>581689</v>
       </c>
       <c r="R226" t="n">
-        <v>6958325</v>
+        <v>6958438</v>
       </c>
       <c r="S226" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24014,10 +24014,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>132985343</v>
+        <v>132985352</v>
       </c>
       <c r="B227" t="n">
-        <v>57958</v>
+        <v>91932</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24025,42 +24025,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>582122</v>
+        <v>582068</v>
       </c>
       <c r="R227" t="n">
-        <v>6958350</v>
+        <v>6958370</v>
       </c>
       <c r="S227" t="n">
         <v>5</v>
@@ -24092,7 +24084,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24102,12 +24094,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24567,10 +24554,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>132985280</v>
+        <v>132985343</v>
       </c>
       <c r="B232" t="n">
-        <v>78345</v>
+        <v>57958</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24578,34 +24565,42 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Dåvamyran, Mpd</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>581836</v>
+        <v>582122</v>
       </c>
       <c r="R232" t="n">
-        <v>6958405</v>
+        <v>6958350</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -24637,7 +24632,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24647,7 +24642,12 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24674,32 +24674,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>132985309</v>
+        <v>132985380</v>
       </c>
       <c r="B233" t="n">
-        <v>83181</v>
+        <v>79589</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1312</v>
+        <v>6459</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24709,13 +24709,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>581573</v>
+        <v>581844</v>
       </c>
       <c r="R233" t="n">
-        <v>6958329</v>
+        <v>6958513</v>
       </c>
       <c r="S233" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>16:41</t>
         </i